--- a/app_notas_uis.xlsx
+++ b/app_notas_uis.xlsx
@@ -19,6 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="10.0"/>
@@ -52,7 +55,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -67,6 +70,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
@@ -83,7 +89,52 @@
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCC0000"/>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -426,7 +477,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
         <v>2.1</v>
@@ -468,13 +522,13 @@
         <v>0</v>
       </c>
       <c r="Q2" s="4"/>
-      <c r="R2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.615)</f>
-        <v>1.615</v>
-      </c>
-      <c r="S2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5383333333333333)</f>
-        <v>0.5383333333</v>
+      <c r="R2" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2150000000000003)</f>
+        <v>2.215</v>
+      </c>
+      <c r="S2" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7383333333333334)</f>
+        <v>0.7383333333</v>
       </c>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
@@ -506,7 +560,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -548,13 +605,13 @@
         <v>5</v>
       </c>
       <c r="Q3" s="4"/>
-      <c r="R3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.535)</f>
-        <v>2.535</v>
-      </c>
-      <c r="S3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8450000000000001)</f>
-        <v>0.845</v>
+      <c r="R3" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1350000000000002)</f>
+        <v>3.135</v>
+      </c>
+      <c r="S3" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0450000000000002)</f>
+        <v>1.045</v>
       </c>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
@@ -586,7 +643,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -628,13 +688,13 @@
         <v>5</v>
       </c>
       <c r="Q4" s="4"/>
-      <c r="R4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.325)</f>
-        <v>2.325</v>
-      </c>
-      <c r="S4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.775)</f>
-        <v>0.775</v>
+      <c r="R4" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.925)</f>
+        <v>2.925</v>
+      </c>
+      <c r="S4" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.975)</f>
+        <v>0.975</v>
       </c>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -666,7 +726,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -708,13 +771,13 @@
         <v>5</v>
       </c>
       <c r="Q5" s="4"/>
-      <c r="R5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6399999999999997)</f>
-        <v>2.64</v>
-      </c>
-      <c r="S5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8799999999999999)</f>
-        <v>0.88</v>
+      <c r="R5" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.24)</f>
+        <v>3.24</v>
+      </c>
+      <c r="S5" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
+        <v>1.08</v>
       </c>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
@@ -746,7 +809,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -788,13 +854,13 @@
         <v>5</v>
       </c>
       <c r="Q6" s="4"/>
-      <c r="R6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5300000000000002)</f>
-        <v>2.53</v>
-      </c>
-      <c r="S6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8433333333333334)</f>
-        <v>0.8433333333</v>
+      <c r="R6" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.13)</f>
+        <v>3.13</v>
+      </c>
+      <c r="S6" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0433333333333332)</f>
+        <v>1.043333333</v>
       </c>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
@@ -826,7 +892,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -868,13 +937,13 @@
         <v>5</v>
       </c>
       <c r="Q7" s="4"/>
-      <c r="R7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0100000000000002)</f>
-        <v>2.01</v>
-      </c>
-      <c r="S7" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.67)</f>
-        <v>0.67</v>
+      <c r="R7" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6100000000000003)</f>
+        <v>2.61</v>
+      </c>
+      <c r="S7" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8700000000000001)</f>
+        <v>0.87</v>
       </c>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
@@ -906,7 +975,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -948,13 +1020,13 @@
         <v>5</v>
       </c>
       <c r="Q8" s="4"/>
-      <c r="R8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.975)</f>
-        <v>1.975</v>
-      </c>
-      <c r="S8" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6583333333333333)</f>
-        <v>0.6583333333</v>
+      <c r="R8" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.575)</f>
+        <v>2.575</v>
+      </c>
+      <c r="S8" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8583333333333334)</f>
+        <v>0.8583333333</v>
       </c>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -986,7 +1058,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G9" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -1028,13 +1103,13 @@
         <v>5</v>
       </c>
       <c r="Q9" s="4"/>
-      <c r="R9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.665)</f>
-        <v>2.665</v>
-      </c>
-      <c r="S9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8883333333333333)</f>
-        <v>0.8883333333</v>
+      <c r="R9" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2649999999999997)</f>
+        <v>3.265</v>
+      </c>
+      <c r="S9" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0883333333333332)</f>
+        <v>1.088333333</v>
       </c>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
@@ -1066,7 +1141,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -1108,13 +1186,13 @@
         <v>5</v>
       </c>
       <c r="Q10" s="4"/>
-      <c r="R10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.74)</f>
-        <v>2.74</v>
-      </c>
-      <c r="S10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9133333333333334)</f>
-        <v>0.9133333333</v>
+      <c r="R10" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.34)</f>
+        <v>3.34</v>
+      </c>
+      <c r="S10" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1133333333333333)</f>
+        <v>1.113333333</v>
       </c>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
@@ -1146,7 +1224,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -1188,13 +1269,13 @@
         <v>5</v>
       </c>
       <c r="Q11" s="4"/>
-      <c r="R11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.48)</f>
-        <v>2.48</v>
-      </c>
-      <c r="S11" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8266666666666667)</f>
-        <v>0.8266666667</v>
+      <c r="R11" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.08)</f>
+        <v>3.08</v>
+      </c>
+      <c r="S11" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0266666666666666)</f>
+        <v>1.026666667</v>
       </c>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
@@ -1226,7 +1307,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G12" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
         <v>3.1</v>
@@ -1268,13 +1352,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="4"/>
-      <c r="R12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3200000000000003)</f>
-        <v>2.32</v>
-      </c>
-      <c r="S12" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7733333333333334)</f>
-        <v>0.7733333333</v>
+      <c r="R12" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.92)</f>
+        <v>2.92</v>
+      </c>
+      <c r="S12" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9733333333333333)</f>
+        <v>0.9733333333</v>
       </c>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
@@ -1306,7 +1390,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F13" s="4"/>
+      <c r="F13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
         <v>2.1</v>
@@ -1348,13 +1435,13 @@
         <v>5</v>
       </c>
       <c r="Q13" s="4"/>
-      <c r="R13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.865)</f>
-        <v>0.865</v>
-      </c>
-      <c r="S13" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.28833333333333333)</f>
-        <v>0.2883333333</v>
+      <c r="R13" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4649999999999999)</f>
+        <v>1.465</v>
+      </c>
+      <c r="S13" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4883333333333333)</f>
+        <v>0.4883333333</v>
       </c>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -1386,7 +1473,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
         <v>2.3</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G14" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -1428,13 +1518,13 @@
         <v>4</v>
       </c>
       <c r="Q14" s="4"/>
-      <c r="R14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.175)</f>
-        <v>3.175</v>
-      </c>
-      <c r="S14" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0583333333333333)</f>
-        <v>1.058333333</v>
+      <c r="R14" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7750000000000004)</f>
+        <v>3.775</v>
+      </c>
+      <c r="S14" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2583333333333335)</f>
+        <v>1.258333333</v>
       </c>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -1466,7 +1556,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F15" s="4"/>
+      <c r="F15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G15" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -1508,13 +1601,13 @@
         <v>5</v>
       </c>
       <c r="Q15" s="4"/>
-      <c r="R15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
-      </c>
-      <c r="S15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8666666666666667)</f>
-        <v>0.8666666667</v>
+      <c r="R15" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
+      <c r="S15" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0666666666666667)</f>
+        <v>1.066666667</v>
       </c>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
@@ -1546,7 +1639,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
@@ -1588,13 +1684,13 @@
         <v>5</v>
       </c>
       <c r="Q16" s="4"/>
-      <c r="R16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.76)</f>
-        <v>2.76</v>
-      </c>
-      <c r="S16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9199999999999999)</f>
-        <v>0.92</v>
+      <c r="R16" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.36)</f>
+        <v>3.36</v>
+      </c>
+      <c r="S16" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1199999999999999)</f>
+        <v>1.12</v>
       </c>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
@@ -1626,7 +1722,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G17" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -1668,13 +1767,13 @@
         <v>5</v>
       </c>
       <c r="Q17" s="4"/>
-      <c r="R17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.245)</f>
-        <v>2.245</v>
-      </c>
-      <c r="S17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7483333333333334)</f>
-        <v>0.7483333333</v>
+      <c r="R17" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8449999999999998)</f>
+        <v>2.845</v>
+      </c>
+      <c r="S17" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9483333333333333)</f>
+        <v>0.9483333333</v>
       </c>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
@@ -1706,7 +1805,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F18" s="4"/>
+      <c r="F18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G18" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -1748,13 +1850,13 @@
         <v>5</v>
       </c>
       <c r="Q18" s="4"/>
-      <c r="R18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.865)</f>
-        <v>2.865</v>
-      </c>
-      <c r="S18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9550000000000001)</f>
-        <v>0.955</v>
+      <c r="R18" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.465)</f>
+        <v>3.465</v>
+      </c>
+      <c r="S18" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.155)</f>
+        <v>1.155</v>
       </c>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
@@ -1786,7 +1888,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F19" s="4"/>
+      <c r="F19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G19" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -1828,13 +1933,13 @@
         <v>5</v>
       </c>
       <c r="Q19" s="4"/>
-      <c r="R19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.43)</f>
-        <v>2.43</v>
-      </c>
-      <c r="S19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.81)</f>
-        <v>0.81</v>
+      <c r="R19" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.03)</f>
+        <v>3.03</v>
+      </c>
+      <c r="S19" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
+        <v>1.01</v>
       </c>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
@@ -1866,7 +1971,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F20" s="4"/>
+      <c r="F20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G20" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
@@ -1908,13 +2016,13 @@
         <v>5</v>
       </c>
       <c r="Q20" s="4"/>
-      <c r="R20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.225)</f>
-        <v>3.225</v>
-      </c>
-      <c r="S20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.075)</f>
-        <v>1.075</v>
+      <c r="R20" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.825)</f>
+        <v>3.825</v>
+      </c>
+      <c r="S20" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2750000000000001)</f>
+        <v>1.275</v>
       </c>
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
@@ -1946,7 +2054,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F21" s="4"/>
+      <c r="F21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G21" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -1988,13 +2099,13 @@
         <v>3</v>
       </c>
       <c r="Q21" s="4"/>
-      <c r="R21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.965)</f>
-        <v>2.965</v>
-      </c>
-      <c r="S21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9883333333333333)</f>
-        <v>0.9883333333</v>
+      <c r="R21" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5649999999999995)</f>
+        <v>3.565</v>
+      </c>
+      <c r="S21" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1883333333333332)</f>
+        <v>1.188333333</v>
       </c>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
@@ -2026,7 +2137,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F22" s="4"/>
+      <c r="F22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G22" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -2068,13 +2182,13 @@
         <v>5</v>
       </c>
       <c r="Q22" s="4"/>
-      <c r="R22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3649999999999998)</f>
-        <v>2.365</v>
-      </c>
-      <c r="S22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7883333333333332)</f>
-        <v>0.7883333333</v>
+      <c r="R22" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.965)</f>
+        <v>2.965</v>
+      </c>
+      <c r="S22" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9883333333333333)</f>
+        <v>0.9883333333</v>
       </c>
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
@@ -2106,7 +2220,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F23" s="4"/>
+      <c r="F23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G23" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -2148,13 +2265,13 @@
         <v>5</v>
       </c>
       <c r="Q23" s="4"/>
-      <c r="R23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3249999999999997)</f>
-        <v>2.325</v>
-      </c>
-      <c r="S23" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7749999999999999)</f>
-        <v>0.775</v>
+      <c r="R23" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.925)</f>
+        <v>2.925</v>
+      </c>
+      <c r="S23" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.975)</f>
+        <v>0.975</v>
       </c>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
@@ -2186,7 +2303,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F24" s="4"/>
+      <c r="F24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G24" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -2228,13 +2348,13 @@
         <v>5</v>
       </c>
       <c r="Q24" s="4"/>
-      <c r="R24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="S24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7666666666666666)</f>
-        <v>0.7666666667</v>
+      <c r="R24" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9000000000000004)</f>
+        <v>2.9</v>
+      </c>
+      <c r="S24" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9666666666666668)</f>
+        <v>0.9666666667</v>
       </c>
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
@@ -2266,7 +2386,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
         <v>1.4</v>
       </c>
-      <c r="F25" s="4"/>
+      <c r="F25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -2308,13 +2431,13 @@
         <v>5</v>
       </c>
       <c r="Q25" s="4"/>
-      <c r="R25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.055)</f>
-        <v>3.055</v>
-      </c>
-      <c r="S25" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0183333333333333)</f>
-        <v>1.018333333</v>
+      <c r="R25" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6550000000000002)</f>
+        <v>3.655</v>
+      </c>
+      <c r="S25" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2183333333333335)</f>
+        <v>1.218333333</v>
       </c>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
@@ -2346,7 +2469,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
         <v>1.4</v>
       </c>
-      <c r="F26" s="4"/>
+      <c r="F26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G26" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
         <v>3.9</v>
@@ -2388,13 +2514,13 @@
         <v>5</v>
       </c>
       <c r="Q26" s="4"/>
-      <c r="R26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.615)</f>
-        <v>2.615</v>
-      </c>
-      <c r="S26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8716666666666667)</f>
-        <v>0.8716666667</v>
+      <c r="R26" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2150000000000003)</f>
+        <v>3.215</v>
+      </c>
+      <c r="S26" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0716666666666668)</f>
+        <v>1.071666667</v>
       </c>
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
@@ -2426,7 +2552,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="F27" s="4"/>
+      <c r="F27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -2468,13 +2597,13 @@
         <v>4</v>
       </c>
       <c r="Q27" s="4"/>
-      <c r="R27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5250000000000004)</f>
-        <v>2.525</v>
-      </c>
-      <c r="S27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8416666666666668)</f>
-        <v>0.8416666667</v>
+      <c r="R27" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.125)</f>
+        <v>3.125</v>
+      </c>
+      <c r="S27" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0416666666666667)</f>
+        <v>1.041666667</v>
       </c>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
@@ -2506,7 +2635,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
@@ -2548,13 +2680,13 @@
         <v>5</v>
       </c>
       <c r="Q28" s="4"/>
-      <c r="R28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.815)</f>
-        <v>1.815</v>
-      </c>
-      <c r="S28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.605)</f>
-        <v>0.605</v>
+      <c r="R28" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.415)</f>
+        <v>2.415</v>
+      </c>
+      <c r="S28" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.805)</f>
+        <v>0.805</v>
       </c>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
@@ -2586,7 +2718,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G29" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -2628,13 +2763,13 @@
         <v>5</v>
       </c>
       <c r="Q29" s="4"/>
-      <c r="R29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.74)</f>
-        <v>2.74</v>
-      </c>
-      <c r="S29" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9133333333333334)</f>
-        <v>0.9133333333</v>
+      <c r="R29" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.34)</f>
+        <v>3.34</v>
+      </c>
+      <c r="S29" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1133333333333333)</f>
+        <v>1.113333333</v>
       </c>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
@@ -2646,6 +2781,22 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="R2:R29">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R29">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>2.8</formula>
+      <formula>2.999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R29">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>2.8</formula>
+    </cfRule>
+  </conditionalFormatting>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2703,11 +2854,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="8" t="str">
+      <c r="H1" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(10%)")</f>
         <v>TUTORIAS(10%)</v>
       </c>
-      <c r="I1" s="8" t="str">
+      <c r="I1" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu(20%)")</f>
         <v>PQT+Tu(20%)</v>
       </c>
@@ -2728,25 +2879,19 @@
         <v>Tr2</v>
       </c>
       <c r="N1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta2")</f>
-        <v>Ta2</v>
-      </c>
-      <c r="O1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr2")</f>
-        <v>Tr2</v>
-      </c>
-      <c r="P1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta3")</f>
-        <v>Ta3</v>
-      </c>
-      <c r="Q1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr3")</f>
         <v>Tr3</v>
       </c>
-      <c r="R1" s="1" t="str">
+      <c r="O1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Q2")</f>
+        <v>Q2</v>
+      </c>
+      <c r="P1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr4")</f>
         <v>Tr4</v>
       </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
       <c r="S1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
         <v>FINAL</v>
@@ -2788,16 +2933,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -2815,24 +2963,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N2" s="4"/>
+      <c r="N2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1149999999999998)</f>
-        <v>2.115</v>
-      </c>
-      <c r="T2" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.705)</f>
-        <v>0.705</v>
+      <c r="S2" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.375)</f>
+        <v>3.375</v>
+      </c>
+      <c r="T2" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.125)</f>
+        <v>1.125</v>
       </c>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="4">
@@ -2858,7 +3009,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -2885,18 +3039,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N3" s="4"/>
+      <c r="N3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-      <c r="S3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.48)</f>
-        <v>2.48</v>
-      </c>
-      <c r="T3" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8266666666666667)</f>
-        <v>0.8266666667</v>
+      <c r="S3" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.96)</f>
+        <v>3.96</v>
+      </c>
+      <c r="T3" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
+        <v>1.32</v>
       </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
@@ -2928,7 +3085,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -2955,18 +3115,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N4" s="4"/>
+      <c r="N4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.48)</f>
-        <v>2.48</v>
-      </c>
-      <c r="T4" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8266666666666667)</f>
-        <v>0.8266666667</v>
+      <c r="S4" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.96)</f>
+        <v>3.96</v>
+      </c>
+      <c r="T4" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
+        <v>1.32</v>
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
@@ -2998,16 +3161,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
-        <v>0.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7)</f>
+        <v>0.7</v>
       </c>
       <c r="J5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -3025,24 +3191,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N5" s="4"/>
+      <c r="N5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4549999999999998)</f>
-        <v>1.455</v>
-      </c>
-      <c r="T5" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.48499999999999993)</f>
-        <v>0.485</v>
+      <c r="S5" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.335)</f>
+        <v>2.335</v>
+      </c>
+      <c r="T5" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7783333333333333)</f>
+        <v>0.7783333333</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
       </c>
       <c r="X5" s="4"/>
       <c r="Y5" s="4">
@@ -3068,16 +3237,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
-        <v>1.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
+        <v>0.9</v>
       </c>
       <c r="J6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3095,24 +3267,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="4"/>
+      <c r="N6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7599999999999998)</f>
-        <v>1.76</v>
-      </c>
-      <c r="T6" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5866666666666666)</f>
-        <v>0.5866666667</v>
+      <c r="S6" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.73)</f>
+        <v>2.73</v>
+      </c>
+      <c r="T6" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.91)</f>
+        <v>0.91</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="X6" s="4"/>
       <c r="Y6" s="4">
@@ -3138,7 +3313,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3165,18 +3343,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N7" s="4"/>
+      <c r="N7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
-      <c r="S7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.375)</f>
-        <v>2.375</v>
-      </c>
-      <c r="T7" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7916666666666666)</f>
-        <v>0.7916666667</v>
+      <c r="S7" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.875)</f>
+        <v>3.875</v>
+      </c>
+      <c r="T7" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2916666666666667)</f>
+        <v>1.291666667</v>
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
@@ -3208,7 +3389,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3235,18 +3419,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N8" s="4"/>
+      <c r="N8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.125)</f>
-        <v>2.125</v>
-      </c>
-      <c r="T8" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7083333333333334)</f>
-        <v>0.7083333333</v>
+      <c r="S8" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.625)</f>
+        <v>3.625</v>
+      </c>
+      <c r="T8" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2083333333333333)</f>
+        <v>1.208333333</v>
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
@@ -3278,16 +3465,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J9" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -3305,24 +3495,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N9" s="4"/>
+      <c r="N9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.26)</f>
-        <v>2.26</v>
-      </c>
-      <c r="T9" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7533333333333333)</f>
-        <v>0.7533333333</v>
+      <c r="S9" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.44)</f>
+        <v>3.44</v>
+      </c>
+      <c r="T9" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1466666666666667)</f>
+        <v>1.146666667</v>
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="4">
@@ -3348,11 +3541,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4">
@@ -3375,24 +3571,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N10" s="4"/>
+      <c r="N10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
-      <c r="S10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.43)</f>
-        <v>2.43</v>
-      </c>
-      <c r="T10" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.81)</f>
-        <v>0.81</v>
+      <c r="S10" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.88)</f>
+        <v>3.88</v>
+      </c>
+      <c r="T10" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2933333333333332)</f>
+        <v>1.293333333</v>
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X10" s="4"/>
       <c r="Y10" s="4">
@@ -3418,7 +3617,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -3445,18 +3647,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N11" s="4"/>
+      <c r="N11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
-      <c r="S11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.22)</f>
-        <v>2.22</v>
-      </c>
-      <c r="T11" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7400000000000001)</f>
-        <v>0.74</v>
+      <c r="S11" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.79)</f>
+        <v>2.79</v>
+      </c>
+      <c r="T11" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.93)</f>
+        <v>0.93</v>
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
@@ -3488,7 +3693,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3515,18 +3723,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N12" s="4"/>
+      <c r="N12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
-      <c r="S12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.375)</f>
-        <v>2.375</v>
-      </c>
-      <c r="T12" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7916666666666666)</f>
-        <v>0.7916666667</v>
+      <c r="S12" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.855)</f>
+        <v>3.855</v>
+      </c>
+      <c r="T12" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.285)</f>
+        <v>1.285</v>
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
@@ -3558,7 +3769,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3585,18 +3799,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N13" s="4"/>
+      <c r="N13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
-      <c r="S13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="T13" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7666666666666666)</f>
-        <v>0.7666666667</v>
+      <c r="S13" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="T13" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2666666666666666)</f>
+        <v>1.266666667</v>
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
@@ -3628,7 +3845,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3655,18 +3875,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N14" s="4"/>
+      <c r="N14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-      <c r="S14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.475)</f>
-        <v>2.475</v>
-      </c>
-      <c r="T14" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8250000000000001)</f>
-        <v>0.825</v>
+      <c r="S14" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.975)</f>
+        <v>3.975</v>
+      </c>
+      <c r="T14" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.325)</f>
+        <v>1.325</v>
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
@@ -3698,16 +3921,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="J15" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3725,24 +3951,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N15" s="4"/>
+      <c r="N15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
-      <c r="S15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.38)</f>
-        <v>2.38</v>
-      </c>
-      <c r="T15" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7933333333333333)</f>
-        <v>0.7933333333</v>
+      <c r="S15" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.58)</f>
+        <v>3.58</v>
+      </c>
+      <c r="T15" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1933333333333334)</f>
+        <v>1.193333333</v>
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="X15" s="4"/>
       <c r="Y15" s="4">
@@ -3768,16 +3997,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
-        <v>1.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
       </c>
       <c r="J16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3795,24 +4027,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="4"/>
+      <c r="N16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4249999999999998)</f>
-        <v>1.425</v>
-      </c>
-      <c r="T16" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4749999999999999)</f>
-        <v>0.475</v>
+      <c r="S16" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.735)</f>
+        <v>2.735</v>
+      </c>
+      <c r="T16" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9116666666666666)</f>
+        <v>0.9116666667</v>
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="X16" s="4"/>
       <c r="Y16" s="4">
@@ -3838,11 +4073,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4">
@@ -3865,24 +4103,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N17" s="4"/>
+      <c r="N17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
-      <c r="S17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9999999999999998)</f>
-        <v>2</v>
-      </c>
-      <c r="T17" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6666666666666666)</f>
-        <v>0.6666666667</v>
+      <c r="S17" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.13)</f>
+        <v>3.13</v>
+      </c>
+      <c r="T17" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0433333333333332)</f>
+        <v>1.043333333</v>
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X17" s="4"/>
       <c r="Y17" s="4">
@@ -3908,7 +4149,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -3935,18 +4179,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N18" s="4"/>
+      <c r="N18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
-      <c r="S18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.355)</f>
-        <v>2.355</v>
-      </c>
-      <c r="T18" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.785)</f>
-        <v>0.785</v>
+      <c r="S18" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.835)</f>
+        <v>3.835</v>
+      </c>
+      <c r="T18" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2783333333333333)</f>
+        <v>1.278333333</v>
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
@@ -3978,11 +4225,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4">
@@ -4005,24 +4255,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N19" s="4"/>
+      <c r="N19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
-      <c r="S19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
-      </c>
-      <c r="T19" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7333333333333334)</f>
-        <v>0.7333333333</v>
+      <c r="S19" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.67)</f>
+        <v>3.67</v>
+      </c>
+      <c r="T19" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2233333333333334)</f>
+        <v>1.223333333</v>
       </c>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X19" s="4"/>
       <c r="Y19" s="4">
@@ -4048,16 +4301,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="E20" s="4"/>
+      <c r="E20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="J20" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4075,24 +4331,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="4"/>
+      <c r="N20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.955)</f>
-        <v>1.955</v>
-      </c>
-      <c r="T20" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6516666666666667)</f>
-        <v>0.6516666667</v>
+      <c r="S20" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.375)</f>
+        <v>3.375</v>
+      </c>
+      <c r="T20" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.125)</f>
+        <v>1.125</v>
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="X20" s="4"/>
       <c r="Y20" s="4">
@@ -4118,7 +4377,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -4145,18 +4407,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N21" s="4"/>
+      <c r="N21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
-      <c r="S21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.33)</f>
-        <v>2.33</v>
-      </c>
-      <c r="T21" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7766666666666667)</f>
-        <v>0.7766666667</v>
+      <c r="S21" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8099999999999996)</f>
+        <v>3.81</v>
+      </c>
+      <c r="T21" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2699999999999998)</f>
+        <v>1.27</v>
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
@@ -4188,16 +4453,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="J22" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4215,24 +4483,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="4"/>
+      <c r="N22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
-      <c r="S22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.775)</f>
-        <v>1.775</v>
-      </c>
-      <c r="T22" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5916666666666667)</f>
-        <v>0.5916666667</v>
+      <c r="S22" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.925)</f>
+        <v>2.925</v>
+      </c>
+      <c r="T22" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.975)</f>
+        <v>0.975</v>
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
       <c r="W22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="X22" s="4"/>
       <c r="Y22" s="4">
@@ -4258,7 +4529,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -4285,18 +4559,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N23" s="4"/>
+      <c r="N23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
-      <c r="S23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.23)</f>
-        <v>2.23</v>
-      </c>
-      <c r="T23" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7433333333333333)</f>
-        <v>0.7433333333</v>
+      <c r="S23" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.71)</f>
+        <v>3.71</v>
+      </c>
+      <c r="T23" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2366666666666666)</f>
+        <v>1.236666667</v>
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
@@ -4328,16 +4605,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J24" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -4355,24 +4635,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N24" s="4"/>
+      <c r="N24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O24" s="4"/>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
-      <c r="S24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.46)</f>
-        <v>2.46</v>
-      </c>
-      <c r="T24" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.82)</f>
-        <v>0.82</v>
+      <c r="S24" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.94)</f>
+        <v>3.94</v>
+      </c>
+      <c r="T24" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3133333333333332)</f>
+        <v>1.313333333</v>
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X24" s="4"/>
       <c r="Y24" s="4">
@@ -4398,7 +4681,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E25" s="4"/>
+      <c r="E25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4425,18 +4711,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N25" s="4"/>
+      <c r="N25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
-      <c r="S25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
-      </c>
-      <c r="T25" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8333333333333334)</f>
-        <v>0.8333333333</v>
+      <c r="S25" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="T25" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3333333333333333)</f>
+        <v>1.333333333</v>
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
@@ -4468,16 +4757,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="E26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="J26" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -4495,24 +4787,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N26" s="4"/>
+      <c r="N26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
-      <c r="S26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4849999999999999)</f>
-        <v>1.485</v>
-      </c>
-      <c r="T26" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.49499999999999994)</f>
-        <v>0.495</v>
+      <c r="S26" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.625)</f>
+        <v>2.625</v>
+      </c>
+      <c r="T26" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.875)</f>
+        <v>0.875</v>
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="X26" s="4"/>
       <c r="Y26" s="4">
@@ -4538,16 +4833,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E27" s="4"/>
+      <c r="E27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="J27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -4565,24 +4863,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N27" s="4"/>
+      <c r="N27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
-      <c r="S27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.43)</f>
-        <v>2.43</v>
-      </c>
-      <c r="T27" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.81)</f>
-        <v>0.81</v>
+      <c r="S27" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4000000000000004)</f>
+        <v>3.4</v>
+      </c>
+      <c r="T27" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1333333333333335)</f>
+        <v>1.133333333</v>
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
       <c r="W27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="X27" s="4"/>
       <c r="Y27" s="4">
@@ -4608,7 +4909,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E28" s="4"/>
+      <c r="E28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -4635,18 +4939,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N28" s="4"/>
+      <c r="N28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
-      <c r="S28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.105)</f>
-        <v>2.105</v>
-      </c>
-      <c r="T28" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7016666666666667)</f>
-        <v>0.7016666667</v>
+      <c r="S28" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.585)</f>
+        <v>3.585</v>
+      </c>
+      <c r="T28" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.195)</f>
+        <v>1.195</v>
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
@@ -4678,16 +4985,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E29" s="4"/>
+      <c r="E29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J29" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -4705,24 +5015,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N29" s="4"/>
+      <c r="N29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
-      <c r="S29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.44)</f>
-        <v>2.44</v>
-      </c>
-      <c r="T29" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8133333333333334)</f>
-        <v>0.8133333333</v>
+      <c r="S29" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.88)</f>
+        <v>3.88</v>
+      </c>
+      <c r="T29" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2933333333333332)</f>
+        <v>1.293333333</v>
       </c>
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
       <c r="W29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X29" s="4"/>
       <c r="Y29" s="4">
@@ -4732,6 +5045,22 @@
       <c r="Z29" s="4"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="S2:S29">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S29">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>2.8</formula>
+      <formula>2.999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S29">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>2.8</formula>
+    </cfRule>
+  </conditionalFormatting>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4788,11 +5117,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="8" t="str">
+      <c r="H1" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(8%)")</f>
         <v>TUTORIAS(8%)</v>
       </c>
-      <c r="I1" s="8" t="str">
+      <c r="I1" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu")</f>
         <v>PQT+Tu</v>
       </c>
@@ -4832,25 +5161,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr4")</f>
         <v>Tr4</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="1"/>
+      <c r="T1" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
         <v>FINAL</v>
       </c>
-      <c r="T1" s="1" t="str">
+      <c r="U1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"meta3.0")</f>
         <v>meta3.0</v>
       </c>
-      <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="str">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"pqt(real)")</f>
         <v>pqt(real)</v>
       </c>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COD")</f>
-        <v>COD</v>
-      </c>
+      <c r="Y1" s="1"/>
       <c r="Z1" s="4"/>
     </row>
     <row r="2">
@@ -4874,7 +5200,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
@@ -4920,25 +5249,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8989999999999996)</f>
-        <v>2.899</v>
-      </c>
-      <c r="T2" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9663333333333332)</f>
-        <v>0.9663333333</v>
-      </c>
-      <c r="U2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.635)</f>
+        <v>3.635</v>
+      </c>
+      <c r="U2" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2116666666666667)</f>
+        <v>1.211666667</v>
+      </c>
       <c r="V2" s="4"/>
-      <c r="W2" s="4">
+      <c r="W2" s="4"/>
+      <c r="X2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261221.0)</f>
-        <v>2261221</v>
-      </c>
+      <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
     </row>
     <row r="3">
@@ -4962,7 +5288,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -5008,25 +5337,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.546)</f>
-        <v>2.546</v>
-      </c>
-      <c r="T3" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8486666666666666)</f>
-        <v>0.8486666667</v>
-      </c>
-      <c r="U3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
+        <v>3.33</v>
+      </c>
+      <c r="U3" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.11)</f>
+        <v>1.11</v>
+      </c>
       <c r="V3" s="4"/>
-      <c r="W3" s="4">
+      <c r="W3" s="4"/>
+      <c r="X3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261862.0)</f>
-        <v>2261862</v>
-      </c>
+      <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
     </row>
     <row r="4">
@@ -5050,7 +5376,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -5096,25 +5425,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.655)</f>
-        <v>2.655</v>
-      </c>
-      <c r="T4" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8849999999999999)</f>
-        <v>0.885</v>
-      </c>
-      <c r="U4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.415)</f>
+        <v>3.415</v>
+      </c>
+      <c r="U4" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1383333333333334)</f>
+        <v>1.138333333</v>
+      </c>
       <c r="V4" s="4"/>
-      <c r="W4" s="4">
+      <c r="W4" s="4"/>
+      <c r="X4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261933.0)</f>
-        <v>2261933</v>
-      </c>
+      <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
     <row r="5">
@@ -5138,7 +5464,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -5184,25 +5513,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8880000000000001)</f>
-        <v>1.888</v>
-      </c>
-      <c r="T5" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6293333333333334)</f>
-        <v>0.6293333333</v>
-      </c>
-      <c r="U5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.64)</f>
+        <v>2.64</v>
+      </c>
+      <c r="U5" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.88)</f>
+        <v>0.88</v>
+      </c>
       <c r="V5" s="4"/>
-      <c r="W5" s="4">
+      <c r="W5" s="4"/>
+      <c r="X5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262154.0)</f>
-        <v>2262154</v>
-      </c>
+      <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
     <row r="6">
@@ -5226,7 +5552,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
@@ -5272,25 +5601,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1580000000000001)</f>
-        <v>1.158</v>
-      </c>
-      <c r="T6" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.38600000000000007)</f>
-        <v>0.386</v>
-      </c>
-      <c r="U6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8300000000000003)</f>
+        <v>1.83</v>
+      </c>
+      <c r="U6" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6100000000000001)</f>
+        <v>0.61</v>
+      </c>
       <c r="V6" s="4"/>
-      <c r="W6" s="4">
+      <c r="W6" s="4"/>
+      <c r="X6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261830.0)</f>
-        <v>2261830</v>
-      </c>
+      <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
     <row r="7">
@@ -5314,7 +5640,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -5360,25 +5689,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.902)</f>
-        <v>2.902</v>
-      </c>
-      <c r="T7" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9673333333333334)</f>
-        <v>0.9673333333</v>
-      </c>
-      <c r="U7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6700000000000004)</f>
+        <v>3.67</v>
+      </c>
+      <c r="U7" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2233333333333334)</f>
+        <v>1.223333333</v>
+      </c>
       <c r="V7" s="4"/>
-      <c r="W7" s="4">
+      <c r="W7" s="4"/>
+      <c r="X7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261224.0)</f>
-        <v>2261224</v>
-      </c>
+      <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
     </row>
     <row r="8">
@@ -5402,7 +5728,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -5448,25 +5777,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.662)</f>
-        <v>2.662</v>
-      </c>
-      <c r="T8" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8873333333333333)</f>
-        <v>0.8873333333</v>
-      </c>
-      <c r="U8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.43)</f>
+        <v>3.43</v>
+      </c>
+      <c r="U8" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1433333333333333)</f>
+        <v>1.143333333</v>
+      </c>
       <c r="V8" s="4"/>
-      <c r="W8" s="4">
+      <c r="W8" s="4"/>
+      <c r="X8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262001.0)</f>
-        <v>2262001</v>
-      </c>
+      <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
     </row>
     <row r="9">
@@ -5490,7 +5816,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
         <v>1.9</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G9" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -5536,25 +5865,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.05)</f>
-        <v>2.05</v>
-      </c>
-      <c r="T9" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6833333333333332)</f>
-        <v>0.6833333333</v>
-      </c>
-      <c r="U9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.81)</f>
+        <v>2.81</v>
+      </c>
+      <c r="U9" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9366666666666666)</f>
+        <v>0.9366666667</v>
+      </c>
       <c r="V9" s="4"/>
-      <c r="W9" s="4">
+      <c r="W9" s="4"/>
+      <c r="X9" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261874.0)</f>
-        <v>2261874</v>
-      </c>
+      <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
     </row>
     <row r="10">
@@ -5578,7 +5904,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -5624,25 +5953,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.043)</f>
-        <v>3.043</v>
-      </c>
-      <c r="T10" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0143333333333333)</f>
-        <v>1.014333333</v>
-      </c>
-      <c r="U10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8350000000000004)</f>
+        <v>3.835</v>
+      </c>
+      <c r="U10" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2783333333333335)</f>
+        <v>1.278333333</v>
+      </c>
       <c r="V10" s="4"/>
-      <c r="W10" s="4">
+      <c r="W10" s="4"/>
+      <c r="X10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261914.0)</f>
-        <v>2261914</v>
-      </c>
+      <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
     </row>
     <row r="11">
@@ -5666,7 +5992,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -5712,25 +6041,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.294)</f>
-        <v>2.294</v>
-      </c>
-      <c r="T11" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7646666666666667)</f>
-        <v>0.7646666667</v>
-      </c>
-      <c r="U11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0700000000000003)</f>
+        <v>3.07</v>
+      </c>
+      <c r="U11" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0233333333333334)</f>
+        <v>1.023333333</v>
+      </c>
       <c r="V11" s="4"/>
-      <c r="W11" s="4">
+      <c r="W11" s="4"/>
+      <c r="X11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262150.0)</f>
-        <v>2262150</v>
-      </c>
+      <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
     </row>
     <row r="12">
@@ -5754,7 +6080,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
         <v>1.7</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G12" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -5800,25 +6129,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5740000000000003)</f>
-        <v>2.574</v>
-      </c>
-      <c r="T12" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8580000000000001)</f>
-        <v>0.858</v>
-      </c>
-      <c r="U12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.35)</f>
+        <v>3.35</v>
+      </c>
+      <c r="U12" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1166666666666667)</f>
+        <v>1.116666667</v>
+      </c>
       <c r="V12" s="4"/>
-      <c r="W12" s="4">
+      <c r="W12" s="4"/>
+      <c r="X12" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2260424.0)</f>
-        <v>2260424</v>
-      </c>
+      <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
     </row>
     <row r="13">
@@ -5842,7 +6168,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="F13" s="4"/>
+      <c r="F13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -5888,25 +6217,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9030000000000005)</f>
-        <v>2.903</v>
-      </c>
-      <c r="T13" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9676666666666668)</f>
-        <v>0.9676666667</v>
-      </c>
-      <c r="U13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.695)</f>
+        <v>3.695</v>
+      </c>
+      <c r="U13" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2316666666666667)</f>
+        <v>1.231666667</v>
+      </c>
       <c r="V13" s="4"/>
-      <c r="W13" s="4">
+      <c r="W13" s="4"/>
+      <c r="X13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262136.0)</f>
-        <v>2262136</v>
-      </c>
+      <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
     </row>
     <row r="14">
@@ -5930,7 +6256,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G14" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
@@ -5976,25 +6305,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8290000000000002)</f>
-        <v>1.829</v>
-      </c>
-      <c r="T14" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6096666666666667)</f>
-        <v>0.6096666667</v>
-      </c>
-      <c r="U14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4850000000000003)</f>
+        <v>2.485</v>
+      </c>
+      <c r="U14" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8283333333333335)</f>
+        <v>0.8283333333</v>
+      </c>
       <c r="V14" s="4"/>
-      <c r="W14" s="4">
+      <c r="W14" s="4"/>
+      <c r="X14" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261756.0)</f>
-        <v>2261756</v>
-      </c>
+      <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
     <row r="15">
@@ -6043,22 +6369,19 @@
       </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
-      <c r="S15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="U15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U15" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
-      <c r="Y15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261849.0)</f>
-        <v>2261849</v>
-      </c>
+      <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
     <row r="16">
@@ -6082,7 +6405,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
@@ -6128,25 +6454,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0860000000000003)</f>
-        <v>2.086</v>
-      </c>
-      <c r="T16" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6953333333333335)</f>
-        <v>0.6953333333</v>
-      </c>
-      <c r="U16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.83)</f>
+        <v>2.83</v>
+      </c>
+      <c r="U16" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9433333333333334)</f>
+        <v>0.9433333333</v>
+      </c>
       <c r="V16" s="4"/>
-      <c r="W16" s="4">
+      <c r="W16" s="4"/>
+      <c r="X16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262090.0)</f>
-        <v>2262090</v>
-      </c>
+      <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
     </row>
     <row r="17">
@@ -6170,7 +6493,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G17" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -6216,25 +6542,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2150000000000003)</f>
-        <v>2.215</v>
-      </c>
-      <c r="T17" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7383333333333334)</f>
-        <v>0.7383333333</v>
-      </c>
-      <c r="U17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9749999999999996)</f>
+        <v>2.975</v>
+      </c>
+      <c r="U17" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9916666666666666)</f>
+        <v>0.9916666667</v>
+      </c>
       <c r="V17" s="4"/>
-      <c r="W17" s="4">
+      <c r="W17" s="4"/>
+      <c r="X17" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262094.0)</f>
-        <v>2262094</v>
-      </c>
+      <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
     </row>
     <row r="18">
@@ -6258,7 +6581,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F18" s="4"/>
+      <c r="F18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G18" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
@@ -6304,25 +6630,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2239999999999998)</f>
-        <v>1.224</v>
-      </c>
-      <c r="T18" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4079999999999999)</f>
-        <v>0.408</v>
-      </c>
-      <c r="U18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
+      <c r="U18" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6)</f>
+        <v>0.6</v>
+      </c>
       <c r="V18" s="4"/>
-      <c r="W18" s="4">
+      <c r="W18" s="4"/>
+      <c r="X18" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261863.0)</f>
-        <v>2261863</v>
-      </c>
+      <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
     </row>
     <row r="19">
@@ -6346,7 +6669,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="F19" s="4"/>
+      <c r="F19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G19" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -6392,25 +6718,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.346)</f>
-        <v>2.346</v>
-      </c>
-      <c r="T19" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.782)</f>
-        <v>0.782</v>
-      </c>
-      <c r="U19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.13)</f>
+        <v>3.13</v>
+      </c>
+      <c r="U19" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0433333333333332)</f>
+        <v>1.043333333</v>
+      </c>
       <c r="V19" s="4"/>
-      <c r="W19" s="4">
+      <c r="W19" s="4"/>
+      <c r="X19" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262075.0)</f>
-        <v>2262075</v>
-      </c>
+      <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
     </row>
     <row r="20">
@@ -6434,7 +6757,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="F20" s="4"/>
+      <c r="F20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G20" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -6480,25 +6806,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2329999999999997)</f>
-        <v>3.233</v>
-      </c>
-      <c r="T20" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0776666666666666)</f>
-        <v>1.077666667</v>
-      </c>
-      <c r="U20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.025)</f>
+        <v>4.025</v>
+      </c>
+      <c r="U20" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3416666666666668)</f>
+        <v>1.341666667</v>
+      </c>
       <c r="V20" s="4"/>
-      <c r="W20" s="4">
+      <c r="W20" s="4"/>
+      <c r="X20" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2260425.0)</f>
-        <v>2260425</v>
-      </c>
+      <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
     </row>
     <row r="21">
@@ -6522,7 +6845,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F21" s="4"/>
+      <c r="F21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G21" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -6568,25 +6894,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.461)</f>
-        <v>2.461</v>
-      </c>
-      <c r="T21" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8203333333333332)</f>
-        <v>0.8203333333</v>
-      </c>
-      <c r="U21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.245)</f>
+        <v>3.245</v>
+      </c>
+      <c r="U21" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0816666666666668)</f>
+        <v>1.081666667</v>
+      </c>
       <c r="V21" s="4"/>
-      <c r="W21" s="4">
+      <c r="W21" s="4"/>
+      <c r="X21" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261219.0)</f>
-        <v>2261219</v>
-      </c>
+      <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
     </row>
     <row r="22">
@@ -6610,7 +6933,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F22" s="4"/>
+      <c r="F22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G22" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -6656,25 +6982,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.77)</f>
-        <v>2.77</v>
-      </c>
-      <c r="T22" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9233333333333333)</f>
-        <v>0.9233333333</v>
-      </c>
-      <c r="U22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5700000000000003)</f>
+        <v>3.57</v>
+      </c>
+      <c r="U22" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1900000000000002)</f>
+        <v>1.19</v>
+      </c>
       <c r="V22" s="4"/>
-      <c r="W22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261864.0)</f>
-        <v>2261864</v>
-      </c>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
     </row>
     <row r="23">
@@ -6698,7 +7021,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="F23" s="4"/>
+      <c r="F23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G23" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -6744,25 +7070,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8680000000000003)</f>
-        <v>2.868</v>
-      </c>
-      <c r="T23" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9560000000000001)</f>
-        <v>0.956</v>
-      </c>
-      <c r="U23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6599999999999997)</f>
+        <v>3.66</v>
+      </c>
+      <c r="U23" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.22)</f>
+        <v>1.22</v>
+      </c>
       <c r="V23" s="4"/>
-      <c r="W23" s="4">
+      <c r="W23" s="4"/>
+      <c r="X23" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261216.0)</f>
-        <v>2261216</v>
-      </c>
+      <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
     </row>
     <row r="24">
@@ -6786,7 +7109,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F24" s="4"/>
+      <c r="F24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G24" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
@@ -6832,25 +7158,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8100000000000003)</f>
-        <v>1.81</v>
-      </c>
-      <c r="T24" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6033333333333334)</f>
-        <v>0.6033333333</v>
-      </c>
-      <c r="U24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.41)</f>
+        <v>2.41</v>
+      </c>
+      <c r="U24" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8033333333333333)</f>
+        <v>0.8033333333</v>
+      </c>
       <c r="V24" s="4"/>
-      <c r="W24" s="4">
+      <c r="W24" s="4"/>
+      <c r="X24" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="X24" s="4"/>
-      <c r="Y24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261215.0)</f>
-        <v>2261215</v>
-      </c>
+      <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
     <row r="25">
@@ -6874,7 +7197,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
         <v>2.7</v>
       </c>
-      <c r="F25" s="4"/>
+      <c r="F25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -6920,25 +7246,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8240000000000003)</f>
-        <v>2.824</v>
-      </c>
-      <c r="T25" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9413333333333335)</f>
-        <v>0.9413333333</v>
-      </c>
-      <c r="U25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6000000000000005)</f>
+        <v>3.6</v>
+      </c>
+      <c r="U25" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2000000000000002)</f>
+        <v>1.2</v>
+      </c>
       <c r="V25" s="4"/>
-      <c r="W25" s="4">
+      <c r="W25" s="4"/>
+      <c r="X25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261195.0)</f>
-        <v>2261195</v>
-      </c>
+      <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
     <row r="26">
@@ -6962,7 +7285,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="F26" s="4"/>
+      <c r="F26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G26" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -7008,25 +7334,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.385)</f>
-        <v>2.385</v>
-      </c>
-      <c r="T26" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7949999999999999)</f>
-        <v>0.795</v>
-      </c>
-      <c r="U26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.145)</f>
+        <v>3.145</v>
+      </c>
+      <c r="U26" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0483333333333333)</f>
+        <v>1.048333333</v>
+      </c>
       <c r="V26" s="4"/>
-      <c r="W26" s="4">
+      <c r="W26" s="4"/>
+      <c r="X26" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261681.0)</f>
-        <v>2261681</v>
-      </c>
+      <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
     </row>
     <row r="27">
@@ -7050,7 +7373,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F27" s="4"/>
+      <c r="F27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
@@ -7096,25 +7422,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1450000000000005)</f>
-        <v>2.145</v>
-      </c>
-      <c r="T27" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7150000000000002)</f>
-        <v>0.715</v>
-      </c>
-      <c r="U27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.865)</f>
+        <v>2.865</v>
+      </c>
+      <c r="U27" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9550000000000001)</f>
+        <v>0.955</v>
+      </c>
       <c r="V27" s="4"/>
-      <c r="W27" s="4">
+      <c r="W27" s="4"/>
+      <c r="X27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="X27" s="4"/>
-      <c r="Y27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261757.0)</f>
-        <v>2261757</v>
-      </c>
+      <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
     </row>
     <row r="28">
@@ -7138,7 +7461,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -7184,25 +7510,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.876)</f>
-        <v>2.876</v>
-      </c>
-      <c r="T28" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9586666666666667)</f>
-        <v>0.9586666667</v>
-      </c>
-      <c r="U28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.66)</f>
+        <v>3.66</v>
+      </c>
+      <c r="U28" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.22)</f>
+        <v>1.22</v>
+      </c>
       <c r="V28" s="4"/>
-      <c r="W28" s="4">
+      <c r="W28" s="4"/>
+      <c r="X28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261218.0)</f>
-        <v>2261218</v>
-      </c>
+      <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
     </row>
     <row r="29">
@@ -7226,7 +7549,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G29" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
@@ -7272,25 +7598,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.729)</f>
-        <v>1.729</v>
-      </c>
-      <c r="T29" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5763333333333334)</f>
-        <v>0.5763333333</v>
-      </c>
-      <c r="U29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.425)</f>
+        <v>2.425</v>
+      </c>
+      <c r="U29" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8083333333333332)</f>
+        <v>0.8083333333</v>
+      </c>
       <c r="V29" s="4"/>
-      <c r="W29" s="4">
+      <c r="W29" s="4"/>
+      <c r="X29" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261915.0)</f>
-        <v>2261915</v>
-      </c>
+      <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
     </row>
     <row r="30">
@@ -7314,7 +7637,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F30" s="4"/>
+      <c r="F30" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G30" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -7345,25 +7671,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1430000000000002)</f>
-        <v>2.143</v>
-      </c>
-      <c r="T30" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7143333333333334)</f>
-        <v>0.7143333333</v>
-      </c>
-      <c r="U30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.935)</f>
+        <v>2.935</v>
+      </c>
+      <c r="U30" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9783333333333334)</f>
+        <v>0.9783333333</v>
+      </c>
       <c r="V30" s="4"/>
-      <c r="W30" s="4">
+      <c r="W30" s="4"/>
+      <c r="X30" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2202217.0)</f>
-        <v>2202217</v>
-      </c>
+      <c r="Y30" s="4"/>
       <c r="Z30" s="4"/>
     </row>
     <row r="31">
@@ -7387,7 +7710,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F31" s="4"/>
+      <c r="F31" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G31" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -7433,25 +7759,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S31" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.393)</f>
-        <v>2.393</v>
-      </c>
-      <c r="T31" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7976666666666666)</f>
-        <v>0.7976666667</v>
-      </c>
-      <c r="U31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.185)</f>
+        <v>3.185</v>
+      </c>
+      <c r="U31" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0616666666666668)</f>
+        <v>1.061666667</v>
+      </c>
       <c r="V31" s="4"/>
-      <c r="W31" s="4">
+      <c r="W31" s="4"/>
+      <c r="X31" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261881.0)</f>
-        <v>2261881</v>
-      </c>
+      <c r="Y31" s="4"/>
       <c r="Z31" s="4"/>
     </row>
     <row r="32">
@@ -7475,7 +7798,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="4"/>
+      <c r="F32" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G32" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
         <v>1.2</v>
@@ -7521,25 +7847,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="S32" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.254)</f>
-        <v>1.254</v>
-      </c>
-      <c r="T32" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.418)</f>
-        <v>0.418</v>
-      </c>
-      <c r="U32" s="4"/>
+      <c r="S32" s="4"/>
+      <c r="T32" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.75)</f>
+        <v>1.75</v>
+      </c>
+      <c r="U32" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5833333333333334)</f>
+        <v>0.5833333333</v>
+      </c>
       <c r="V32" s="4"/>
-      <c r="W32" s="4">
+      <c r="W32" s="4"/>
+      <c r="X32" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
         <v>1.2</v>
       </c>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262036.0)</f>
-        <v>2262036</v>
-      </c>
+      <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
     </row>
     <row r="33">
@@ -7563,7 +7886,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F33" s="4"/>
+      <c r="F33" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G33" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -7609,25 +7935,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S33" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.349)</f>
-        <v>2.349</v>
-      </c>
-      <c r="T33" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.783)</f>
-        <v>0.783</v>
-      </c>
-      <c r="U33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.125)</f>
+        <v>3.125</v>
+      </c>
+      <c r="U33" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0416666666666667)</f>
+        <v>1.041666667</v>
+      </c>
       <c r="V33" s="4"/>
-      <c r="W33" s="4">
+      <c r="W33" s="4"/>
+      <c r="X33" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262165.0)</f>
-        <v>2262165</v>
-      </c>
+      <c r="Y33" s="4"/>
       <c r="Z33" s="4"/>
     </row>
     <row r="34">
@@ -7651,7 +7974,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="F34" s="4"/>
+      <c r="F34" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G34" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -7697,25 +8023,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S34" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9530000000000003)</f>
-        <v>2.953</v>
-      </c>
-      <c r="T34" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9843333333333334)</f>
-        <v>0.9843333333</v>
-      </c>
-      <c r="U34" s="4"/>
+      <c r="S34" s="4"/>
+      <c r="T34" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.745)</f>
+        <v>3.745</v>
+      </c>
+      <c r="U34" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2483333333333333)</f>
+        <v>1.248333333</v>
+      </c>
       <c r="V34" s="4"/>
-      <c r="W34" s="4">
+      <c r="W34" s="4"/>
+      <c r="X34" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262141.0)</f>
-        <v>2262141</v>
-      </c>
+      <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
     </row>
     <row r="35">
@@ -7739,7 +8062,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F35" s="4"/>
+      <c r="F35" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G35" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -7785,25 +8111,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S35" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.26)</f>
-        <v>2.26</v>
-      </c>
-      <c r="T35" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7533333333333333)</f>
-        <v>0.7533333333</v>
-      </c>
-      <c r="U35" s="4"/>
+      <c r="S35" s="4"/>
+      <c r="T35" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.02)</f>
+        <v>3.02</v>
+      </c>
+      <c r="U35" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0066666666666666)</f>
+        <v>1.006666667</v>
+      </c>
       <c r="V35" s="4"/>
-      <c r="W35" s="4">
+      <c r="W35" s="4"/>
+      <c r="X35" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262202.0)</f>
-        <v>2262202</v>
-      </c>
+      <c r="Y35" s="4"/>
       <c r="Z35" s="4"/>
     </row>
     <row r="36">
@@ -7827,7 +8150,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F36" s="4"/>
+      <c r="F36" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G36" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -7873,25 +8199,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S36" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.523)</f>
-        <v>2.523</v>
-      </c>
-      <c r="T36" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8410000000000001)</f>
-        <v>0.841</v>
-      </c>
-      <c r="U36" s="4"/>
+      <c r="S36" s="4"/>
+      <c r="T36" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.315)</f>
+        <v>3.315</v>
+      </c>
+      <c r="U36" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.105)</f>
+        <v>1.105</v>
+      </c>
       <c r="V36" s="4"/>
-      <c r="W36" s="4">
+      <c r="W36" s="4"/>
+      <c r="X36" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262161.0)</f>
-        <v>2262161</v>
-      </c>
+      <c r="Y36" s="4"/>
       <c r="Z36" s="4"/>
     </row>
     <row r="37">
@@ -7915,7 +8238,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="F37" s="4"/>
+      <c r="F37" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G37" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -7961,25 +8287,22 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S37" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7160000000000002)</f>
-        <v>1.716</v>
-      </c>
-      <c r="T37" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5720000000000001)</f>
-        <v>0.572</v>
-      </c>
-      <c r="U37" s="4"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.42)</f>
+        <v>2.42</v>
+      </c>
+      <c r="U37" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8066666666666666)</f>
+        <v>0.8066666667</v>
+      </c>
       <c r="V37" s="4"/>
-      <c r="W37" s="4">
+      <c r="W37" s="4"/>
+      <c r="X37" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261809.0)</f>
-        <v>2261809</v>
-      </c>
+      <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
     </row>
     <row r="38">
@@ -8003,7 +8326,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
-      <c r="F38" s="4"/>
+      <c r="F38" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G38" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -8049,28 +8375,41 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S38" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8390000000000004)</f>
-        <v>2.839</v>
-      </c>
-      <c r="T38" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9463333333333335)</f>
-        <v>0.9463333333</v>
-      </c>
-      <c r="U38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.615)</f>
+        <v>3.615</v>
+      </c>
+      <c r="U38" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.205)</f>
+        <v>1.205</v>
+      </c>
       <c r="V38" s="4"/>
-      <c r="W38" s="4">
+      <c r="W38" s="4"/>
+      <c r="X38" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262214.0)</f>
-        <v>2262214</v>
-      </c>
+      <c r="Y38" s="4"/>
       <c r="Z38" s="4"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="T2:T38">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T38">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>2.8</formula>
+      <formula>2.999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T38">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>2.8</formula>
+    </cfRule>
+  </conditionalFormatting>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -8128,11 +8467,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="8" t="str">
+      <c r="H1" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(10%)")</f>
         <v>TUTORIAS(10%)</v>
       </c>
-      <c r="I1" s="8" t="str">
+      <c r="I1" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu")</f>
         <v>PQT+Tu</v>
       </c>
@@ -8153,25 +8492,19 @@
         <v>Tr2</v>
       </c>
       <c r="N1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta2")</f>
-        <v>Ta2</v>
-      </c>
-      <c r="O1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr2")</f>
-        <v>Tr2</v>
-      </c>
-      <c r="P1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta3")</f>
-        <v>Ta3</v>
-      </c>
-      <c r="Q1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr3")</f>
         <v>Tr3</v>
       </c>
-      <c r="R1" s="1" t="str">
+      <c r="O1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Q2")</f>
+        <v>Q2</v>
+      </c>
+      <c r="P1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr4")</f>
         <v>Tr4</v>
       </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
       <c r="S1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
         <v>FINAL</v>
@@ -8213,11 +8546,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4">
@@ -8240,24 +8576,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N2" s="4"/>
+      <c r="N2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.435)</f>
-        <v>2.435</v>
-      </c>
-      <c r="T2" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8116666666666666)</f>
-        <v>0.8116666667</v>
+      <c r="S2" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.705)</f>
+        <v>3.705</v>
+      </c>
+      <c r="T2" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.235)</f>
+        <v>1.235</v>
       </c>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="4">
@@ -8283,11 +8622,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4">
@@ -8310,24 +8652,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N3" s="4"/>
+      <c r="N3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-      <c r="S3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.82)</f>
-        <v>1.82</v>
-      </c>
-      <c r="T3" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6066666666666667)</f>
-        <v>0.6066666667</v>
+      <c r="S3" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.11)</f>
+        <v>3.11</v>
+      </c>
+      <c r="T3" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0366666666666666)</f>
+        <v>1.036666667</v>
       </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
       <c r="W3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X3" s="4"/>
       <c r="Y3" s="4">
@@ -8353,16 +8698,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="J4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -8372,29 +8720,35 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="L4" s="4"/>
+      <c r="L4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="M4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N4" s="4"/>
+      <c r="N4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="T4" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5666666666666667)</f>
-        <v>0.5666666667</v>
+      <c r="S4" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.97)</f>
+        <v>2.97</v>
+      </c>
+      <c r="T4" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9900000000000001)</f>
+        <v>0.99</v>
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="4">
@@ -8420,11 +8774,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4">
@@ -8447,24 +8804,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N5" s="4"/>
+      <c r="N5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.105)</f>
-        <v>2.105</v>
-      </c>
-      <c r="T5" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7016666666666667)</f>
-        <v>0.7016666667</v>
+      <c r="S5" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3150000000000004)</f>
+        <v>3.315</v>
+      </c>
+      <c r="T5" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1050000000000002)</f>
+        <v>1.105</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X5" s="4"/>
       <c r="Y5" s="4">
@@ -8490,11 +8850,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4">
@@ -8517,24 +8880,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N6" s="4"/>
+      <c r="N6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.18)</f>
-        <v>2.18</v>
-      </c>
-      <c r="T6" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7266666666666667)</f>
-        <v>0.7266666667</v>
+      <c r="S6" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.63)</f>
+        <v>3.63</v>
+      </c>
+      <c r="T6" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.21)</f>
+        <v>1.21</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X6" s="4"/>
       <c r="Y6" s="4">
@@ -8560,7 +8926,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -8592,13 +8961,13 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
-      <c r="S7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9549999999999998)</f>
-        <v>1.955</v>
-      </c>
-      <c r="T7" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6516666666666666)</f>
-        <v>0.6516666667</v>
+      <c r="S7" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.385)</f>
+        <v>2.385</v>
+      </c>
+      <c r="T7" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7949999999999999)</f>
+        <v>0.795</v>
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
@@ -8630,7 +8999,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8657,18 +9029,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N8" s="4"/>
+      <c r="N8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.425)</f>
-        <v>2.425</v>
-      </c>
-      <c r="T8" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8083333333333332)</f>
-        <v>0.8083333333</v>
+      <c r="S8" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.725)</f>
+        <v>3.725</v>
+      </c>
+      <c r="T8" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2416666666666667)</f>
+        <v>1.241666667</v>
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
@@ -8700,7 +9075,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -8714,11 +9092,11 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="T9" s="9">
+      <c r="S9" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="10">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -8749,16 +9127,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="J10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -8776,24 +9157,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N10" s="4"/>
+      <c r="N10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
-      <c r="S10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.885)</f>
-        <v>1.885</v>
-      </c>
-      <c r="T10" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6283333333333333)</f>
-        <v>0.6283333333</v>
+      <c r="S10" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.335)</f>
+        <v>3.335</v>
+      </c>
+      <c r="T10" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1116666666666666)</f>
+        <v>1.111666667</v>
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="X10" s="4"/>
       <c r="Y10" s="4">
@@ -8819,7 +9203,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
         <v>3.6</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8846,18 +9233,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N11" s="4"/>
+      <c r="N11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
-      <c r="S11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="T11" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6666666666666666)</f>
-        <v>0.6666666667</v>
+      <c r="S11" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.44)</f>
+        <v>3.44</v>
+      </c>
+      <c r="T11" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1466666666666667)</f>
+        <v>1.146666667</v>
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
@@ -8889,11 +9279,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4">
@@ -8916,24 +9309,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N12" s="4"/>
+      <c r="N12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
-      <c r="S12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9799999999999998)</f>
-        <v>1.98</v>
-      </c>
-      <c r="T12" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6599999999999999)</f>
-        <v>0.66</v>
+      <c r="S12" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2700000000000005)</f>
+        <v>3.27</v>
+      </c>
+      <c r="T12" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.09)</f>
+        <v>1.09</v>
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X12" s="4"/>
       <c r="Y12" s="4">
@@ -8959,11 +9355,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4">
@@ -8986,24 +9385,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N13" s="4"/>
+      <c r="N13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
-      <c r="S13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.055)</f>
-        <v>2.055</v>
-      </c>
-      <c r="T13" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.685)</f>
-        <v>0.685</v>
+      <c r="S13" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.325)</f>
+        <v>3.325</v>
+      </c>
+      <c r="T13" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1083333333333334)</f>
+        <v>1.108333333</v>
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
       <c r="W13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X13" s="4"/>
       <c r="Y13" s="4">
@@ -9029,16 +9431,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J14" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -9056,24 +9461,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N14" s="4"/>
+      <c r="N14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-      <c r="S14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.335)</f>
-        <v>2.335</v>
-      </c>
-      <c r="T14" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7783333333333333)</f>
-        <v>0.7783333333</v>
+      <c r="S14" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.815)</f>
+        <v>3.815</v>
+      </c>
+      <c r="T14" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2716666666666667)</f>
+        <v>1.271666667</v>
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X14" s="4"/>
       <c r="Y14" s="4">
@@ -9099,16 +9507,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="J15" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -9118,29 +9529,35 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="L15" s="4"/>
+      <c r="L15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="M15" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N15" s="4"/>
+      <c r="N15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
-      <c r="S15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0749999999999997)</f>
-        <v>2.075</v>
-      </c>
-      <c r="T15" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6916666666666665)</f>
-        <v>0.6916666667</v>
+      <c r="S15" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2350000000000003)</f>
+        <v>3.235</v>
+      </c>
+      <c r="T15" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0783333333333334)</f>
+        <v>1.078333333</v>
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="X15" s="4"/>
       <c r="Y15" s="4">
@@ -9166,11 +9583,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4">
@@ -9193,24 +9613,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N16" s="4"/>
+      <c r="N16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.325)</f>
-        <v>2.325</v>
-      </c>
-      <c r="T16" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.775)</f>
-        <v>0.775</v>
+      <c r="S16" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6149999999999998)</f>
+        <v>3.615</v>
+      </c>
+      <c r="T16" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2049999999999998)</f>
+        <v>1.205</v>
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X16" s="4"/>
       <c r="Y16" s="4">
@@ -9236,11 +9659,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4">
@@ -9263,24 +9689,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N17" s="4"/>
+      <c r="N17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
-      <c r="S17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9999999999999998)</f>
-        <v>2</v>
-      </c>
-      <c r="T17" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6666666666666666)</f>
-        <v>0.6666666667</v>
+      <c r="S17" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9699999999999998)</f>
+        <v>2.97</v>
+      </c>
+      <c r="T17" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9899999999999999)</f>
+        <v>0.99</v>
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X17" s="4"/>
       <c r="Y17" s="4">
@@ -9306,16 +9735,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="J18" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -9333,24 +9765,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N18" s="4"/>
+      <c r="N18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
-      <c r="S18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.885)</f>
-        <v>1.885</v>
-      </c>
-      <c r="T18" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6283333333333333)</f>
-        <v>0.6283333333</v>
+      <c r="S18" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.975)</f>
+        <v>2.975</v>
+      </c>
+      <c r="T18" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9916666666666667)</f>
+        <v>0.9916666667</v>
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="X18" s="4"/>
       <c r="Y18" s="4">
@@ -9376,11 +9811,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4">
@@ -9403,24 +9841,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N19" s="4"/>
+      <c r="N19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
-      <c r="S19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.295)</f>
-        <v>2.295</v>
-      </c>
-      <c r="T19" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.765)</f>
-        <v>0.765</v>
+      <c r="S19" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.665)</f>
+        <v>3.665</v>
+      </c>
+      <c r="T19" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2216666666666667)</f>
+        <v>1.221666667</v>
       </c>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X19" s="4"/>
       <c r="Y19" s="4">
@@ -9446,16 +9887,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E20" s="4"/>
+      <c r="E20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J20" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -9473,24 +9917,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N20" s="4"/>
+      <c r="N20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9899999999999998)</f>
-        <v>1.99</v>
-      </c>
-      <c r="T20" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6633333333333332)</f>
-        <v>0.6633333333</v>
+      <c r="S20" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.29)</f>
+        <v>3.29</v>
+      </c>
+      <c r="T20" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0966666666666667)</f>
+        <v>1.096666667</v>
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X20" s="4"/>
       <c r="Y20" s="4">
@@ -9516,11 +9963,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4">
@@ -9543,24 +9993,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N21" s="4"/>
+      <c r="N21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
-      <c r="S21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.18)</f>
-        <v>2.18</v>
-      </c>
-      <c r="T21" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7266666666666667)</f>
-        <v>0.7266666667</v>
+      <c r="S21" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.63)</f>
+        <v>3.63</v>
+      </c>
+      <c r="T21" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.21)</f>
+        <v>1.21</v>
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
       <c r="W21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X21" s="4"/>
       <c r="Y21" s="4">
@@ -9586,11 +10039,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4">
@@ -9613,24 +10069,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N22" s="4"/>
+      <c r="N22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
-      <c r="S22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.15)</f>
-        <v>2.15</v>
-      </c>
-      <c r="T22" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7166666666666667)</f>
-        <v>0.7166666667</v>
+      <c r="S22" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.62)</f>
+        <v>3.62</v>
+      </c>
+      <c r="T22" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2066666666666668)</f>
+        <v>1.206666667</v>
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
       <c r="W22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X22" s="4"/>
       <c r="Y22" s="4">
@@ -9656,16 +10115,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="J23" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -9683,24 +10145,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="4"/>
+      <c r="N23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
-      <c r="S23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.38)</f>
-        <v>2.38</v>
-      </c>
-      <c r="T23" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7933333333333333)</f>
-        <v>0.7933333333</v>
+      <c r="S23" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="T23" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2666666666666666)</f>
+        <v>1.266666667</v>
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
       <c r="W23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="X23" s="4"/>
       <c r="Y23" s="4">
@@ -9726,16 +10191,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J24" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -9753,24 +10221,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N24" s="4"/>
+      <c r="N24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O24" s="4"/>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
-      <c r="S24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.26)</f>
-        <v>2.26</v>
-      </c>
-      <c r="T24" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7533333333333333)</f>
-        <v>0.7533333333</v>
+      <c r="S24" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.62)</f>
+        <v>3.62</v>
+      </c>
+      <c r="T24" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2066666666666668)</f>
+        <v>1.206666667</v>
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X24" s="4"/>
       <c r="Y24" s="4">
@@ -9796,7 +10267,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
         <v>3.9</v>
       </c>
-      <c r="E25" s="4"/>
+      <c r="E25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -9823,18 +10297,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N25" s="4"/>
+      <c r="N25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
-      <c r="S25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.225)</f>
-        <v>2.225</v>
-      </c>
-      <c r="T25" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7416666666666667)</f>
-        <v>0.7416666667</v>
+      <c r="S25" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.725)</f>
+        <v>3.725</v>
+      </c>
+      <c r="T25" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2416666666666667)</f>
+        <v>1.241666667</v>
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
@@ -9866,16 +10343,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="E26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
       </c>
       <c r="J26" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -9893,24 +10373,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N26" s="4"/>
+      <c r="N26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
-      <c r="S26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8400000000000001)</f>
-        <v>0.84</v>
-      </c>
-      <c r="T26" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.28)</f>
-        <v>0.28</v>
+      <c r="S26" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.03)</f>
+        <v>1.03</v>
+      </c>
+      <c r="T26" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3433333333333333)</f>
+        <v>0.3433333333</v>
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="X26" s="4"/>
       <c r="Y26" s="4">
@@ -9929,18 +10412,21 @@
         <v>TABARES GAVIRIA JUAN ANDRES</v>
       </c>
       <c r="C27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="D27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="E27" s="4"/>
+      <c r="E27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4">
@@ -9963,24 +10449,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N27" s="4"/>
+      <c r="N27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
-      <c r="S27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5199999999999998)</f>
-        <v>1.52</v>
-      </c>
-      <c r="T27" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5066666666666666)</f>
-        <v>0.5066666667</v>
+      <c r="S27" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.585)</f>
+        <v>2.585</v>
+      </c>
+      <c r="T27" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8616666666666667)</f>
+        <v>0.8616666667</v>
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
       <c r="W27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X27" s="4"/>
       <c r="Y27" s="4">
@@ -10006,11 +10495,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="E28" s="4"/>
+      <c r="E28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4">
@@ -10033,24 +10525,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N28" s="4"/>
+      <c r="N28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
-      <c r="S28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.69)</f>
-        <v>1.69</v>
-      </c>
-      <c r="T28" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5633333333333334)</f>
-        <v>0.5633333333</v>
+      <c r="S28" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9400000000000004)</f>
+        <v>2.94</v>
+      </c>
+      <c r="T28" s="10">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9800000000000001)</f>
+        <v>0.98</v>
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
       <c r="W28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X28" s="4"/>
       <c r="Y28" s="4">
@@ -10060,6 +10555,22 @@
       <c r="Z28" s="4"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="S2:S28">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S28">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>2.8</formula>
+      <formula>2.9999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S28">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+      <formula>2.8</formula>
+    </cfRule>
+  </conditionalFormatting>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/app_notas_uis.xlsx
+++ b/app_notas_uis.xlsx
@@ -19,9 +19,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="3">
     <font>
       <sz val="10.0"/>
@@ -55,7 +52,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -70,9 +67,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
@@ -435,26 +429,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Q6")</f>
         <v>Q6</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="3" t="str">
+      <c r="Q1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr2")</f>
+        <v>Tr2</v>
+      </c>
+      <c r="R1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta4")</f>
+        <v>Ta4</v>
+      </c>
+      <c r="S1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr3")</f>
+        <v>Tr3</v>
+      </c>
+      <c r="T1" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
         <v>FINAL</v>
       </c>
-      <c r="S1" s="1" t="str">
+      <c r="U1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"meta3.0")</f>
         <v>meta3.0</v>
       </c>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
-        <v>FINAL</v>
-      </c>
-      <c r="X1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COD")</f>
-        <v>COD</v>
-      </c>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="4">
@@ -477,10 +474,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
         <v>2.1</v>
@@ -521,23 +515,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2150000000000003)</f>
-        <v>2.215</v>
-      </c>
-      <c r="S2" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7383333333333334)</f>
-        <v>0.7383333333</v>
-      </c>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="Q2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.615)</f>
+        <v>1.615</v>
+      </c>
+      <c r="U2" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5383333333333333)</f>
+        <v>0.5383333333</v>
+      </c>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
-      <c r="X2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2243499.0)</f>
-        <v>2243499</v>
-      </c>
+      <c r="X2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="4">
@@ -560,13 +557,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -581,8 +575,8 @@
         <v>4.1</v>
       </c>
       <c r="K3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="L3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -604,23 +598,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1350000000000002)</f>
-        <v>3.135</v>
-      </c>
-      <c r="S3" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0450000000000002)</f>
-        <v>1.045</v>
-      </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="Q3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S3" s="4"/>
+      <c r="T3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.58)</f>
+        <v>2.58</v>
+      </c>
+      <c r="U3" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.86)</f>
+        <v>0.86</v>
+      </c>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
-      <c r="X3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2252349.0)</f>
-        <v>2252349</v>
-      </c>
+      <c r="X3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="4">
@@ -643,10 +640,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -687,23 +681,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.925)</f>
-        <v>2.925</v>
-      </c>
-      <c r="S4" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.975)</f>
-        <v>0.975</v>
-      </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="Q4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="S4" s="4"/>
+      <c r="T4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.325)</f>
+        <v>2.325</v>
+      </c>
+      <c r="U4" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.775)</f>
+        <v>0.775</v>
+      </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
-      <c r="X4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2230490.0)</f>
-        <v>2230490</v>
-      </c>
+      <c r="X4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="4">
@@ -726,10 +723,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -770,23 +764,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.24)</f>
-        <v>3.24</v>
-      </c>
-      <c r="S5" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
-      </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
+      <c r="Q5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S5" s="4"/>
+      <c r="T5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6399999999999997)</f>
+        <v>2.64</v>
+      </c>
+      <c r="U5" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8799999999999999)</f>
+        <v>0.88</v>
+      </c>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
-      <c r="X5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2252243.0)</f>
-        <v>2252243</v>
-      </c>
+      <c r="X5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="4">
@@ -809,10 +806,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F6" s="4"/>
       <c r="G6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -853,23 +847,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.13)</f>
-        <v>3.13</v>
-      </c>
-      <c r="S6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0433333333333332)</f>
-        <v>1.043333333</v>
-      </c>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
+      <c r="Q6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="S6" s="4"/>
+      <c r="T6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5300000000000002)</f>
+        <v>2.53</v>
+      </c>
+      <c r="U6" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8433333333333334)</f>
+        <v>0.8433333333</v>
+      </c>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
-      <c r="X6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201182.0)</f>
-        <v>2201182</v>
-      </c>
+      <c r="X6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="4">
@@ -892,10 +889,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F7" s="4"/>
       <c r="G7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -936,23 +930,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6100000000000003)</f>
-        <v>2.61</v>
-      </c>
-      <c r="S7" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8700000000000001)</f>
-        <v>0.87</v>
-      </c>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
+      <c r="Q7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S7" s="4"/>
+      <c r="T7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0100000000000002)</f>
+        <v>2.01</v>
+      </c>
+      <c r="U7" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.67)</f>
+        <v>0.67</v>
+      </c>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
-      <c r="X7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2253170.0)</f>
-        <v>2253170</v>
-      </c>
+      <c r="X7" s="4"/>
     </row>
     <row r="8">
       <c r="A8" s="4">
@@ -975,10 +972,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="F8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F8" s="4"/>
       <c r="G8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -1019,23 +1013,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.575)</f>
-        <v>2.575</v>
-      </c>
-      <c r="S8" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8583333333333334)</f>
-        <v>0.8583333333</v>
-      </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
+      <c r="Q8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S8" s="4"/>
+      <c r="T8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.975)</f>
+        <v>1.975</v>
+      </c>
+      <c r="U8" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6583333333333333)</f>
+        <v>0.6583333333</v>
+      </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
-      <c r="X8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2251360.0)</f>
-        <v>2251360</v>
-      </c>
+      <c r="X8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="4">
@@ -1058,10 +1055,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F9" s="4"/>
       <c r="G9" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -1102,23 +1096,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2649999999999997)</f>
-        <v>3.265</v>
-      </c>
-      <c r="S9" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0883333333333332)</f>
-        <v>1.088333333</v>
-      </c>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
+      <c r="Q9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S9" s="4"/>
+      <c r="T9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.665)</f>
+        <v>2.665</v>
+      </c>
+      <c r="U9" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8883333333333333)</f>
+        <v>0.8883333333</v>
+      </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
-      <c r="X9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2252431.0)</f>
-        <v>2252431</v>
-      </c>
+      <c r="X9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="4">
@@ -1141,10 +1138,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F10" s="4"/>
       <c r="G10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -1185,23 +1179,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.34)</f>
-        <v>3.34</v>
-      </c>
-      <c r="S10" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1133333333333333)</f>
-        <v>1.113333333</v>
-      </c>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
+      <c r="Q10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S10" s="4"/>
+      <c r="T10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.74)</f>
+        <v>2.74</v>
+      </c>
+      <c r="U10" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9133333333333334)</f>
+        <v>0.9133333333</v>
+      </c>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
-      <c r="X10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2241550.0)</f>
-        <v>2241550</v>
-      </c>
+      <c r="X10" s="4"/>
     </row>
     <row r="11">
       <c r="A11" s="4">
@@ -1224,10 +1221,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F11" s="4"/>
       <c r="G11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -1268,23 +1262,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.08)</f>
-        <v>3.08</v>
-      </c>
-      <c r="S11" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0266666666666666)</f>
-        <v>1.026666667</v>
-      </c>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
+      <c r="Q11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="S11" s="4"/>
+      <c r="T11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.48)</f>
+        <v>2.48</v>
+      </c>
+      <c r="U11" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8266666666666667)</f>
+        <v>0.8266666667</v>
+      </c>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
-      <c r="X11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2253113.0)</f>
-        <v>2253113</v>
-      </c>
+      <c r="X11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="4">
@@ -1307,10 +1304,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F12" s="4"/>
       <c r="G12" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
         <v>3.1</v>
@@ -1351,23 +1345,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.92)</f>
-        <v>2.92</v>
-      </c>
-      <c r="S12" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9733333333333333)</f>
-        <v>0.9733333333</v>
-      </c>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
+      <c r="Q12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="S12" s="4"/>
+      <c r="T12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3200000000000003)</f>
+        <v>2.32</v>
+      </c>
+      <c r="U12" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7733333333333334)</f>
+        <v>0.7733333333</v>
+      </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
-      <c r="X12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2252452.0)</f>
-        <v>2252452</v>
-      </c>
+      <c r="X12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="4">
@@ -1390,10 +1387,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F13" s="4"/>
       <c r="G13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
         <v>2.1</v>
@@ -1434,23 +1428,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4649999999999999)</f>
-        <v>1.465</v>
-      </c>
-      <c r="S13" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4883333333333333)</f>
-        <v>0.4883333333</v>
-      </c>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
+      <c r="Q13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S13" s="4"/>
+      <c r="T13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.865)</f>
+        <v>0.865</v>
+      </c>
+      <c r="U13" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.28833333333333333)</f>
+        <v>0.2883333333</v>
+      </c>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
-      <c r="X13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2251568.0)</f>
-        <v>2251568</v>
-      </c>
+      <c r="X13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="4">
@@ -1473,10 +1470,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
         <v>2.3</v>
       </c>
-      <c r="F14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F14" s="4"/>
       <c r="G14" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -1517,23 +1511,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7750000000000004)</f>
-        <v>3.775</v>
-      </c>
-      <c r="S14" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2583333333333335)</f>
-        <v>1.258333333</v>
-      </c>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
+      <c r="Q14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S14" s="4"/>
+      <c r="T14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.175)</f>
+        <v>3.175</v>
+      </c>
+      <c r="U14" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0583333333333333)</f>
+        <v>1.058333333</v>
+      </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
-      <c r="X14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2242408.0)</f>
-        <v>2242408</v>
-      </c>
+      <c r="X14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="4">
@@ -1556,10 +1553,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F15" s="4"/>
       <c r="G15" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -1601,22 +1595,22 @@
         <v>5</v>
       </c>
       <c r="Q15" s="4"/>
-      <c r="R15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
-      </c>
-      <c r="S15" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0666666666666667)</f>
-        <v>1.066666667</v>
-      </c>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
+      <c r="R15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="4"/>
+      <c r="T15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="U15" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8666666666666667)</f>
+        <v>0.8666666667</v>
+      </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
-      <c r="X15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2250506.0)</f>
-        <v>2250506</v>
-      </c>
+      <c r="X15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="4">
@@ -1639,10 +1633,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="F16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F16" s="4"/>
       <c r="G16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
@@ -1683,23 +1674,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.36)</f>
-        <v>3.36</v>
-      </c>
-      <c r="S16" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1199999999999999)</f>
-        <v>1.12</v>
-      </c>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
+      <c r="Q16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S16" s="4"/>
+      <c r="T16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.76)</f>
+        <v>2.76</v>
+      </c>
+      <c r="U16" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9199999999999999)</f>
+        <v>0.92</v>
+      </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
-      <c r="X16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2242040.0)</f>
-        <v>2242040</v>
-      </c>
+      <c r="X16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="4">
@@ -1722,10 +1716,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F17" s="4"/>
       <c r="G17" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -1766,23 +1757,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8449999999999998)</f>
-        <v>2.845</v>
-      </c>
-      <c r="S17" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9483333333333333)</f>
-        <v>0.9483333333</v>
-      </c>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
+      <c r="Q17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S17" s="4"/>
+      <c r="T17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.245)</f>
+        <v>2.245</v>
+      </c>
+      <c r="U17" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7483333333333334)</f>
+        <v>0.7483333333</v>
+      </c>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
-      <c r="X17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2251822.0)</f>
-        <v>2251822</v>
-      </c>
+      <c r="X17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="4">
@@ -1805,10 +1799,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F18" s="4"/>
       <c r="G18" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -1849,23 +1840,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.465)</f>
-        <v>3.465</v>
-      </c>
-      <c r="S18" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.155)</f>
-        <v>1.155</v>
-      </c>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
+      <c r="Q18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S18" s="4"/>
+      <c r="T18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.865)</f>
+        <v>2.865</v>
+      </c>
+      <c r="U18" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9550000000000001)</f>
+        <v>0.955</v>
+      </c>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
-      <c r="X18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2250810.0)</f>
-        <v>2250810</v>
-      </c>
+      <c r="X18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="4">
@@ -1888,10 +1882,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F19" s="4"/>
       <c r="G19" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -1932,23 +1923,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.03)</f>
-        <v>3.03</v>
-      </c>
-      <c r="S19" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
-        <v>1.01</v>
-      </c>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
+      <c r="Q19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S19" s="4"/>
+      <c r="T19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.43)</f>
+        <v>2.43</v>
+      </c>
+      <c r="U19" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.81)</f>
+        <v>0.81</v>
+      </c>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
-      <c r="X19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2242515.0)</f>
-        <v>2242515</v>
-      </c>
+      <c r="X19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="4">
@@ -1971,10 +1965,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F20" s="4"/>
       <c r="G20" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
@@ -2015,23 +2006,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.825)</f>
-        <v>3.825</v>
-      </c>
-      <c r="S20" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2750000000000001)</f>
-        <v>1.275</v>
-      </c>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
+      <c r="Q20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S20" s="4"/>
+      <c r="T20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.225)</f>
+        <v>3.225</v>
+      </c>
+      <c r="U20" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.075)</f>
+        <v>1.075</v>
+      </c>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
-      <c r="X20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2230105.0)</f>
-        <v>2230105</v>
-      </c>
+      <c r="X20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="4">
@@ -2054,10 +2048,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F21" s="4"/>
       <c r="G21" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -2098,23 +2089,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5649999999999995)</f>
-        <v>3.565</v>
-      </c>
-      <c r="S21" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1883333333333332)</f>
-        <v>1.188333333</v>
-      </c>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
+      <c r="Q21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S21" s="4"/>
+      <c r="T21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.965)</f>
+        <v>2.965</v>
+      </c>
+      <c r="U21" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9883333333333333)</f>
+        <v>0.9883333333</v>
+      </c>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
-      <c r="X21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2242480.0)</f>
-        <v>2242480</v>
-      </c>
+      <c r="X21" s="4"/>
     </row>
     <row r="22">
       <c r="A22" s="4">
@@ -2137,10 +2131,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F22" s="4"/>
       <c r="G22" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -2181,23 +2172,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.965)</f>
-        <v>2.965</v>
-      </c>
-      <c r="S22" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9883333333333333)</f>
-        <v>0.9883333333</v>
-      </c>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
+      <c r="Q22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S22" s="4"/>
+      <c r="T22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3649999999999998)</f>
+        <v>2.365</v>
+      </c>
+      <c r="U22" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7883333333333332)</f>
+        <v>0.7883333333</v>
+      </c>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
-      <c r="X22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2252703.0)</f>
-        <v>2252703</v>
-      </c>
+      <c r="X22" s="4"/>
     </row>
     <row r="23">
       <c r="A23" s="4">
@@ -2220,10 +2214,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F23" s="4"/>
       <c r="G23" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -2264,23 +2255,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.925)</f>
-        <v>2.925</v>
-      </c>
-      <c r="S23" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.975)</f>
-        <v>0.975</v>
-      </c>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
+      <c r="Q23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S23" s="4"/>
+      <c r="T23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3249999999999997)</f>
+        <v>2.325</v>
+      </c>
+      <c r="U23" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7749999999999999)</f>
+        <v>0.775</v>
+      </c>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
-      <c r="X23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2242906.0)</f>
-        <v>2242906</v>
-      </c>
+      <c r="X23" s="4"/>
     </row>
     <row r="24">
       <c r="A24" s="4">
@@ -2303,10 +2297,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F24" s="4"/>
       <c r="G24" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -2347,23 +2338,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9000000000000004)</f>
-        <v>2.9</v>
-      </c>
-      <c r="S24" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9666666666666668)</f>
-        <v>0.9666666667</v>
-      </c>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
+      <c r="Q24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S24" s="4"/>
+      <c r="T24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="U24" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7666666666666666)</f>
+        <v>0.7666666667</v>
+      </c>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
-      <c r="X24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2253727.0)</f>
-        <v>2253727</v>
-      </c>
+      <c r="X24" s="4"/>
     </row>
     <row r="25">
       <c r="A25" s="4">
@@ -2386,10 +2380,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
         <v>1.4</v>
       </c>
-      <c r="F25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F25" s="4"/>
       <c r="G25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -2430,23 +2421,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6550000000000002)</f>
-        <v>3.655</v>
-      </c>
-      <c r="S25" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2183333333333335)</f>
-        <v>1.218333333</v>
-      </c>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
+      <c r="Q25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S25" s="4"/>
+      <c r="T25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.055)</f>
+        <v>3.055</v>
+      </c>
+      <c r="U25" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0183333333333333)</f>
+        <v>1.018333333</v>
+      </c>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
-      <c r="X25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2253228.0)</f>
-        <v>2253228</v>
-      </c>
+      <c r="X25" s="4"/>
     </row>
     <row r="26">
       <c r="A26" s="4">
@@ -2469,10 +2463,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
         <v>1.4</v>
       </c>
-      <c r="F26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F26" s="4"/>
       <c r="G26" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
         <v>3.9</v>
@@ -2513,23 +2504,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2150000000000003)</f>
-        <v>3.215</v>
-      </c>
-      <c r="S26" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0716666666666668)</f>
-        <v>1.071666667</v>
-      </c>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
+      <c r="Q26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S26" s="4"/>
+      <c r="T26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.615)</f>
+        <v>2.615</v>
+      </c>
+      <c r="U26" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8716666666666667)</f>
+        <v>0.8716666667</v>
+      </c>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
-      <c r="X26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2253073.0)</f>
-        <v>2253073</v>
-      </c>
+      <c r="X26" s="4"/>
     </row>
     <row r="27">
       <c r="A27" s="4">
@@ -2552,10 +2546,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="F27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F27" s="4"/>
       <c r="G27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -2596,23 +2587,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.125)</f>
-        <v>3.125</v>
-      </c>
-      <c r="S27" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0416666666666667)</f>
-        <v>1.041666667</v>
-      </c>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
+      <c r="Q27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S27" s="4"/>
+      <c r="T27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5250000000000004)</f>
+        <v>2.525</v>
+      </c>
+      <c r="U27" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8416666666666668)</f>
+        <v>0.8416666667</v>
+      </c>
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
-      <c r="X27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2252470.0)</f>
-        <v>2252470</v>
-      </c>
+      <c r="X27" s="4"/>
     </row>
     <row r="28">
       <c r="A28" s="4">
@@ -2632,16 +2626,13 @@
         <v>2.9</v>
       </c>
       <c r="E28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="F28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
+      <c r="F28" s="4"/>
       <c r="G28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="H28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -2656,8 +2647,8 @@
         <v>5</v>
       </c>
       <c r="K28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="L28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -2668,8 +2659,8 @@
         <v>5</v>
       </c>
       <c r="N28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="O28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -2679,23 +2670,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.415)</f>
-        <v>2.415</v>
-      </c>
-      <c r="S28" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.805)</f>
-        <v>0.805</v>
-      </c>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
+      <c r="Q28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S28" s="4"/>
+      <c r="T28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.045)</f>
+        <v>2.045</v>
+      </c>
+      <c r="U28" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6816666666666666)</f>
+        <v>0.6816666667</v>
+      </c>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
-      <c r="X28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2252265.0)</f>
-        <v>2252265</v>
-      </c>
+      <c r="X28" s="4"/>
     </row>
     <row r="29">
       <c r="A29" s="4">
@@ -2718,10 +2712,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="F29" s="4"/>
       <c r="G29" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -2762,23 +2753,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.34)</f>
-        <v>3.34</v>
-      </c>
-      <c r="S29" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1133333333333333)</f>
-        <v>1.113333333</v>
-      </c>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
+      <c r="Q29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="R29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="S29" s="4"/>
+      <c r="T29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.74)</f>
+        <v>2.74</v>
+      </c>
+      <c r="U29" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9133333333333334)</f>
+        <v>0.9133333333</v>
+      </c>
       <c r="V29" s="4"/>
       <c r="W29" s="4"/>
-      <c r="X29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2242893.0)</f>
-        <v>2242893</v>
-      </c>
+      <c r="X29" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="R2:R29">
@@ -2854,11 +2848,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="9" t="str">
+      <c r="H1" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(10%)")</f>
         <v>TUTORIAS(10%)</v>
       </c>
-      <c r="I1" s="9" t="str">
+      <c r="I1" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu(20%)")</f>
         <v>PQT+Tu(20%)</v>
       </c>
@@ -2939,8 +2933,8 @@
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4">
@@ -2968,22 +2962,25 @@
         <v>5</v>
       </c>
       <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
+      <c r="P2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.375)</f>
-        <v>3.375</v>
-      </c>
-      <c r="T2" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.125)</f>
-        <v>1.125</v>
+      <c r="S2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.395)</f>
+        <v>3.395</v>
+      </c>
+      <c r="T2" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1316666666666666)</f>
+        <v>1.131666667</v>
       </c>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="4">
@@ -3015,13 +3012,13 @@
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="J3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3044,22 +3041,25 @@
         <v>5</v>
       </c>
       <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
+      <c r="P3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-      <c r="S3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.96)</f>
-        <v>3.96</v>
-      </c>
-      <c r="T3" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
-        <v>1.32</v>
+      <c r="S3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
+        <v>3.98</v>
+      </c>
+      <c r="T3" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3266666666666667)</f>
+        <v>1.326666667</v>
       </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
       <c r="W3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="X3" s="4"/>
       <c r="Y3" s="4">
@@ -3091,13 +3091,13 @@
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="J4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3120,22 +3120,25 @@
         <v>5</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
+      <c r="P4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.96)</f>
-        <v>3.96</v>
-      </c>
-      <c r="T4" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
-        <v>1.32</v>
+      <c r="S4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
+        <v>3.98</v>
+      </c>
+      <c r="T4" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3266666666666667)</f>
+        <v>1.326666667</v>
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="4">
@@ -3167,13 +3170,13 @@
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7)</f>
-        <v>0.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="J5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -3196,22 +3199,25 @@
         <v>0</v>
       </c>
       <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
+      <c r="P5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.335)</f>
-        <v>2.335</v>
-      </c>
-      <c r="T5" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7783333333333333)</f>
-        <v>0.7783333333</v>
+      <c r="S5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.455)</f>
+        <v>2.455</v>
+      </c>
+      <c r="T5" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8183333333333334)</f>
+        <v>0.8183333333</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="X5" s="4"/>
       <c r="Y5" s="4">
@@ -3243,13 +3249,13 @@
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
-        <v>0.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
       </c>
       <c r="J6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3272,22 +3278,25 @@
         <v>0</v>
       </c>
       <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
+      <c r="P6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.73)</f>
-        <v>2.73</v>
-      </c>
-      <c r="T6" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.91)</f>
-        <v>0.91</v>
+      <c r="S6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.85)</f>
+        <v>2.85</v>
+      </c>
+      <c r="T6" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9500000000000001)</f>
+        <v>0.95</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="X6" s="4"/>
       <c r="Y6" s="4">
@@ -3348,14 +3357,17 @@
         <v>5</v>
       </c>
       <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
+      <c r="P7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
-      <c r="S7" s="7">
+      <c r="S7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.875)</f>
         <v>3.875</v>
       </c>
-      <c r="T7" s="10">
+      <c r="T7" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2916666666666667)</f>
         <v>1.291666667</v>
       </c>
@@ -3395,13 +3407,13 @@
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
       </c>
       <c r="J8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3424,22 +3436,25 @@
         <v>5</v>
       </c>
       <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
+      <c r="P8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.625)</f>
-        <v>3.625</v>
-      </c>
-      <c r="T8" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2083333333333333)</f>
-        <v>1.208333333</v>
+      <c r="S8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.465)</f>
+        <v>3.465</v>
+      </c>
+      <c r="T8" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.155)</f>
+        <v>1.155</v>
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="X8" s="4"/>
       <c r="Y8" s="4">
@@ -3471,8 +3486,8 @@
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4">
@@ -3500,22 +3515,25 @@
         <v>5</v>
       </c>
       <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
+      <c r="P9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.44)</f>
-        <v>3.44</v>
-      </c>
-      <c r="T9" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1466666666666667)</f>
-        <v>1.146666667</v>
+      <c r="S9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.46)</f>
+        <v>3.46</v>
+      </c>
+      <c r="T9" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1533333333333333)</f>
+        <v>1.153333333</v>
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="4">
@@ -3547,13 +3565,13 @@
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -3576,22 +3594,25 @@
         <v>5</v>
       </c>
       <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
+      <c r="P10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
-      <c r="S10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.88)</f>
-        <v>3.88</v>
-      </c>
-      <c r="T10" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2933333333333332)</f>
-        <v>1.293333333</v>
+      <c r="S10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
+      <c r="T10" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X10" s="4"/>
       <c r="Y10" s="4">
@@ -3618,13 +3639,13 @@
         <v>4</v>
       </c>
       <c r="E11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
-        <v>0.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4">
@@ -3652,22 +3673,25 @@
         <v>5</v>
       </c>
       <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
+      <c r="P11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
-      <c r="S11" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.79)</f>
-        <v>2.79</v>
-      </c>
-      <c r="T11" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.93)</f>
-        <v>0.93</v>
+      <c r="S11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.71)</f>
+        <v>3.71</v>
+      </c>
+      <c r="T11" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2366666666666666)</f>
+        <v>1.236666667</v>
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
       <c r="W11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="X11" s="4"/>
       <c r="Y11" s="4">
@@ -3728,14 +3752,17 @@
         <v>5</v>
       </c>
       <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
+      <c r="P12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
-      <c r="S12" s="7">
+      <c r="S12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.855)</f>
         <v>3.855</v>
       </c>
-      <c r="T12" s="10">
+      <c r="T12" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.285)</f>
         <v>1.285</v>
       </c>
@@ -3804,14 +3831,17 @@
         <v>5</v>
       </c>
       <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
+      <c r="P13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
-      <c r="S13" s="7">
+      <c r="S13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="T13" s="10">
+      <c r="T13" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2666666666666666)</f>
         <v>1.266666667</v>
       </c>
@@ -3880,14 +3910,17 @@
         <v>5</v>
       </c>
       <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
+      <c r="P14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-      <c r="S14" s="7">
+      <c r="S14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.975)</f>
         <v>3.975</v>
       </c>
-      <c r="T14" s="10">
+      <c r="T14" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.325)</f>
         <v>1.325</v>
       </c>
@@ -3927,13 +3960,13 @@
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="J15" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3956,22 +3989,25 @@
         <v>0</v>
       </c>
       <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
+      <c r="P15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
-      <c r="S15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.58)</f>
-        <v>3.58</v>
-      </c>
-      <c r="T15" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1933333333333334)</f>
-        <v>1.193333333</v>
+      <c r="S15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.64)</f>
+        <v>3.64</v>
+      </c>
+      <c r="T15" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2133333333333334)</f>
+        <v>1.213333333</v>
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="X15" s="4"/>
       <c r="Y15" s="4">
@@ -4003,13 +4039,13 @@
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
       </c>
       <c r="J16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4032,22 +4068,25 @@
         <v>5</v>
       </c>
       <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.735)</f>
-        <v>2.735</v>
-      </c>
-      <c r="T16" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9116666666666666)</f>
-        <v>0.9116666667</v>
+      <c r="S16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.815)</f>
+        <v>2.815</v>
+      </c>
+      <c r="T16" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9383333333333334)</f>
+        <v>0.9383333333</v>
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="X16" s="4"/>
       <c r="Y16" s="4">
@@ -4079,13 +4118,13 @@
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J17" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -4108,22 +4147,25 @@
         <v>5</v>
       </c>
       <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
+      <c r="P17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
-      <c r="S17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.13)</f>
-        <v>3.13</v>
-      </c>
-      <c r="T17" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0433333333333332)</f>
-        <v>1.043333333</v>
+      <c r="S17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.15)</f>
+        <v>3.15</v>
+      </c>
+      <c r="T17" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.05)</f>
+        <v>1.05</v>
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X17" s="4"/>
       <c r="Y17" s="4">
@@ -4155,13 +4197,13 @@
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="J18" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4184,22 +4226,25 @@
         <v>5</v>
       </c>
       <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
+      <c r="P18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
-      <c r="S18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.835)</f>
-        <v>3.835</v>
-      </c>
-      <c r="T18" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2783333333333333)</f>
-        <v>1.278333333</v>
+      <c r="S18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.855)</f>
+        <v>3.855</v>
+      </c>
+      <c r="T18" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.285)</f>
+        <v>1.285</v>
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="X18" s="4"/>
       <c r="Y18" s="4">
@@ -4231,13 +4276,13 @@
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J19" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -4260,22 +4305,25 @@
         <v>5</v>
       </c>
       <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
+      <c r="P19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
-      <c r="S19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.67)</f>
-        <v>3.67</v>
-      </c>
-      <c r="T19" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2233333333333334)</f>
-        <v>1.223333333</v>
+      <c r="S19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.69)</f>
+        <v>3.69</v>
+      </c>
+      <c r="T19" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.23)</f>
+        <v>1.23</v>
       </c>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X19" s="4"/>
       <c r="Y19" s="4">
@@ -4307,13 +4355,13 @@
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
       </c>
       <c r="J20" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4336,22 +4384,25 @@
         <v>5</v>
       </c>
       <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
+      <c r="P20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.375)</f>
-        <v>3.375</v>
-      </c>
-      <c r="T20" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.125)</f>
-        <v>1.125</v>
+      <c r="S20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.415)</f>
+        <v>3.415</v>
+      </c>
+      <c r="T20" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1383333333333334)</f>
+        <v>1.138333333</v>
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="X20" s="4"/>
       <c r="Y20" s="4">
@@ -4383,13 +4434,13 @@
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="J21" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4412,22 +4463,25 @@
         <v>5</v>
       </c>
       <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
+      <c r="P21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
-      <c r="S21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8099999999999996)</f>
-        <v>3.81</v>
-      </c>
-      <c r="T21" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2699999999999998)</f>
-        <v>1.27</v>
+      <c r="S21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8299999999999996)</f>
+        <v>3.83</v>
+      </c>
+      <c r="T21" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2766666666666666)</f>
+        <v>1.276666667</v>
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
       <c r="W21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="X21" s="4"/>
       <c r="Y21" s="4">
@@ -4459,13 +4513,13 @@
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
       </c>
       <c r="J22" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4488,22 +4542,25 @@
         <v>5</v>
       </c>
       <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
+      <c r="P22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
-      <c r="S22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.925)</f>
-        <v>2.925</v>
-      </c>
-      <c r="T22" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.975)</f>
-        <v>0.975</v>
+      <c r="S22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.805)</f>
+        <v>2.805</v>
+      </c>
+      <c r="T22" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.935)</f>
+        <v>0.935</v>
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
       <c r="W22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="X22" s="4"/>
       <c r="Y22" s="4">
@@ -4564,14 +4621,17 @@
         <v>5</v>
       </c>
       <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
+      <c r="P23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
-      <c r="S23" s="7">
+      <c r="S23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.71)</f>
         <v>3.71</v>
       </c>
-      <c r="T23" s="10">
+      <c r="T23" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2366666666666666)</f>
         <v>1.236666667</v>
       </c>
@@ -4611,8 +4671,8 @@
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4">
@@ -4640,22 +4700,25 @@
         <v>5</v>
       </c>
       <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
+      <c r="P24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
-      <c r="S24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.94)</f>
-        <v>3.94</v>
-      </c>
-      <c r="T24" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3133333333333332)</f>
-        <v>1.313333333</v>
+      <c r="S24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.96)</f>
+        <v>3.96</v>
+      </c>
+      <c r="T24" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
+        <v>1.32</v>
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="X24" s="4"/>
       <c r="Y24" s="4">
@@ -4716,14 +4779,17 @@
         <v>5</v>
       </c>
       <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
+      <c r="P25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
-      <c r="S25" s="7">
+      <c r="S25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="T25" s="10">
+      <c r="T25" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3333333333333333)</f>
         <v>1.333333333</v>
       </c>
@@ -4763,8 +4829,8 @@
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4">
@@ -4792,22 +4858,25 @@
         <v>5</v>
       </c>
       <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
+      <c r="P26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
-      <c r="S26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.625)</f>
-        <v>2.625</v>
-      </c>
-      <c r="T26" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.875)</f>
-        <v>0.875</v>
+      <c r="S26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6450000000000005)</f>
+        <v>2.645</v>
+      </c>
+      <c r="T26" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8816666666666668)</f>
+        <v>0.8816666667</v>
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X26" s="4"/>
       <c r="Y26" s="4">
@@ -4839,13 +4908,13 @@
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="J27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -4868,22 +4937,25 @@
         <v>0</v>
       </c>
       <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
+      <c r="P27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
-      <c r="S27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4000000000000004)</f>
-        <v>3.4</v>
-      </c>
-      <c r="T27" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1333333333333335)</f>
-        <v>1.133333333</v>
+      <c r="S27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4600000000000004)</f>
+        <v>3.46</v>
+      </c>
+      <c r="T27" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1533333333333335)</f>
+        <v>1.153333333</v>
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
       <c r="W27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="X27" s="4"/>
       <c r="Y27" s="4">
@@ -4915,13 +4987,13 @@
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="J28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4944,22 +5016,25 @@
         <v>5</v>
       </c>
       <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
+      <c r="P28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
-      <c r="S28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.585)</f>
-        <v>3.585</v>
-      </c>
-      <c r="T28" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.195)</f>
-        <v>1.195</v>
+      <c r="S28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.605)</f>
+        <v>3.605</v>
+      </c>
+      <c r="T28" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2016666666666667)</f>
+        <v>1.201666667</v>
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
       <c r="W28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="X28" s="4"/>
       <c r="Y28" s="4">
@@ -4991,8 +5066,8 @@
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4">
@@ -5020,22 +5095,25 @@
         <v>5</v>
       </c>
       <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
+      <c r="P29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
-      <c r="S29" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.88)</f>
-        <v>3.88</v>
-      </c>
-      <c r="T29" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2933333333333332)</f>
-        <v>1.293333333</v>
+      <c r="S29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
+      <c r="T29" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
       </c>
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
       <c r="W29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X29" s="4"/>
       <c r="Y29" s="4">
@@ -5117,11 +5195,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="9" t="str">
+      <c r="H1" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(8%)")</f>
         <v>TUTORIAS(8%)</v>
       </c>
-      <c r="I1" s="9" t="str">
+      <c r="I1" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu")</f>
         <v>PQT+Tu</v>
       </c>
@@ -5161,22 +5239,28 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr4")</f>
         <v>Tr4</v>
       </c>
-      <c r="S1" s="1"/>
-      <c r="T1" s="3" t="str">
+      <c r="S1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr5")</f>
+        <v>Tr5</v>
+      </c>
+      <c r="T1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr6")</f>
+        <v>Tr6</v>
+      </c>
+      <c r="U1" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
         <v>FINAL</v>
       </c>
-      <c r="U1" s="1" t="str">
+      <c r="V1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"meta3.0")</f>
         <v>meta3.0</v>
       </c>
-      <c r="V1" s="1"/>
       <c r="W1" s="1"/>
-      <c r="X1" s="1" t="str">
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"pqt(real)")</f>
         <v>pqt(real)</v>
       </c>
-      <c r="Y1" s="1"/>
       <c r="Z1" s="4"/>
     </row>
     <row r="2">
@@ -5200,10 +5284,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="F2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
@@ -5249,22 +5330,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S2" s="4"/>
-      <c r="T2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.635)</f>
-        <v>3.635</v>
-      </c>
-      <c r="U2" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2116666666666667)</f>
-        <v>1.211666667</v>
-      </c>
-      <c r="V2" s="4"/>
+      <c r="S2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T2" s="4"/>
+      <c r="U2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2349999999999994)</f>
+        <v>3.235</v>
+      </c>
+      <c r="V2" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0783333333333331)</f>
+        <v>1.078333333</v>
+      </c>
       <c r="W2" s="4"/>
-      <c r="X2" s="4">
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
     </row>
     <row r="3">
@@ -5288,10 +5372,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -5337,22 +5418,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S3" s="4"/>
-      <c r="T3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
-        <v>3.33</v>
-      </c>
-      <c r="U3" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.11)</f>
-        <v>1.11</v>
-      </c>
-      <c r="V3" s="4"/>
+      <c r="S3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T3" s="4"/>
+      <c r="U3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9299999999999997)</f>
+        <v>2.93</v>
+      </c>
+      <c r="V3" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9766666666666666)</f>
+        <v>0.9766666667</v>
+      </c>
       <c r="W3" s="4"/>
-      <c r="X3" s="4">
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
     </row>
     <row r="4">
@@ -5376,10 +5460,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -5425,22 +5506,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S4" s="4"/>
-      <c r="T4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.415)</f>
-        <v>3.415</v>
-      </c>
-      <c r="U4" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1383333333333334)</f>
-        <v>1.138333333</v>
-      </c>
-      <c r="V4" s="4"/>
+      <c r="S4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T4" s="4"/>
+      <c r="U4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0149999999999997)</f>
+        <v>3.015</v>
+      </c>
+      <c r="V4" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.005)</f>
+        <v>1.005</v>
+      </c>
       <c r="W4" s="4"/>
-      <c r="X4" s="4">
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
     <row r="5">
@@ -5464,10 +5548,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="F5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -5513,22 +5594,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S5" s="4"/>
-      <c r="T5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.64)</f>
-        <v>2.64</v>
-      </c>
-      <c r="U5" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.88)</f>
-        <v>0.88</v>
-      </c>
-      <c r="V5" s="4"/>
+      <c r="S5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T5" s="4"/>
+      <c r="U5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.24)</f>
+        <v>2.24</v>
+      </c>
+      <c r="V5" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7466666666666667)</f>
+        <v>0.7466666667</v>
+      </c>
       <c r="W5" s="4"/>
-      <c r="X5" s="4">
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
     <row r="6">
@@ -5552,10 +5636,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F6" s="4"/>
       <c r="G6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
@@ -5601,22 +5682,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="S6" s="4"/>
-      <c r="T6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8300000000000003)</f>
-        <v>1.83</v>
-      </c>
-      <c r="U6" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6100000000000001)</f>
-        <v>0.61</v>
-      </c>
-      <c r="V6" s="4"/>
+      <c r="S6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="4"/>
+      <c r="U6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4300000000000002)</f>
+        <v>1.43</v>
+      </c>
+      <c r="V6" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.47666666666666674)</f>
+        <v>0.4766666667</v>
+      </c>
       <c r="W6" s="4"/>
-      <c r="X6" s="4">
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
-      <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
     <row r="7">
@@ -5640,10 +5724,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F7" s="4"/>
       <c r="G7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -5689,22 +5770,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S7" s="4"/>
-      <c r="T7" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6700000000000004)</f>
-        <v>3.67</v>
-      </c>
-      <c r="U7" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2233333333333334)</f>
-        <v>1.223333333</v>
-      </c>
-      <c r="V7" s="4"/>
+      <c r="S7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T7" s="4"/>
+      <c r="U7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.27)</f>
+        <v>3.27</v>
+      </c>
+      <c r="V7" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.09)</f>
+        <v>1.09</v>
+      </c>
       <c r="W7" s="4"/>
-      <c r="X7" s="4">
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
     </row>
     <row r="8">
@@ -5728,10 +5812,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F8" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F8" s="4"/>
       <c r="G8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -5777,22 +5858,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S8" s="4"/>
-      <c r="T8" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.43)</f>
-        <v>3.43</v>
-      </c>
-      <c r="U8" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1433333333333333)</f>
-        <v>1.143333333</v>
-      </c>
-      <c r="V8" s="4"/>
+      <c r="S8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T8" s="4"/>
+      <c r="U8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.03)</f>
+        <v>3.03</v>
+      </c>
+      <c r="V8" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
+        <v>1.01</v>
+      </c>
       <c r="W8" s="4"/>
-      <c r="X8" s="4">
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
     </row>
     <row r="9">
@@ -5816,10 +5900,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
         <v>1.9</v>
       </c>
-      <c r="F9" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F9" s="4"/>
       <c r="G9" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -5865,22 +5946,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S9" s="4"/>
-      <c r="T9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.81)</f>
-        <v>2.81</v>
-      </c>
-      <c r="U9" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9366666666666666)</f>
-        <v>0.9366666667</v>
-      </c>
-      <c r="V9" s="4"/>
+      <c r="S9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T9" s="4"/>
+      <c r="U9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4099999999999997)</f>
+        <v>2.41</v>
+      </c>
+      <c r="V9" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8033333333333332)</f>
+        <v>0.8033333333</v>
+      </c>
       <c r="W9" s="4"/>
-      <c r="X9" s="4">
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
     </row>
     <row r="10">
@@ -5904,10 +5988,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F10" s="4"/>
       <c r="G10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -5953,22 +6034,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S10" s="4"/>
-      <c r="T10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8350000000000004)</f>
-        <v>3.835</v>
-      </c>
-      <c r="U10" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2783333333333335)</f>
-        <v>1.278333333</v>
-      </c>
-      <c r="V10" s="4"/>
+      <c r="S10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T10" s="4"/>
+      <c r="U10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.435)</f>
+        <v>3.435</v>
+      </c>
+      <c r="V10" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.145)</f>
+        <v>1.145</v>
+      </c>
       <c r="W10" s="4"/>
-      <c r="X10" s="4">
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
     </row>
     <row r="11">
@@ -5992,10 +6076,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="F11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F11" s="4"/>
       <c r="G11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -6041,22 +6122,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S11" s="4"/>
-      <c r="T11" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0700000000000003)</f>
-        <v>3.07</v>
-      </c>
-      <c r="U11" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0233333333333334)</f>
-        <v>1.023333333</v>
-      </c>
-      <c r="V11" s="4"/>
+      <c r="S11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T11" s="4"/>
+      <c r="U11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.67)</f>
+        <v>2.67</v>
+      </c>
+      <c r="V11" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.89)</f>
+        <v>0.89</v>
+      </c>
       <c r="W11" s="4"/>
-      <c r="X11" s="4">
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
     </row>
     <row r="12">
@@ -6080,10 +6164,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
         <v>1.7</v>
       </c>
-      <c r="F12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F12" s="4"/>
       <c r="G12" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -6129,22 +6210,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S12" s="4"/>
-      <c r="T12" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.35)</f>
-        <v>3.35</v>
-      </c>
-      <c r="U12" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1166666666666667)</f>
-        <v>1.116666667</v>
-      </c>
-      <c r="V12" s="4"/>
+      <c r="S12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T12" s="4"/>
+      <c r="U12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.95)</f>
+        <v>2.95</v>
+      </c>
+      <c r="V12" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9833333333333334)</f>
+        <v>0.9833333333</v>
+      </c>
       <c r="W12" s="4"/>
-      <c r="X12" s="4">
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
     </row>
     <row r="13">
@@ -6168,10 +6252,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="F13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F13" s="4"/>
       <c r="G13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -6217,22 +6298,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S13" s="4"/>
-      <c r="T13" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.695)</f>
-        <v>3.695</v>
-      </c>
-      <c r="U13" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2316666666666667)</f>
-        <v>1.231666667</v>
-      </c>
-      <c r="V13" s="4"/>
+      <c r="S13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T13" s="4"/>
+      <c r="U13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2950000000000004)</f>
+        <v>3.295</v>
+      </c>
+      <c r="V13" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0983333333333334)</f>
+        <v>1.098333333</v>
+      </c>
       <c r="W13" s="4"/>
-      <c r="X13" s="4">
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
     </row>
     <row r="14">
@@ -6256,10 +6340,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="F14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F14" s="4"/>
       <c r="G14" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
@@ -6305,22 +6386,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S14" s="4"/>
-      <c r="T14" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4850000000000003)</f>
-        <v>2.485</v>
-      </c>
-      <c r="U14" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8283333333333335)</f>
-        <v>0.8283333333</v>
-      </c>
-      <c r="V14" s="4"/>
+      <c r="S14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T14" s="4"/>
+      <c r="U14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.085)</f>
+        <v>2.085</v>
+      </c>
+      <c r="V14" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.695)</f>
+        <v>0.695</v>
+      </c>
       <c r="W14" s="4"/>
-      <c r="X14" s="4">
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
     <row r="15">
@@ -6370,15 +6454,15 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
-      <c r="T15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="U15" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="V15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="V15" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
@@ -6405,10 +6489,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F16" s="4"/>
       <c r="G16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
@@ -6454,22 +6535,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S16" s="4"/>
-      <c r="T16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.83)</f>
-        <v>2.83</v>
-      </c>
-      <c r="U16" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9433333333333334)</f>
-        <v>0.9433333333</v>
-      </c>
-      <c r="V16" s="4"/>
+      <c r="S16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T16" s="4"/>
+      <c r="U16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.43)</f>
+        <v>2.43</v>
+      </c>
+      <c r="V16" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.81)</f>
+        <v>0.81</v>
+      </c>
       <c r="W16" s="4"/>
-      <c r="X16" s="4">
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
     </row>
     <row r="17">
@@ -6493,10 +6577,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="F17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F17" s="4"/>
       <c r="G17" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -6542,22 +6623,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S17" s="4"/>
-      <c r="T17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9749999999999996)</f>
-        <v>2.975</v>
-      </c>
-      <c r="U17" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9916666666666666)</f>
-        <v>0.9916666667</v>
-      </c>
-      <c r="V17" s="4"/>
+      <c r="S17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T17" s="4"/>
+      <c r="U17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.575)</f>
+        <v>2.575</v>
+      </c>
+      <c r="V17" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8583333333333334)</f>
+        <v>0.8583333333</v>
+      </c>
       <c r="W17" s="4"/>
-      <c r="X17" s="4">
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
     </row>
     <row r="18">
@@ -6578,13 +6662,10 @@
         <v>1.5</v>
       </c>
       <c r="E18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="F18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F18" s="4"/>
       <c r="G18" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
@@ -6630,22 +6711,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S18" s="4"/>
-      <c r="T18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
-      </c>
-      <c r="U18" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6)</f>
-        <v>0.6</v>
-      </c>
-      <c r="V18" s="4"/>
+      <c r="S18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="4"/>
+      <c r="U18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.775)</f>
+        <v>1.775</v>
+      </c>
+      <c r="V18" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5916666666666667)</f>
+        <v>0.5916666667</v>
+      </c>
       <c r="W18" s="4"/>
-      <c r="X18" s="4">
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
     </row>
     <row r="19">
@@ -6669,10 +6753,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="F19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F19" s="4"/>
       <c r="G19" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -6718,22 +6799,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S19" s="4"/>
-      <c r="T19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.13)</f>
-        <v>3.13</v>
-      </c>
-      <c r="U19" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0433333333333332)</f>
-        <v>1.043333333</v>
-      </c>
-      <c r="V19" s="4"/>
+      <c r="S19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T19" s="4"/>
+      <c r="U19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7300000000000004)</f>
+        <v>2.73</v>
+      </c>
+      <c r="V19" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9100000000000001)</f>
+        <v>0.91</v>
+      </c>
       <c r="W19" s="4"/>
-      <c r="X19" s="4">
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
     </row>
     <row r="20">
@@ -6757,10 +6841,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="F20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F20" s="4"/>
       <c r="G20" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -6806,22 +6887,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S20" s="4"/>
-      <c r="T20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.025)</f>
-        <v>4.025</v>
-      </c>
-      <c r="U20" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3416666666666668)</f>
-        <v>1.341666667</v>
-      </c>
-      <c r="V20" s="4"/>
+      <c r="S20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T20" s="4"/>
+      <c r="U20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6249999999999996)</f>
+        <v>3.625</v>
+      </c>
+      <c r="V20" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2083333333333333)</f>
+        <v>1.208333333</v>
+      </c>
       <c r="W20" s="4"/>
-      <c r="X20" s="4">
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
     </row>
     <row r="21">
@@ -6845,10 +6929,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F21" s="4"/>
       <c r="G21" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -6894,22 +6975,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S21" s="4"/>
-      <c r="T21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.245)</f>
-        <v>3.245</v>
-      </c>
-      <c r="U21" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0816666666666668)</f>
-        <v>1.081666667</v>
-      </c>
-      <c r="V21" s="4"/>
+      <c r="S21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T21" s="4"/>
+      <c r="U21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8449999999999998)</f>
+        <v>2.845</v>
+      </c>
+      <c r="V21" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9483333333333333)</f>
+        <v>0.9483333333</v>
+      </c>
       <c r="W21" s="4"/>
-      <c r="X21" s="4">
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
     </row>
     <row r="22">
@@ -6933,10 +7017,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F22" s="4"/>
       <c r="G22" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -6982,22 +7063,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S22" s="4"/>
-      <c r="T22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5700000000000003)</f>
-        <v>3.57</v>
-      </c>
-      <c r="U22" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1900000000000002)</f>
-        <v>1.19</v>
-      </c>
-      <c r="V22" s="4"/>
+      <c r="S22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T22" s="4"/>
+      <c r="U22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.17)</f>
+        <v>3.17</v>
+      </c>
+      <c r="V22" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0566666666666666)</f>
+        <v>1.056666667</v>
+      </c>
       <c r="W22" s="4"/>
-      <c r="X22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="Y22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Z22" s="4"/>
     </row>
     <row r="23">
@@ -7021,10 +7105,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="F23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F23" s="4"/>
       <c r="G23" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -7070,22 +7151,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S23" s="4"/>
-      <c r="T23" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6599999999999997)</f>
-        <v>3.66</v>
-      </c>
-      <c r="U23" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.22)</f>
-        <v>1.22</v>
-      </c>
-      <c r="V23" s="4"/>
+      <c r="S23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T23" s="4"/>
+      <c r="U23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2600000000000002)</f>
+        <v>3.26</v>
+      </c>
+      <c r="V23" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0866666666666667)</f>
+        <v>1.086666667</v>
+      </c>
       <c r="W23" s="4"/>
-      <c r="X23" s="4">
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
     </row>
     <row r="24">
@@ -7109,10 +7193,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F24" s="4"/>
       <c r="G24" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
@@ -7158,22 +7239,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S24" s="4"/>
-      <c r="T24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.41)</f>
-        <v>2.41</v>
-      </c>
-      <c r="U24" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8033333333333333)</f>
-        <v>0.8033333333</v>
-      </c>
-      <c r="V24" s="4"/>
+      <c r="S24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T24" s="4"/>
+      <c r="U24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0100000000000002)</f>
+        <v>2.01</v>
+      </c>
+      <c r="V24" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.67)</f>
+        <v>0.67</v>
+      </c>
       <c r="W24" s="4"/>
-      <c r="X24" s="4">
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
     <row r="25">
@@ -7197,10 +7281,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
         <v>2.7</v>
       </c>
-      <c r="F25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F25" s="4"/>
       <c r="G25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -7246,22 +7327,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S25" s="4"/>
-      <c r="T25" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6000000000000005)</f>
-        <v>3.6</v>
-      </c>
-      <c r="U25" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2000000000000002)</f>
-        <v>1.2</v>
-      </c>
-      <c r="V25" s="4"/>
+      <c r="S25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T25" s="4"/>
+      <c r="U25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
+      <c r="V25" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0666666666666667)</f>
+        <v>1.066666667</v>
+      </c>
       <c r="W25" s="4"/>
-      <c r="X25" s="4">
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
     <row r="26">
@@ -7285,10 +7369,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="F26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F26" s="4"/>
       <c r="G26" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -7334,22 +7415,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S26" s="4"/>
-      <c r="T26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.145)</f>
-        <v>3.145</v>
-      </c>
-      <c r="U26" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0483333333333333)</f>
-        <v>1.048333333</v>
-      </c>
-      <c r="V26" s="4"/>
+      <c r="S26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T26" s="4"/>
+      <c r="U26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7449999999999997)</f>
+        <v>2.745</v>
+      </c>
+      <c r="V26" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9149999999999999)</f>
+        <v>0.915</v>
+      </c>
       <c r="W26" s="4"/>
-      <c r="X26" s="4">
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
     </row>
     <row r="27">
@@ -7373,10 +7457,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F27" s="4"/>
       <c r="G27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
@@ -7422,22 +7503,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S27" s="4"/>
-      <c r="T27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.865)</f>
-        <v>2.865</v>
-      </c>
-      <c r="U27" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9550000000000001)</f>
-        <v>0.955</v>
-      </c>
-      <c r="V27" s="4"/>
+      <c r="S27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T27" s="4"/>
+      <c r="U27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4650000000000003)</f>
+        <v>2.465</v>
+      </c>
+      <c r="V27" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8216666666666668)</f>
+        <v>0.8216666667</v>
+      </c>
       <c r="W27" s="4"/>
-      <c r="X27" s="4">
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
     </row>
     <row r="28">
@@ -7461,10 +7545,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F28" s="4"/>
       <c r="G28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -7510,22 +7591,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S28" s="4"/>
-      <c r="T28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.66)</f>
-        <v>3.66</v>
-      </c>
-      <c r="U28" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.22)</f>
-        <v>1.22</v>
-      </c>
-      <c r="V28" s="4"/>
+      <c r="S28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T28" s="4"/>
+      <c r="U28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.26)</f>
+        <v>3.26</v>
+      </c>
+      <c r="V28" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0866666666666667)</f>
+        <v>1.086666667</v>
+      </c>
       <c r="W28" s="4"/>
-      <c r="X28" s="4">
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
     </row>
     <row r="29">
@@ -7549,10 +7633,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F29" s="4"/>
       <c r="G29" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
@@ -7598,22 +7679,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S29" s="4"/>
-      <c r="T29" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.425)</f>
-        <v>2.425</v>
-      </c>
-      <c r="U29" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8083333333333332)</f>
-        <v>0.8083333333</v>
-      </c>
-      <c r="V29" s="4"/>
+      <c r="S29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T29" s="4"/>
+      <c r="U29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.025)</f>
+        <v>2.025</v>
+      </c>
+      <c r="V29" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6749999999999999)</f>
+        <v>0.675</v>
+      </c>
       <c r="W29" s="4"/>
-      <c r="X29" s="4">
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
-      <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
     </row>
     <row r="30">
@@ -7637,10 +7721,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F30" s="4"/>
       <c r="G30" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -7671,22 +7752,28 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S30" s="4"/>
-      <c r="T30" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.935)</f>
-        <v>2.935</v>
-      </c>
-      <c r="U30" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9783333333333334)</f>
-        <v>0.9783333333</v>
-      </c>
-      <c r="V30" s="4"/>
+      <c r="S30" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T30" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U30" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.535)</f>
+        <v>2.535</v>
+      </c>
+      <c r="V30" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8450000000000001)</f>
+        <v>0.845</v>
+      </c>
       <c r="W30" s="4"/>
-      <c r="X30" s="4">
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Y30" s="4"/>
       <c r="Z30" s="4"/>
     </row>
     <row r="31">
@@ -7710,10 +7797,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F31" s="4"/>
       <c r="G31" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -7759,22 +7843,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S31" s="4"/>
-      <c r="T31" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.185)</f>
-        <v>3.185</v>
-      </c>
-      <c r="U31" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0616666666666668)</f>
-        <v>1.061666667</v>
-      </c>
-      <c r="V31" s="4"/>
+      <c r="S31" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T31" s="4"/>
+      <c r="U31" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7849999999999997)</f>
+        <v>2.785</v>
+      </c>
+      <c r="V31" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9283333333333332)</f>
+        <v>0.9283333333</v>
+      </c>
       <c r="W31" s="4"/>
-      <c r="X31" s="4">
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Y31" s="4"/>
       <c r="Z31" s="4"/>
     </row>
     <row r="32">
@@ -7798,10 +7885,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F32" s="4"/>
       <c r="G32" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
         <v>1.2</v>
@@ -7847,22 +7931,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="S32" s="4"/>
-      <c r="T32" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.75)</f>
-        <v>1.75</v>
-      </c>
-      <c r="U32" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5833333333333334)</f>
-        <v>0.5833333333</v>
-      </c>
-      <c r="V32" s="4"/>
+      <c r="S32" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T32" s="4"/>
+      <c r="U32" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3499999999999999)</f>
+        <v>1.35</v>
+      </c>
+      <c r="V32" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.44999999999999996)</f>
+        <v>0.45</v>
+      </c>
       <c r="W32" s="4"/>
-      <c r="X32" s="4">
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
         <v>1.2</v>
       </c>
-      <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
     </row>
     <row r="33">
@@ -7886,10 +7973,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F33" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F33" s="4"/>
       <c r="G33" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -7935,22 +8019,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S33" s="4"/>
-      <c r="T33" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.125)</f>
-        <v>3.125</v>
-      </c>
-      <c r="U33" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0416666666666667)</f>
-        <v>1.041666667</v>
-      </c>
-      <c r="V33" s="4"/>
+      <c r="S33" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T33" s="4"/>
+      <c r="U33" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.725)</f>
+        <v>2.725</v>
+      </c>
+      <c r="V33" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9083333333333333)</f>
+        <v>0.9083333333</v>
+      </c>
       <c r="W33" s="4"/>
-      <c r="X33" s="4">
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="Y33" s="4"/>
       <c r="Z33" s="4"/>
     </row>
     <row r="34">
@@ -7974,10 +8061,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="F34" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F34" s="4"/>
       <c r="G34" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -8023,22 +8107,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S34" s="4"/>
-      <c r="T34" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.745)</f>
-        <v>3.745</v>
-      </c>
-      <c r="U34" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2483333333333333)</f>
-        <v>1.248333333</v>
-      </c>
-      <c r="V34" s="4"/>
+      <c r="S34" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T34" s="4"/>
+      <c r="U34" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.345)</f>
+        <v>3.345</v>
+      </c>
+      <c r="V34" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.115)</f>
+        <v>1.115</v>
+      </c>
       <c r="W34" s="4"/>
-      <c r="X34" s="4">
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
     </row>
     <row r="35">
@@ -8062,10 +8149,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F35" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F35" s="4"/>
       <c r="G35" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -8111,22 +8195,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S35" s="4"/>
-      <c r="T35" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.02)</f>
-        <v>3.02</v>
-      </c>
-      <c r="U35" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0066666666666666)</f>
-        <v>1.006666667</v>
-      </c>
-      <c r="V35" s="4"/>
+      <c r="S35" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T35" s="4"/>
+      <c r="U35" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6199999999999997)</f>
+        <v>2.62</v>
+      </c>
+      <c r="V35" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8733333333333332)</f>
+        <v>0.8733333333</v>
+      </c>
       <c r="W35" s="4"/>
-      <c r="X35" s="4">
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="Y35" s="4"/>
       <c r="Z35" s="4"/>
     </row>
     <row r="36">
@@ -8150,10 +8237,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F36" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F36" s="4"/>
       <c r="G36" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -8199,22 +8283,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S36" s="4"/>
-      <c r="T36" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.315)</f>
-        <v>3.315</v>
-      </c>
-      <c r="U36" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.105)</f>
-        <v>1.105</v>
-      </c>
-      <c r="V36" s="4"/>
+      <c r="S36" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T36" s="4"/>
+      <c r="U36" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.915)</f>
+        <v>2.915</v>
+      </c>
+      <c r="V36" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9716666666666667)</f>
+        <v>0.9716666667</v>
+      </c>
       <c r="W36" s="4"/>
-      <c r="X36" s="4">
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Y36" s="4"/>
       <c r="Z36" s="4"/>
     </row>
     <row r="37">
@@ -8238,10 +8325,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="F37" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F37" s="4"/>
       <c r="G37" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -8287,22 +8371,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S37" s="4"/>
-      <c r="T37" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.42)</f>
-        <v>2.42</v>
-      </c>
-      <c r="U37" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8066666666666666)</f>
-        <v>0.8066666667</v>
-      </c>
-      <c r="V37" s="4"/>
+      <c r="S37" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T37" s="4"/>
+      <c r="U37" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.02)</f>
+        <v>2.02</v>
+      </c>
+      <c r="V37" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6733333333333333)</f>
+        <v>0.6733333333</v>
+      </c>
       <c r="W37" s="4"/>
-      <c r="X37" s="4">
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
     </row>
     <row r="38">
@@ -8326,10 +8413,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
-      <c r="F38" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="F38" s="4"/>
       <c r="G38" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -8375,22 +8459,25 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S38" s="4"/>
-      <c r="T38" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.615)</f>
-        <v>3.615</v>
-      </c>
-      <c r="U38" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.205)</f>
-        <v>1.205</v>
-      </c>
-      <c r="V38" s="4"/>
+      <c r="S38" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T38" s="4"/>
+      <c r="U38" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2150000000000003)</f>
+        <v>3.215</v>
+      </c>
+      <c r="V38" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0716666666666668)</f>
+        <v>1.071666667</v>
+      </c>
       <c r="W38" s="4"/>
-      <c r="X38" s="4">
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="Y38" s="4"/>
       <c r="Z38" s="4"/>
     </row>
   </sheetData>
@@ -8467,11 +8554,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="9" t="str">
+      <c r="H1" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(10%)")</f>
         <v>TUTORIAS(10%)</v>
       </c>
-      <c r="I1" s="9" t="str">
+      <c r="I1" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu")</f>
         <v>PQT+Tu</v>
       </c>
@@ -8552,13 +8639,13 @@
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -8581,22 +8668,25 @@
         <v>5</v>
       </c>
       <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
+      <c r="P2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.705)</f>
-        <v>3.705</v>
-      </c>
-      <c r="T2" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.235)</f>
-        <v>1.235</v>
+      <c r="S2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.725)</f>
+        <v>3.725</v>
+      </c>
+      <c r="T2" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2416666666666667)</f>
+        <v>1.241666667</v>
       </c>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="4">
@@ -8628,13 +8718,13 @@
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -8657,22 +8747,25 @@
         <v>5</v>
       </c>
       <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
+      <c r="P3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-      <c r="S3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.11)</f>
-        <v>3.11</v>
-      </c>
-      <c r="T3" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0366666666666666)</f>
-        <v>1.036666667</v>
+      <c r="S3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.13)</f>
+        <v>3.13</v>
+      </c>
+      <c r="T3" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0433333333333332)</f>
+        <v>1.043333333</v>
       </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
       <c r="W3" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X3" s="4"/>
       <c r="Y3" s="4">
@@ -8704,13 +8797,13 @@
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="J4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -8733,22 +8826,25 @@
         <v>5</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
+      <c r="P4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.97)</f>
-        <v>2.97</v>
-      </c>
-      <c r="T4" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9900000000000001)</f>
-        <v>0.99</v>
+      <c r="S4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0300000000000002)</f>
+        <v>3.03</v>
+      </c>
+      <c r="T4" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
+        <v>1.01</v>
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="4">
@@ -8780,13 +8876,13 @@
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -8809,22 +8905,25 @@
         <v>5</v>
       </c>
       <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
+      <c r="P5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3150000000000004)</f>
-        <v>3.315</v>
-      </c>
-      <c r="T5" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1050000000000002)</f>
-        <v>1.105</v>
+      <c r="S5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.335)</f>
+        <v>3.335</v>
+      </c>
+      <c r="T5" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1116666666666666)</f>
+        <v>1.111666667</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X5" s="4"/>
       <c r="Y5" s="4">
@@ -8856,13 +8955,13 @@
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -8885,22 +8984,25 @@
         <v>5</v>
       </c>
       <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
+      <c r="P6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.63)</f>
-        <v>3.63</v>
-      </c>
-      <c r="T6" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.21)</f>
-        <v>1.21</v>
+      <c r="S6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.65)</f>
+        <v>3.65</v>
+      </c>
+      <c r="T6" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2166666666666666)</f>
+        <v>1.216666667</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X6" s="4"/>
       <c r="Y6" s="4">
@@ -8927,18 +9029,18 @@
         <v>3.7</v>
       </c>
       <c r="E7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="J7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -8958,22 +9060,25 @@
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
+      <c r="P7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
-      <c r="S7" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.385)</f>
-        <v>2.385</v>
-      </c>
-      <c r="T7" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7949999999999999)</f>
-        <v>0.795</v>
+      <c r="S7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.605)</f>
+        <v>2.605</v>
+      </c>
+      <c r="T7" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8683333333333333)</f>
+        <v>0.8683333333</v>
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
       <c r="W7" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="X7" s="4"/>
       <c r="Y7" s="4">
@@ -9034,14 +9139,17 @@
         <v>5</v>
       </c>
       <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
+      <c r="P8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="7">
+      <c r="S8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.725)</f>
         <v>3.725</v>
       </c>
-      <c r="T8" s="10">
+      <c r="T8" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2416666666666667)</f>
         <v>1.241666667</v>
       </c>
@@ -9092,11 +9200,11 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="T9" s="10">
+      <c r="S9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -9133,8 +9241,8 @@
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4">
@@ -9162,22 +9270,25 @@
         <v>5</v>
       </c>
       <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
+      <c r="P10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
-      <c r="S10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.335)</f>
-        <v>3.335</v>
-      </c>
-      <c r="T10" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1116666666666666)</f>
-        <v>1.111666667</v>
+      <c r="S10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3550000000000004)</f>
+        <v>3.355</v>
+      </c>
+      <c r="T10" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1183333333333334)</f>
+        <v>1.118333333</v>
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X10" s="4"/>
       <c r="Y10" s="4">
@@ -9238,14 +9349,17 @@
         <v>5</v>
       </c>
       <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
+      <c r="P11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
-      <c r="S11" s="7">
+      <c r="S11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.44)</f>
         <v>3.44</v>
       </c>
-      <c r="T11" s="10">
+      <c r="T11" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1466666666666667)</f>
         <v>1.146666667</v>
       </c>
@@ -9285,13 +9399,13 @@
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J12" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -9314,22 +9428,25 @@
         <v>5</v>
       </c>
       <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
+      <c r="P12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
-      <c r="S12" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2700000000000005)</f>
-        <v>3.27</v>
-      </c>
-      <c r="T12" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.09)</f>
-        <v>1.09</v>
+      <c r="S12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.29)</f>
+        <v>3.29</v>
+      </c>
+      <c r="T12" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0966666666666667)</f>
+        <v>1.096666667</v>
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X12" s="4"/>
       <c r="Y12" s="4">
@@ -9361,13 +9478,13 @@
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -9390,22 +9507,25 @@
         <v>5</v>
       </c>
       <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
+      <c r="P13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
-      <c r="S13" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.325)</f>
-        <v>3.325</v>
-      </c>
-      <c r="T13" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1083333333333334)</f>
-        <v>1.108333333</v>
+      <c r="S13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3449999999999998)</f>
+        <v>3.345</v>
+      </c>
+      <c r="T13" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.115)</f>
+        <v>1.115</v>
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
       <c r="W13" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X13" s="4"/>
       <c r="Y13" s="4">
@@ -9437,8 +9557,8 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4">
@@ -9466,22 +9586,25 @@
         <v>5</v>
       </c>
       <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
+      <c r="P14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-      <c r="S14" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.815)</f>
-        <v>3.815</v>
-      </c>
-      <c r="T14" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2716666666666667)</f>
-        <v>1.271666667</v>
+      <c r="S14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.835)</f>
+        <v>3.835</v>
+      </c>
+      <c r="T14" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2783333333333333)</f>
+        <v>1.278333333</v>
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="X14" s="4"/>
       <c r="Y14" s="4">
@@ -9513,13 +9636,13 @@
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="J15" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -9542,22 +9665,25 @@
         <v>5</v>
       </c>
       <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
+      <c r="P15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
-      <c r="S15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2350000000000003)</f>
-        <v>3.235</v>
-      </c>
-      <c r="T15" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0783333333333334)</f>
-        <v>1.078333333</v>
+      <c r="S15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2950000000000004)</f>
+        <v>3.295</v>
+      </c>
+      <c r="T15" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0983333333333334)</f>
+        <v>1.098333333</v>
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="X15" s="4"/>
       <c r="Y15" s="4">
@@ -9589,13 +9715,13 @@
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -9618,22 +9744,25 @@
         <v>5</v>
       </c>
       <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6149999999999998)</f>
-        <v>3.615</v>
-      </c>
-      <c r="T16" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2049999999999998)</f>
-        <v>1.205</v>
+      <c r="S16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.635)</f>
+        <v>3.635</v>
+      </c>
+      <c r="T16" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2116666666666667)</f>
+        <v>1.211666667</v>
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X16" s="4"/>
       <c r="Y16" s="4">
@@ -9665,13 +9794,13 @@
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J17" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -9694,22 +9823,25 @@
         <v>5</v>
       </c>
       <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
+      <c r="P17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
-      <c r="S17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9699999999999998)</f>
-        <v>2.97</v>
-      </c>
-      <c r="T17" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9899999999999999)</f>
-        <v>0.99</v>
+      <c r="S17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9899999999999998)</f>
+        <v>2.99</v>
+      </c>
+      <c r="T17" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9966666666666666)</f>
+        <v>0.9966666667</v>
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X17" s="4"/>
       <c r="Y17" s="4">
@@ -9741,8 +9873,8 @@
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4">
@@ -9770,22 +9902,25 @@
         <v>5</v>
       </c>
       <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
+      <c r="P18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
-      <c r="S18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.975)</f>
-        <v>2.975</v>
-      </c>
-      <c r="T18" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9916666666666667)</f>
-        <v>0.9916666667</v>
+      <c r="S18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.995)</f>
+        <v>2.995</v>
+      </c>
+      <c r="T18" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9983333333333334)</f>
+        <v>0.9983333333</v>
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X18" s="4"/>
       <c r="Y18" s="4">
@@ -9817,13 +9952,13 @@
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J19" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -9846,22 +9981,25 @@
         <v>5</v>
       </c>
       <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
+      <c r="P19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
-      <c r="S19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.665)</f>
-        <v>3.665</v>
-      </c>
-      <c r="T19" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2216666666666667)</f>
-        <v>1.221666667</v>
+      <c r="S19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.685)</f>
+        <v>3.685</v>
+      </c>
+      <c r="T19" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2283333333333333)</f>
+        <v>1.228333333</v>
       </c>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X19" s="4"/>
       <c r="Y19" s="4">
@@ -9893,8 +10031,8 @@
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4">
@@ -9922,22 +10060,25 @@
         <v>5</v>
       </c>
       <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
+      <c r="P20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.29)</f>
-        <v>3.29</v>
-      </c>
-      <c r="T20" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0966666666666667)</f>
-        <v>1.096666667</v>
+      <c r="S20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.31)</f>
+        <v>3.31</v>
+      </c>
+      <c r="T20" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1033333333333333)</f>
+        <v>1.103333333</v>
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X20" s="4"/>
       <c r="Y20" s="4">
@@ -9969,13 +10110,13 @@
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J21" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -9998,22 +10139,25 @@
         <v>5</v>
       </c>
       <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
+      <c r="P21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
-      <c r="S21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.63)</f>
-        <v>3.63</v>
-      </c>
-      <c r="T21" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.21)</f>
-        <v>1.21</v>
+      <c r="S21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.65)</f>
+        <v>3.65</v>
+      </c>
+      <c r="T21" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2166666666666666)</f>
+        <v>1.216666667</v>
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
       <c r="W21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X21" s="4"/>
       <c r="Y21" s="4">
@@ -10045,13 +10189,13 @@
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="J22" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -10074,22 +10218,25 @@
         <v>5</v>
       </c>
       <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
+      <c r="P22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
-      <c r="S22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.62)</f>
-        <v>3.62</v>
-      </c>
-      <c r="T22" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2066666666666668)</f>
-        <v>1.206666667</v>
+      <c r="S22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.64)</f>
+        <v>3.64</v>
+      </c>
+      <c r="T22" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2133333333333334)</f>
+        <v>1.213333333</v>
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
       <c r="W22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X22" s="4"/>
       <c r="Y22" s="4">
@@ -10121,51 +10268,54 @@
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="J23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="K23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="L23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="M23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="J23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="K23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="L23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="M23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
-      </c>
-      <c r="T23" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2666666666666666)</f>
-        <v>1.266666667</v>
+      <c r="T23" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3333333333333333)</f>
+        <v>1.333333333</v>
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
       <c r="W23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="X23" s="4"/>
       <c r="Y23" s="4">
@@ -10197,8 +10347,8 @@
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4">
@@ -10226,22 +10376,25 @@
         <v>5</v>
       </c>
       <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
+      <c r="P24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
-      <c r="S24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.62)</f>
-        <v>3.62</v>
-      </c>
-      <c r="T24" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2066666666666668)</f>
-        <v>1.206666667</v>
+      <c r="S24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.64)</f>
+        <v>3.64</v>
+      </c>
+      <c r="T24" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2133333333333334)</f>
+        <v>1.213333333</v>
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="X24" s="4"/>
       <c r="Y24" s="4">
@@ -10302,14 +10455,17 @@
         <v>5</v>
       </c>
       <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
+      <c r="P25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
-      <c r="S25" s="7">
+      <c r="S25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.725)</f>
         <v>3.725</v>
       </c>
-      <c r="T25" s="10">
+      <c r="T25" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2416666666666667)</f>
         <v>1.241666667</v>
       </c>
@@ -10349,13 +10505,13 @@
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
-        <v>1.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
+        <v>1.1</v>
       </c>
       <c r="J26" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -10378,22 +10534,25 @@
         <v>0</v>
       </c>
       <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
+      <c r="P26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
-      <c r="S26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.03)</f>
-        <v>1.03</v>
-      </c>
-      <c r="T26" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3433333333333333)</f>
-        <v>0.3433333333</v>
+      <c r="S26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9500000000000001)</f>
+        <v>0.95</v>
+      </c>
+      <c r="T26" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3166666666666667)</f>
+        <v>0.3166666667</v>
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="X26" s="4"/>
       <c r="Y26" s="4">
@@ -10425,13 +10584,13 @@
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J27" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -10454,22 +10613,25 @@
         <v>5</v>
       </c>
       <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
+      <c r="P27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
-      <c r="S27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.585)</f>
-        <v>2.585</v>
-      </c>
-      <c r="T27" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8616666666666667)</f>
-        <v>0.8616666667</v>
+      <c r="S27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.605)</f>
+        <v>2.605</v>
+      </c>
+      <c r="T27" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8683333333333333)</f>
+        <v>0.8683333333</v>
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
       <c r="W27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X27" s="4"/>
       <c r="Y27" s="4">
@@ -10501,13 +10663,13 @@
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="J28" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -10530,22 +10692,25 @@
         <v>5</v>
       </c>
       <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
+      <c r="P28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
-      <c r="S28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9400000000000004)</f>
-        <v>2.94</v>
-      </c>
-      <c r="T28" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9800000000000001)</f>
-        <v>0.98</v>
+      <c r="S28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.96)</f>
+        <v>2.96</v>
+      </c>
+      <c r="T28" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9866666666666667)</f>
+        <v>0.9866666667</v>
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
       <c r="W28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X28" s="4"/>
       <c r="Y28" s="4">

--- a/app_notas_uis.xlsx
+++ b/app_notas_uis.xlsx
@@ -5163,12 +5163,12 @@
     <col customWidth="1" min="23" max="23" width="7.75"/>
     <col customWidth="1" min="24" max="24" width="3.88"/>
     <col customWidth="1" min="25" max="25" width="7.75"/>
-    <col customWidth="1" min="26" max="26" width="3.88"/>
+    <col customWidth="1" min="26" max="37" width="3.88"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1IBQjOws3WhAXDJftgpUWc3oN7u_5yElNOe9-ViV3LKs"",""CALC1!A1:Y38"")"),"No")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1IBQjOws3WhAXDJftgpUWc3oN7u_5yElNOe9-ViV3LKs"",""CALC1!A1:AA38"")"),"No")</f>
         <v>No</v>
       </c>
       <c r="B1" s="2" t="str">
@@ -5262,6 +5262,20 @@
         <v>pqt(real)</v>
       </c>
       <c r="Z1" s="4"/>
+      <c r="AA1" s="4" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COD")</f>
+        <v>COD</v>
+      </c>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
     </row>
     <row r="2">
       <c r="A2" s="4">
@@ -5350,6 +5364,20 @@
         <v>4.2</v>
       </c>
       <c r="Z2" s="4"/>
+      <c r="AA2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261221.0)</f>
+        <v>2261221</v>
+      </c>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+      <c r="AK2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="4">
@@ -5438,6 +5466,20 @@
         <v>4.8</v>
       </c>
       <c r="Z3" s="4"/>
+      <c r="AA3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261862.0)</f>
+        <v>2261862</v>
+      </c>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="4">
@@ -5526,6 +5568,20 @@
         <v>4.5</v>
       </c>
       <c r="Z4" s="4"/>
+      <c r="AA4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261933.0)</f>
+        <v>2261933</v>
+      </c>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4"/>
+      <c r="AH4" s="4"/>
+      <c r="AI4" s="4"/>
+      <c r="AJ4" s="4"/>
+      <c r="AK4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="4">
@@ -5614,6 +5670,20 @@
         <v>4.4</v>
       </c>
       <c r="Z5" s="4"/>
+      <c r="AA5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262154.0)</f>
+        <v>2262154</v>
+      </c>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="4"/>
+      <c r="AH5" s="4"/>
+      <c r="AI5" s="4"/>
+      <c r="AJ5" s="4"/>
+      <c r="AK5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="4">
@@ -5702,6 +5772,20 @@
         <v>3.4</v>
       </c>
       <c r="Z6" s="4"/>
+      <c r="AA6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261830.0)</f>
+        <v>2261830</v>
+      </c>
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
+      <c r="AH6" s="4"/>
+      <c r="AI6" s="4"/>
+      <c r="AJ6" s="4"/>
+      <c r="AK6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="4">
@@ -5790,6 +5874,20 @@
         <v>4.6</v>
       </c>
       <c r="Z7" s="4"/>
+      <c r="AA7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261224.0)</f>
+        <v>2261224</v>
+      </c>
+      <c r="AB7" s="4"/>
+      <c r="AC7" s="4"/>
+      <c r="AD7" s="4"/>
+      <c r="AE7" s="4"/>
+      <c r="AF7" s="4"/>
+      <c r="AG7" s="4"/>
+      <c r="AH7" s="4"/>
+      <c r="AI7" s="4"/>
+      <c r="AJ7" s="4"/>
+      <c r="AK7" s="4"/>
     </row>
     <row r="8">
       <c r="A8" s="4">
@@ -5878,6 +5976,20 @@
         <v>4.6</v>
       </c>
       <c r="Z8" s="4"/>
+      <c r="AA8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262001.0)</f>
+        <v>2262001</v>
+      </c>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AH8" s="4"/>
+      <c r="AI8" s="4"/>
+      <c r="AJ8" s="4"/>
+      <c r="AK8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="4">
@@ -5966,6 +6078,20 @@
         <v>4.5</v>
       </c>
       <c r="Z9" s="4"/>
+      <c r="AA9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261874.0)</f>
+        <v>2261874</v>
+      </c>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="4"/>
+      <c r="AG9" s="4"/>
+      <c r="AH9" s="4"/>
+      <c r="AI9" s="4"/>
+      <c r="AJ9" s="4"/>
+      <c r="AK9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="4">
@@ -6054,6 +6180,20 @@
         <v>4.9</v>
       </c>
       <c r="Z10" s="4"/>
+      <c r="AA10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261914.0)</f>
+        <v>2261914</v>
+      </c>
+      <c r="AB10" s="4"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4"/>
+      <c r="AF10" s="4"/>
+      <c r="AG10" s="4"/>
+      <c r="AH10" s="4"/>
+      <c r="AI10" s="4"/>
+      <c r="AJ10" s="4"/>
+      <c r="AK10" s="4"/>
     </row>
     <row r="11">
       <c r="A11" s="4">
@@ -6142,6 +6282,20 @@
         <v>4.7</v>
       </c>
       <c r="Z11" s="4"/>
+      <c r="AA11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262150.0)</f>
+        <v>2262150</v>
+      </c>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4"/>
+      <c r="AI11" s="4"/>
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="4">
@@ -6230,6 +6384,20 @@
         <v>4.7</v>
       </c>
       <c r="Z12" s="4"/>
+      <c r="AA12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2260424.0)</f>
+        <v>2260424</v>
+      </c>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4"/>
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="4">
@@ -6318,6 +6486,20 @@
         <v>4.9</v>
       </c>
       <c r="Z13" s="4"/>
+      <c r="AA13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262136.0)</f>
+        <v>2262136</v>
+      </c>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="4"/>
+      <c r="AE13" s="4"/>
+      <c r="AF13" s="4"/>
+      <c r="AG13" s="4"/>
+      <c r="AH13" s="4"/>
+      <c r="AI13" s="4"/>
+      <c r="AJ13" s="4"/>
+      <c r="AK13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="4">
@@ -6406,6 +6588,20 @@
         <v>3.2</v>
       </c>
       <c r="Z14" s="4"/>
+      <c r="AA14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261756.0)</f>
+        <v>2261756</v>
+      </c>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4"/>
+      <c r="AF14" s="4"/>
+      <c r="AG14" s="4"/>
+      <c r="AH14" s="4"/>
+      <c r="AI14" s="4"/>
+      <c r="AJ14" s="4"/>
+      <c r="AK14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="4">
@@ -6467,6 +6663,20 @@
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
+      <c r="AA15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261849.0)</f>
+        <v>2261849</v>
+      </c>
+      <c r="AB15" s="4"/>
+      <c r="AC15" s="4"/>
+      <c r="AD15" s="4"/>
+      <c r="AE15" s="4"/>
+      <c r="AF15" s="4"/>
+      <c r="AG15" s="4"/>
+      <c r="AH15" s="4"/>
+      <c r="AI15" s="4"/>
+      <c r="AJ15" s="4"/>
+      <c r="AK15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="4">
@@ -6555,6 +6765,20 @@
         <v>4.3</v>
       </c>
       <c r="Z16" s="4"/>
+      <c r="AA16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262090.0)</f>
+        <v>2262090</v>
+      </c>
+      <c r="AB16" s="4"/>
+      <c r="AC16" s="4"/>
+      <c r="AD16" s="4"/>
+      <c r="AE16" s="4"/>
+      <c r="AF16" s="4"/>
+      <c r="AG16" s="4"/>
+      <c r="AH16" s="4"/>
+      <c r="AI16" s="4"/>
+      <c r="AJ16" s="4"/>
+      <c r="AK16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="4">
@@ -6643,6 +6867,20 @@
         <v>4.5</v>
       </c>
       <c r="Z17" s="4"/>
+      <c r="AA17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262094.0)</f>
+        <v>2262094</v>
+      </c>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AF17" s="4"/>
+      <c r="AG17" s="4"/>
+      <c r="AH17" s="4"/>
+      <c r="AI17" s="4"/>
+      <c r="AJ17" s="4"/>
+      <c r="AK17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="4">
@@ -6731,6 +6969,20 @@
         <v>2.2</v>
       </c>
       <c r="Z18" s="4"/>
+      <c r="AA18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261863.0)</f>
+        <v>2261863</v>
+      </c>
+      <c r="AB18" s="4"/>
+      <c r="AC18" s="4"/>
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="4"/>
+      <c r="AF18" s="4"/>
+      <c r="AG18" s="4"/>
+      <c r="AH18" s="4"/>
+      <c r="AI18" s="4"/>
+      <c r="AJ18" s="4"/>
+      <c r="AK18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="4">
@@ -6819,6 +7071,20 @@
         <v>4.8</v>
       </c>
       <c r="Z19" s="4"/>
+      <c r="AA19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262075.0)</f>
+        <v>2262075</v>
+      </c>
+      <c r="AB19" s="4"/>
+      <c r="AC19" s="4"/>
+      <c r="AD19" s="4"/>
+      <c r="AE19" s="4"/>
+      <c r="AF19" s="4"/>
+      <c r="AG19" s="4"/>
+      <c r="AH19" s="4"/>
+      <c r="AI19" s="4"/>
+      <c r="AJ19" s="4"/>
+      <c r="AK19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="4">
@@ -6907,6 +7173,20 @@
         <v>4.9</v>
       </c>
       <c r="Z20" s="4"/>
+      <c r="AA20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2260425.0)</f>
+        <v>2260425</v>
+      </c>
+      <c r="AB20" s="4"/>
+      <c r="AC20" s="4"/>
+      <c r="AD20" s="4"/>
+      <c r="AE20" s="4"/>
+      <c r="AF20" s="4"/>
+      <c r="AG20" s="4"/>
+      <c r="AH20" s="4"/>
+      <c r="AI20" s="4"/>
+      <c r="AJ20" s="4"/>
+      <c r="AK20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="4">
@@ -6995,6 +7275,20 @@
         <v>4.8</v>
       </c>
       <c r="Z21" s="4"/>
+      <c r="AA21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261219.0)</f>
+        <v>2261219</v>
+      </c>
+      <c r="AB21" s="4"/>
+      <c r="AC21" s="4"/>
+      <c r="AD21" s="4"/>
+      <c r="AE21" s="4"/>
+      <c r="AF21" s="4"/>
+      <c r="AG21" s="4"/>
+      <c r="AH21" s="4"/>
+      <c r="AI21" s="4"/>
+      <c r="AJ21" s="4"/>
+      <c r="AK21" s="4"/>
     </row>
     <row r="22">
       <c r="A22" s="4">
@@ -7083,6 +7377,20 @@
         <v>5</v>
       </c>
       <c r="Z22" s="4"/>
+      <c r="AA22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261864.0)</f>
+        <v>2261864</v>
+      </c>
+      <c r="AB22" s="4"/>
+      <c r="AC22" s="4"/>
+      <c r="AD22" s="4"/>
+      <c r="AE22" s="4"/>
+      <c r="AF22" s="4"/>
+      <c r="AG22" s="4"/>
+      <c r="AH22" s="4"/>
+      <c r="AI22" s="4"/>
+      <c r="AJ22" s="4"/>
+      <c r="AK22" s="4"/>
     </row>
     <row r="23">
       <c r="A23" s="4">
@@ -7171,6 +7479,20 @@
         <v>4.9</v>
       </c>
       <c r="Z23" s="4"/>
+      <c r="AA23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261216.0)</f>
+        <v>2261216</v>
+      </c>
+      <c r="AB23" s="4"/>
+      <c r="AC23" s="4"/>
+      <c r="AD23" s="4"/>
+      <c r="AE23" s="4"/>
+      <c r="AF23" s="4"/>
+      <c r="AG23" s="4"/>
+      <c r="AH23" s="4"/>
+      <c r="AI23" s="4"/>
+      <c r="AJ23" s="4"/>
+      <c r="AK23" s="4"/>
     </row>
     <row r="24">
       <c r="A24" s="4">
@@ -7259,6 +7581,20 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="4"/>
+      <c r="AA24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261215.0)</f>
+        <v>2261215</v>
+      </c>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AF24" s="4"/>
+      <c r="AG24" s="4"/>
+      <c r="AH24" s="4"/>
+      <c r="AI24" s="4"/>
+      <c r="AJ24" s="4"/>
+      <c r="AK24" s="4"/>
     </row>
     <row r="25">
       <c r="A25" s="4">
@@ -7347,6 +7683,20 @@
         <v>4.7</v>
       </c>
       <c r="Z25" s="4"/>
+      <c r="AA25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261195.0)</f>
+        <v>2261195</v>
+      </c>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AF25" s="4"/>
+      <c r="AG25" s="4"/>
+      <c r="AH25" s="4"/>
+      <c r="AI25" s="4"/>
+      <c r="AJ25" s="4"/>
+      <c r="AK25" s="4"/>
     </row>
     <row r="26">
       <c r="A26" s="4">
@@ -7435,6 +7785,20 @@
         <v>4.5</v>
       </c>
       <c r="Z26" s="4"/>
+      <c r="AA26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261681.0)</f>
+        <v>2261681</v>
+      </c>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+      <c r="AF26" s="4"/>
+      <c r="AG26" s="4"/>
+      <c r="AH26" s="4"/>
+      <c r="AI26" s="4"/>
+      <c r="AJ26" s="4"/>
+      <c r="AK26" s="4"/>
     </row>
     <row r="27">
       <c r="A27" s="4">
@@ -7523,6 +7887,20 @@
         <v>4</v>
       </c>
       <c r="Z27" s="4"/>
+      <c r="AA27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261757.0)</f>
+        <v>2261757</v>
+      </c>
+      <c r="AB27" s="4"/>
+      <c r="AC27" s="4"/>
+      <c r="AD27" s="4"/>
+      <c r="AE27" s="4"/>
+      <c r="AF27" s="4"/>
+      <c r="AG27" s="4"/>
+      <c r="AH27" s="4"/>
+      <c r="AI27" s="4"/>
+      <c r="AJ27" s="4"/>
+      <c r="AK27" s="4"/>
     </row>
     <row r="28">
       <c r="A28" s="4">
@@ -7611,6 +7989,20 @@
         <v>4.8</v>
       </c>
       <c r="Z28" s="4"/>
+      <c r="AA28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261218.0)</f>
+        <v>2261218</v>
+      </c>
+      <c r="AB28" s="4"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="4"/>
+      <c r="AF28" s="4"/>
+      <c r="AG28" s="4"/>
+      <c r="AH28" s="4"/>
+      <c r="AI28" s="4"/>
+      <c r="AJ28" s="4"/>
+      <c r="AK28" s="4"/>
     </row>
     <row r="29">
       <c r="A29" s="4">
@@ -7699,6 +8091,20 @@
         <v>3.7</v>
       </c>
       <c r="Z29" s="4"/>
+      <c r="AA29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261915.0)</f>
+        <v>2261915</v>
+      </c>
+      <c r="AB29" s="4"/>
+      <c r="AC29" s="4"/>
+      <c r="AD29" s="4"/>
+      <c r="AE29" s="4"/>
+      <c r="AF29" s="4"/>
+      <c r="AG29" s="4"/>
+      <c r="AH29" s="4"/>
+      <c r="AI29" s="4"/>
+      <c r="AJ29" s="4"/>
+      <c r="AK29" s="4"/>
     </row>
     <row r="30">
       <c r="A30" s="4">
@@ -7775,6 +8181,20 @@
         <v>4.9</v>
       </c>
       <c r="Z30" s="4"/>
+      <c r="AA30" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2202217.0)</f>
+        <v>2202217</v>
+      </c>
+      <c r="AB30" s="4"/>
+      <c r="AC30" s="4"/>
+      <c r="AD30" s="4"/>
+      <c r="AE30" s="4"/>
+      <c r="AF30" s="4"/>
+      <c r="AG30" s="4"/>
+      <c r="AH30" s="4"/>
+      <c r="AI30" s="4"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="4"/>
     </row>
     <row r="31">
       <c r="A31" s="4">
@@ -7863,6 +8283,20 @@
         <v>4.9</v>
       </c>
       <c r="Z31" s="4"/>
+      <c r="AA31" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261881.0)</f>
+        <v>2261881</v>
+      </c>
+      <c r="AB31" s="4"/>
+      <c r="AC31" s="4"/>
+      <c r="AD31" s="4"/>
+      <c r="AE31" s="4"/>
+      <c r="AF31" s="4"/>
+      <c r="AG31" s="4"/>
+      <c r="AH31" s="4"/>
+      <c r="AI31" s="4"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
     </row>
     <row r="32">
       <c r="A32" s="4">
@@ -7951,6 +8385,20 @@
         <v>1.2</v>
       </c>
       <c r="Z32" s="4"/>
+      <c r="AA32" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262036.0)</f>
+        <v>2262036</v>
+      </c>
+      <c r="AB32" s="4"/>
+      <c r="AC32" s="4"/>
+      <c r="AD32" s="4"/>
+      <c r="AE32" s="4"/>
+      <c r="AF32" s="4"/>
+      <c r="AG32" s="4"/>
+      <c r="AH32" s="4"/>
+      <c r="AI32" s="4"/>
+      <c r="AJ32" s="4"/>
+      <c r="AK32" s="4"/>
     </row>
     <row r="33">
       <c r="A33" s="4">
@@ -8039,6 +8487,20 @@
         <v>4.7</v>
       </c>
       <c r="Z33" s="4"/>
+      <c r="AA33" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262165.0)</f>
+        <v>2262165</v>
+      </c>
+      <c r="AB33" s="4"/>
+      <c r="AC33" s="4"/>
+      <c r="AD33" s="4"/>
+      <c r="AE33" s="4"/>
+      <c r="AF33" s="4"/>
+      <c r="AG33" s="4"/>
+      <c r="AH33" s="4"/>
+      <c r="AI33" s="4"/>
+      <c r="AJ33" s="4"/>
+      <c r="AK33" s="4"/>
     </row>
     <row r="34">
       <c r="A34" s="4">
@@ -8127,6 +8589,20 @@
         <v>4.9</v>
       </c>
       <c r="Z34" s="4"/>
+      <c r="AA34" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262141.0)</f>
+        <v>2262141</v>
+      </c>
+      <c r="AB34" s="4"/>
+      <c r="AC34" s="4"/>
+      <c r="AD34" s="4"/>
+      <c r="AE34" s="4"/>
+      <c r="AF34" s="4"/>
+      <c r="AG34" s="4"/>
+      <c r="AH34" s="4"/>
+      <c r="AI34" s="4"/>
+      <c r="AJ34" s="4"/>
+      <c r="AK34" s="4"/>
     </row>
     <row r="35">
       <c r="A35" s="4">
@@ -8215,6 +8691,20 @@
         <v>4.5</v>
       </c>
       <c r="Z35" s="4"/>
+      <c r="AA35" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262202.0)</f>
+        <v>2262202</v>
+      </c>
+      <c r="AB35" s="4"/>
+      <c r="AC35" s="4"/>
+      <c r="AD35" s="4"/>
+      <c r="AE35" s="4"/>
+      <c r="AF35" s="4"/>
+      <c r="AG35" s="4"/>
+      <c r="AH35" s="4"/>
+      <c r="AI35" s="4"/>
+      <c r="AJ35" s="4"/>
+      <c r="AK35" s="4"/>
     </row>
     <row r="36">
       <c r="A36" s="4">
@@ -8303,6 +8793,20 @@
         <v>4.9</v>
       </c>
       <c r="Z36" s="4"/>
+      <c r="AA36" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262161.0)</f>
+        <v>2262161</v>
+      </c>
+      <c r="AB36" s="4"/>
+      <c r="AC36" s="4"/>
+      <c r="AD36" s="4"/>
+      <c r="AE36" s="4"/>
+      <c r="AF36" s="4"/>
+      <c r="AG36" s="4"/>
+      <c r="AH36" s="4"/>
+      <c r="AI36" s="4"/>
+      <c r="AJ36" s="4"/>
+      <c r="AK36" s="4"/>
     </row>
     <row r="37">
       <c r="A37" s="4">
@@ -8391,6 +8895,20 @@
         <v>3.8</v>
       </c>
       <c r="Z37" s="4"/>
+      <c r="AA37" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261809.0)</f>
+        <v>2261809</v>
+      </c>
+      <c r="AB37" s="4"/>
+      <c r="AC37" s="4"/>
+      <c r="AD37" s="4"/>
+      <c r="AE37" s="4"/>
+      <c r="AF37" s="4"/>
+      <c r="AG37" s="4"/>
+      <c r="AH37" s="4"/>
+      <c r="AI37" s="4"/>
+      <c r="AJ37" s="4"/>
+      <c r="AK37" s="4"/>
     </row>
     <row r="38">
       <c r="A38" s="4">
@@ -8479,6 +8997,20 @@
         <v>4.7</v>
       </c>
       <c r="Z38" s="4"/>
+      <c r="AA38" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262214.0)</f>
+        <v>2262214</v>
+      </c>
+      <c r="AB38" s="4"/>
+      <c r="AC38" s="4"/>
+      <c r="AD38" s="4"/>
+      <c r="AE38" s="4"/>
+      <c r="AF38" s="4"/>
+      <c r="AG38" s="4"/>
+      <c r="AH38" s="4"/>
+      <c r="AI38" s="4"/>
+      <c r="AJ38" s="4"/>
+      <c r="AK38" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="T2:T38">

--- a/app_notas_uis.xlsx
+++ b/app_notas_uis.xlsx
@@ -19,6 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="10.0"/>
@@ -52,7 +55,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -66,6 +69,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -487,7 +493,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
         <v>2.1</v>
@@ -537,13 +546,13 @@
         <v>0</v>
       </c>
       <c r="S2" s="6"/>
-      <c r="T2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.615)</f>
-        <v>1.615</v>
-      </c>
-      <c r="U2" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5383333333333333)</f>
-        <v>0.5383333333</v>
+      <c r="T2" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.015)</f>
+        <v>2.015</v>
+      </c>
+      <c r="U2" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6716666666666667)</f>
+        <v>0.6716666667</v>
       </c>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
@@ -579,7 +588,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -629,13 +641,13 @@
         <v>5</v>
       </c>
       <c r="S3" s="6"/>
-      <c r="T3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.58)</f>
-        <v>2.58</v>
-      </c>
-      <c r="U3" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.86)</f>
-        <v>0.86</v>
+      <c r="T3" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.18)</f>
+        <v>3.18</v>
+      </c>
+      <c r="U3" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.06)</f>
+        <v>1.06</v>
       </c>
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
@@ -671,7 +683,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
       <c r="G4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -721,13 +736,13 @@
         <v>3.5</v>
       </c>
       <c r="S4" s="6"/>
-      <c r="T4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.325)</f>
-        <v>2.325</v>
-      </c>
-      <c r="U4" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.775)</f>
-        <v>0.775</v>
+      <c r="T4" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.905)</f>
+        <v>2.905</v>
+      </c>
+      <c r="U4" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9683333333333333)</f>
+        <v>0.9683333333</v>
       </c>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
@@ -763,7 +778,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -813,13 +831,13 @@
         <v>5</v>
       </c>
       <c r="S5" s="6"/>
-      <c r="T5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6399999999999997)</f>
-        <v>2.64</v>
-      </c>
-      <c r="U5" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8799999999999999)</f>
-        <v>0.88</v>
+      <c r="T5" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.24)</f>
+        <v>3.24</v>
+      </c>
+      <c r="U5" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
+        <v>1.08</v>
       </c>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
@@ -855,7 +873,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
       <c r="G6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -905,13 +926,13 @@
         <v>3.5</v>
       </c>
       <c r="S6" s="6"/>
-      <c r="T6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5300000000000002)</f>
-        <v>2.53</v>
-      </c>
-      <c r="U6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8433333333333334)</f>
-        <v>0.8433333333</v>
+      <c r="T6" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1100000000000003)</f>
+        <v>3.11</v>
+      </c>
+      <c r="U6" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0366666666666668)</f>
+        <v>1.036666667</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
@@ -947,7 +968,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="G7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -997,13 +1021,13 @@
         <v>5</v>
       </c>
       <c r="S7" s="6"/>
-      <c r="T7" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0100000000000002)</f>
-        <v>2.01</v>
-      </c>
-      <c r="U7" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.67)</f>
-        <v>0.67</v>
+      <c r="T7" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5100000000000002)</f>
+        <v>2.51</v>
+      </c>
+      <c r="U7" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8366666666666668)</f>
+        <v>0.8366666667</v>
       </c>
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
@@ -1039,7 +1063,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="F8" s="6"/>
+      <c r="F8" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -1089,13 +1116,13 @@
         <v>5</v>
       </c>
       <c r="S8" s="6"/>
-      <c r="T8" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.975)</f>
-        <v>1.975</v>
-      </c>
-      <c r="U8" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6583333333333333)</f>
-        <v>0.6583333333</v>
+      <c r="T8" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.575)</f>
+        <v>2.575</v>
+      </c>
+      <c r="U8" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8583333333333334)</f>
+        <v>0.8583333333</v>
       </c>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
@@ -1131,7 +1158,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -1181,13 +1211,13 @@
         <v>5</v>
       </c>
       <c r="S9" s="6"/>
-      <c r="T9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.665)</f>
-        <v>2.665</v>
-      </c>
-      <c r="U9" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8883333333333333)</f>
-        <v>0.8883333333</v>
+      <c r="T9" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2649999999999997)</f>
+        <v>3.265</v>
+      </c>
+      <c r="U9" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0883333333333332)</f>
+        <v>1.088333333</v>
       </c>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
@@ -1223,7 +1253,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="6"/>
+      <c r="F10" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -1273,13 +1306,13 @@
         <v>5</v>
       </c>
       <c r="S10" s="6"/>
-      <c r="T10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.74)</f>
-        <v>2.74</v>
-      </c>
-      <c r="U10" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9133333333333334)</f>
-        <v>0.9133333333</v>
+      <c r="T10" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.34)</f>
+        <v>3.34</v>
+      </c>
+      <c r="U10" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1133333333333333)</f>
+        <v>1.113333333</v>
       </c>
       <c r="V10" s="6"/>
       <c r="W10" s="6"/>
@@ -1315,7 +1348,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -1365,13 +1401,13 @@
         <v>4.5</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="T11" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.48)</f>
-        <v>2.48</v>
-      </c>
-      <c r="U11" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8266666666666667)</f>
-        <v>0.8266666667</v>
+      <c r="T11" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.08)</f>
+        <v>3.08</v>
+      </c>
+      <c r="U11" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0266666666666666)</f>
+        <v>1.026666667</v>
       </c>
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
@@ -1407,7 +1443,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F12" s="6"/>
+      <c r="F12" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
         <v>3.1</v>
@@ -1457,13 +1496,13 @@
         <v>4.5</v>
       </c>
       <c r="S12" s="6"/>
-      <c r="T12" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3200000000000003)</f>
-        <v>2.32</v>
-      </c>
-      <c r="U12" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7733333333333334)</f>
-        <v>0.7733333333</v>
+      <c r="T12" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.92)</f>
+        <v>2.92</v>
+      </c>
+      <c r="U12" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9733333333333333)</f>
+        <v>0.9733333333</v>
       </c>
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
@@ -1499,7 +1538,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
         <v>2.1</v>
@@ -1549,13 +1591,13 @@
         <v>5</v>
       </c>
       <c r="S13" s="6"/>
-      <c r="T13" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.865)</f>
-        <v>0.865</v>
-      </c>
-      <c r="U13" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.28833333333333333)</f>
-        <v>0.2883333333</v>
+      <c r="T13" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4649999999999999)</f>
+        <v>1.465</v>
+      </c>
+      <c r="U13" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4883333333333333)</f>
+        <v>0.4883333333</v>
       </c>
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
@@ -1591,7 +1633,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
         <v>2.3</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -1641,13 +1686,13 @@
         <v>5</v>
       </c>
       <c r="S14" s="6"/>
-      <c r="T14" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.175)</f>
-        <v>3.175</v>
-      </c>
-      <c r="U14" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0583333333333333)</f>
-        <v>1.058333333</v>
+      <c r="T14" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7750000000000004)</f>
+        <v>3.775</v>
+      </c>
+      <c r="U14" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2583333333333335)</f>
+        <v>1.258333333</v>
       </c>
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
@@ -1683,7 +1728,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -1730,13 +1778,13 @@
         <v>0</v>
       </c>
       <c r="S15" s="6"/>
-      <c r="T15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
-      </c>
-      <c r="U15" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8666666666666667)</f>
-        <v>0.8666666667</v>
+      <c r="T15" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="U15" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
@@ -1772,7 +1820,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="G16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
@@ -1822,13 +1873,13 @@
         <v>5</v>
       </c>
       <c r="S16" s="6"/>
-      <c r="T16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.76)</f>
-        <v>2.76</v>
-      </c>
-      <c r="U16" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9199999999999999)</f>
-        <v>0.92</v>
+      <c r="T16" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.26)</f>
+        <v>3.26</v>
+      </c>
+      <c r="U16" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0866666666666667)</f>
+        <v>1.086666667</v>
       </c>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
@@ -1864,7 +1915,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -1914,13 +1968,13 @@
         <v>5</v>
       </c>
       <c r="S17" s="6"/>
-      <c r="T17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.245)</f>
-        <v>2.245</v>
-      </c>
-      <c r="U17" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7483333333333334)</f>
-        <v>0.7483333333</v>
+      <c r="T17" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8449999999999998)</f>
+        <v>2.845</v>
+      </c>
+      <c r="U17" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9483333333333333)</f>
+        <v>0.9483333333</v>
       </c>
       <c r="V17" s="6"/>
       <c r="W17" s="6"/>
@@ -1956,7 +2010,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -2006,13 +2063,13 @@
         <v>5</v>
       </c>
       <c r="S18" s="6"/>
-      <c r="T18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.865)</f>
-        <v>2.865</v>
-      </c>
-      <c r="U18" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9550000000000001)</f>
-        <v>0.955</v>
+      <c r="T18" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.465)</f>
+        <v>3.465</v>
+      </c>
+      <c r="U18" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.155)</f>
+        <v>1.155</v>
       </c>
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
@@ -2048,7 +2105,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -2098,13 +2158,13 @@
         <v>5</v>
       </c>
       <c r="S19" s="6"/>
-      <c r="T19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.43)</f>
-        <v>2.43</v>
-      </c>
-      <c r="U19" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.81)</f>
-        <v>0.81</v>
+      <c r="T19" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.03)</f>
+        <v>3.03</v>
+      </c>
+      <c r="U19" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
+        <v>1.01</v>
       </c>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
@@ -2140,7 +2200,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F20" s="6"/>
+      <c r="F20" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
@@ -2190,13 +2253,13 @@
         <v>5</v>
       </c>
       <c r="S20" s="6"/>
-      <c r="T20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.225)</f>
-        <v>3.225</v>
-      </c>
-      <c r="U20" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.075)</f>
-        <v>1.075</v>
+      <c r="T20" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.825)</f>
+        <v>3.825</v>
+      </c>
+      <c r="U20" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2750000000000001)</f>
+        <v>1.275</v>
       </c>
       <c r="V20" s="6"/>
       <c r="W20" s="6"/>
@@ -2232,7 +2295,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -2282,13 +2348,13 @@
         <v>5</v>
       </c>
       <c r="S21" s="6"/>
-      <c r="T21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.965)</f>
-        <v>2.965</v>
-      </c>
-      <c r="U21" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9883333333333333)</f>
-        <v>0.9883333333</v>
+      <c r="T21" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5649999999999995)</f>
+        <v>3.565</v>
+      </c>
+      <c r="U21" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1883333333333332)</f>
+        <v>1.188333333</v>
       </c>
       <c r="V21" s="6"/>
       <c r="W21" s="6"/>
@@ -2324,7 +2390,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F22" s="6"/>
+      <c r="F22" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -2374,13 +2443,13 @@
         <v>5</v>
       </c>
       <c r="S22" s="6"/>
-      <c r="T22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3649999999999998)</f>
-        <v>2.365</v>
-      </c>
-      <c r="U22" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7883333333333332)</f>
-        <v>0.7883333333</v>
+      <c r="T22" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.965)</f>
+        <v>2.965</v>
+      </c>
+      <c r="U22" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9883333333333333)</f>
+        <v>0.9883333333</v>
       </c>
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
@@ -2416,7 +2485,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F23" s="6"/>
+      <c r="F23" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -2466,13 +2538,13 @@
         <v>5</v>
       </c>
       <c r="S23" s="6"/>
-      <c r="T23" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3249999999999997)</f>
-        <v>2.325</v>
-      </c>
-      <c r="U23" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7749999999999999)</f>
-        <v>0.775</v>
+      <c r="T23" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.925)</f>
+        <v>2.925</v>
+      </c>
+      <c r="U23" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.975)</f>
+        <v>0.975</v>
       </c>
       <c r="V23" s="6"/>
       <c r="W23" s="6"/>
@@ -2508,7 +2580,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F24" s="6"/>
+      <c r="F24" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -2558,13 +2633,13 @@
         <v>5</v>
       </c>
       <c r="S24" s="6"/>
-      <c r="T24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="U24" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7666666666666666)</f>
-        <v>0.7666666667</v>
+      <c r="T24" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9000000000000004)</f>
+        <v>2.9</v>
+      </c>
+      <c r="U24" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9666666666666668)</f>
+        <v>0.9666666667</v>
       </c>
       <c r="V24" s="6"/>
       <c r="W24" s="6"/>
@@ -2600,7 +2675,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
         <v>1.4</v>
       </c>
-      <c r="F25" s="6"/>
+      <c r="F25" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -2650,13 +2728,13 @@
         <v>5</v>
       </c>
       <c r="S25" s="6"/>
-      <c r="T25" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.055)</f>
-        <v>3.055</v>
-      </c>
-      <c r="U25" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0183333333333333)</f>
-        <v>1.018333333</v>
+      <c r="T25" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6550000000000002)</f>
+        <v>3.655</v>
+      </c>
+      <c r="U25" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2183333333333335)</f>
+        <v>1.218333333</v>
       </c>
       <c r="V25" s="6"/>
       <c r="W25" s="6"/>
@@ -2692,7 +2770,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
         <v>1.4</v>
       </c>
-      <c r="F26" s="6"/>
+      <c r="F26" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
         <v>3.9</v>
@@ -2742,13 +2823,13 @@
         <v>5</v>
       </c>
       <c r="S26" s="6"/>
-      <c r="T26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.615)</f>
-        <v>2.615</v>
-      </c>
-      <c r="U26" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8716666666666667)</f>
-        <v>0.8716666667</v>
+      <c r="T26" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2150000000000003)</f>
+        <v>3.215</v>
+      </c>
+      <c r="U26" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0716666666666668)</f>
+        <v>1.071666667</v>
       </c>
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
@@ -2784,7 +2865,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="F27" s="6"/>
+      <c r="F27" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -2834,13 +2918,13 @@
         <v>5</v>
       </c>
       <c r="S27" s="6"/>
-      <c r="T27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5250000000000004)</f>
-        <v>2.525</v>
-      </c>
-      <c r="U27" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8416666666666668)</f>
-        <v>0.8416666667</v>
+      <c r="T27" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.125)</f>
+        <v>3.125</v>
+      </c>
+      <c r="U27" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0416666666666667)</f>
+        <v>1.041666667</v>
       </c>
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
@@ -2876,7 +2960,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F28" s="6"/>
+      <c r="F28" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -2926,13 +3013,13 @@
         <v>5</v>
       </c>
       <c r="S28" s="6"/>
-      <c r="T28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.045)</f>
-        <v>2.045</v>
-      </c>
-      <c r="U28" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6816666666666666)</f>
-        <v>0.6816666667</v>
+      <c r="T28" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.645)</f>
+        <v>2.645</v>
+      </c>
+      <c r="U28" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8816666666666667)</f>
+        <v>0.8816666667</v>
       </c>
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
@@ -2968,7 +3055,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F29" s="6"/>
+      <c r="F29" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -3018,13 +3108,13 @@
         <v>5</v>
       </c>
       <c r="S29" s="6"/>
-      <c r="T29" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.74)</f>
-        <v>2.74</v>
-      </c>
-      <c r="U29" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9133333333333334)</f>
-        <v>0.9133333333</v>
+      <c r="T29" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.34)</f>
+        <v>3.34</v>
+      </c>
+      <c r="U29" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1133333333333333)</f>
+        <v>1.113333333</v>
       </c>
       <c r="V29" s="6"/>
       <c r="W29" s="6"/>
@@ -3113,11 +3203,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="9" t="str">
+      <c r="H1" s="10" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(10%)")</f>
         <v>TUTORIAS(10%)</v>
       </c>
-      <c r="I1" s="9" t="str">
+      <c r="I1" s="10" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu(20%)")</f>
         <v>PQT+Tu(20%)</v>
       </c>
@@ -3149,7 +3239,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr4")</f>
         <v>Tr4</v>
       </c>
-      <c r="Q1" s="1"/>
+      <c r="Q1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta2")</f>
+        <v>Ta2</v>
+      </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
@@ -3196,15 +3289,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
-      </c>
-      <c r="H2" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -3226,26 +3325,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O2" s="6"/>
+      <c r="O2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="P2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
-      <c r="S2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.395)</f>
-        <v>3.395</v>
-      </c>
-      <c r="T2" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1316666666666666)</f>
-        <v>1.131666667</v>
+      <c r="S2" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4350000000000005)</f>
+        <v>4.435</v>
+      </c>
+      <c r="T2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4783333333333335)</f>
+        <v>1.478333333</v>
       </c>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
       <c r="W2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X2" s="6"/>
       <c r="Y2" s="6">
@@ -3275,15 +3377,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
-      </c>
-      <c r="H3" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3305,20 +3413,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O3" s="6"/>
+      <c r="O3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
-      <c r="S3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
-        <v>3.98</v>
-      </c>
-      <c r="T3" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3266666666666667)</f>
-        <v>1.326666667</v>
+      <c r="S3" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6666666666666667)</f>
+        <v>1.666666667</v>
       </c>
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
@@ -3354,15 +3465,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
-      </c>
-      <c r="H4" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3384,20 +3501,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O4" s="6"/>
+      <c r="O4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.98)</f>
-        <v>3.98</v>
-      </c>
-      <c r="T4" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3266666666666667)</f>
-        <v>1.326666667</v>
+      <c r="S4" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6666666666666667)</f>
+        <v>1.666666667</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -3433,15 +3553,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
         <v>3.9</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="G5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="H5" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="H5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="J5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -3463,26 +3589,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="6"/>
+      <c r="O5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
+        <v>3.33</v>
+      </c>
       <c r="P5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.455)</f>
-        <v>2.455</v>
-      </c>
-      <c r="T5" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8183333333333334)</f>
-        <v>0.8183333333</v>
+      <c r="S5" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.575)</f>
+        <v>3.575</v>
+      </c>
+      <c r="T5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1916666666666667)</f>
+        <v>1.191666667</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
       <c r="W5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="X5" s="6"/>
       <c r="Y5" s="6">
@@ -3512,15 +3641,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="G6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="H6" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="H6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
-        <v>1.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="J6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3542,26 +3677,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="6"/>
+      <c r="O6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.75)</f>
+        <v>1.75</v>
+      </c>
       <c r="P6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.85)</f>
-        <v>2.85</v>
-      </c>
-      <c r="T6" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9500000000000001)</f>
-        <v>0.95</v>
+      <c r="S6" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.91)</f>
+        <v>3.91</v>
+      </c>
+      <c r="T6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3033333333333335)</f>
+        <v>1.303333333</v>
       </c>
       <c r="U6" s="6"/>
       <c r="V6" s="6"/>
       <c r="W6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="X6" s="6"/>
       <c r="Y6" s="6">
@@ -3591,15 +3729,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3621,26 +3765,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O7" s="6"/>
+      <c r="O7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.62)</f>
+        <v>4.62</v>
+      </c>
       <c r="P7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
-      <c r="S7" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.875)</f>
-        <v>3.875</v>
-      </c>
-      <c r="T7" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2916666666666667)</f>
-        <v>1.291666667</v>
+      <c r="S7" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.875)</f>
+        <v>4.875</v>
+      </c>
+      <c r="T7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.625)</f>
+        <v>1.625</v>
       </c>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
       <c r="W7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="X7" s="6"/>
       <c r="Y7" s="6">
@@ -3670,15 +3817,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F8" s="6"/>
+      <c r="F8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
-      </c>
-      <c r="H8" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3700,26 +3853,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O8" s="6"/>
+      <c r="O8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
-      <c r="S8" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.465)</f>
-        <v>3.465</v>
-      </c>
-      <c r="T8" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.155)</f>
-        <v>1.155</v>
+      <c r="S8" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.565)</f>
+        <v>4.565</v>
+      </c>
+      <c r="T8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5216666666666667)</f>
+        <v>1.521666667</v>
       </c>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="X8" s="6"/>
       <c r="Y8" s="6">
@@ -3749,15 +3905,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="H9" s="6"/>
+      <c r="H9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -3779,26 +3941,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O9" s="6"/>
+      <c r="O9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
+        <v>3.33</v>
+      </c>
       <c r="P9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
-      <c r="S9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.46)</f>
-        <v>3.46</v>
-      </c>
-      <c r="T9" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1533333333333333)</f>
-        <v>1.153333333</v>
+      <c r="S9" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.86)</f>
+        <v>3.86</v>
+      </c>
+      <c r="T9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2866666666666666)</f>
+        <v>1.286666667</v>
       </c>
       <c r="U9" s="6"/>
       <c r="V9" s="6"/>
       <c r="W9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X9" s="6"/>
       <c r="Y9" s="6">
@@ -3828,15 +3993,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F10" s="6"/>
+      <c r="F10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H10" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -3858,26 +4029,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O10" s="6"/>
+      <c r="O10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
-      <c r="S10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
-        <v>3.9</v>
-      </c>
-      <c r="T10" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
-        <v>1.3</v>
+      <c r="S10" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.96)</f>
+        <v>4.96</v>
+      </c>
+      <c r="T10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6533333333333333)</f>
+        <v>1.653333333</v>
       </c>
       <c r="U10" s="6"/>
       <c r="V10" s="6"/>
       <c r="W10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X10" s="6"/>
       <c r="Y10" s="6">
@@ -3907,15 +4081,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="H11" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -3937,26 +4117,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O11" s="6"/>
+      <c r="O11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.17)</f>
+        <v>4.17</v>
+      </c>
       <c r="P11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
-      <c r="S11" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.71)</f>
-        <v>3.71</v>
-      </c>
-      <c r="T11" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2366666666666666)</f>
-        <v>1.236666667</v>
+      <c r="S11" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.73)</f>
+        <v>4.73</v>
+      </c>
+      <c r="T11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5766666666666669)</f>
+        <v>1.576666667</v>
       </c>
       <c r="U11" s="6"/>
       <c r="V11" s="6"/>
       <c r="W11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X11" s="6"/>
       <c r="Y11" s="6">
@@ -3986,15 +4169,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="F12" s="6"/>
+      <c r="F12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4016,26 +4205,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O12" s="6"/>
+      <c r="O12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.55)</f>
+        <v>4.55</v>
+      </c>
       <c r="P12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
-      <c r="S12" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.855)</f>
-        <v>3.855</v>
-      </c>
-      <c r="T12" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.285)</f>
-        <v>1.285</v>
+      <c r="S12" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.855)</f>
+        <v>4.855</v>
+      </c>
+      <c r="T12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6183333333333334)</f>
+        <v>1.618333333</v>
       </c>
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
       <c r="W12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="X12" s="6"/>
       <c r="Y12" s="6">
@@ -4065,15 +4257,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="G13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4095,20 +4293,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
-      <c r="S13" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
-      </c>
-      <c r="T13" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2666666666666666)</f>
-        <v>1.266666667</v>
+      <c r="S13" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="T13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5666666666666667)</f>
+        <v>1.566666667</v>
       </c>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
@@ -4144,15 +4345,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="H14" s="6"/>
+      <c r="H14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4174,26 +4381,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O14" s="6"/>
+      <c r="O14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.55)</f>
+        <v>4.55</v>
+      </c>
       <c r="P14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
-      <c r="S14" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.975)</f>
-        <v>3.975</v>
-      </c>
-      <c r="T14" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.325)</f>
-        <v>1.325</v>
+      <c r="S14" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.975)</f>
+        <v>4.975</v>
+      </c>
+      <c r="T14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6583333333333332)</f>
+        <v>1.658333333</v>
       </c>
       <c r="U14" s="6"/>
       <c r="V14" s="6"/>
       <c r="W14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="X14" s="6"/>
       <c r="Y14" s="6">
@@ -4223,15 +4433,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
-      </c>
-      <c r="H15" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="H15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="J15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4253,26 +4469,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O15" s="6"/>
+      <c r="O15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
-      <c r="S15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.64)</f>
-        <v>3.64</v>
-      </c>
-      <c r="T15" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2133333333333334)</f>
-        <v>1.213333333</v>
+      <c r="S15" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.840000000000001)</f>
+        <v>4.84</v>
+      </c>
+      <c r="T15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6133333333333335)</f>
+        <v>1.613333333</v>
       </c>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="X15" s="6"/>
       <c r="Y15" s="6">
@@ -4302,15 +4521,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
-      </c>
-      <c r="H16" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
+      <c r="H16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="J16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4332,20 +4557,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O16" s="6"/>
+      <c r="O16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="P16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
-      <c r="S16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.815)</f>
-        <v>2.815</v>
-      </c>
-      <c r="T16" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9383333333333334)</f>
-        <v>0.9383333333</v>
+      <c r="S16" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.995)</f>
+        <v>3.995</v>
+      </c>
+      <c r="T16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3316666666666668)</f>
+        <v>1.331666667</v>
       </c>
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
@@ -4381,15 +4609,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="G17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H17" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="H17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="J17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -4411,26 +4645,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O17" s="6"/>
+      <c r="O17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
+      </c>
       <c r="P17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
-      <c r="S17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.15)</f>
-        <v>3.15</v>
-      </c>
-      <c r="T17" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.05)</f>
-        <v>1.05</v>
+      <c r="S17" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.63)</f>
+        <v>3.63</v>
+      </c>
+      <c r="T17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.21)</f>
+        <v>1.21</v>
       </c>
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
       <c r="W17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="X17" s="6"/>
       <c r="Y17" s="6">
@@ -4460,15 +4697,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="G18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4490,26 +4733,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O18" s="6"/>
+      <c r="O18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.63)</f>
+        <v>3.63</v>
+      </c>
       <c r="P18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
-      <c r="S18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.855)</f>
-        <v>3.855</v>
-      </c>
-      <c r="T18" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.285)</f>
-        <v>1.285</v>
+      <c r="S18" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.655)</f>
+        <v>4.655</v>
+      </c>
+      <c r="T18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5516666666666667)</f>
+        <v>1.551666667</v>
       </c>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
       <c r="W18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X18" s="6"/>
       <c r="Y18" s="6">
@@ -4539,15 +4785,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H19" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -4569,20 +4821,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O19" s="6"/>
+      <c r="O19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
-      <c r="S19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.69)</f>
-        <v>3.69</v>
-      </c>
-      <c r="T19" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.23)</f>
-        <v>1.23</v>
+      <c r="S19" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.73)</f>
+        <v>4.73</v>
+      </c>
+      <c r="T19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5766666666666669)</f>
+        <v>1.576666667</v>
       </c>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
@@ -4618,15 +4873,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F20" s="6"/>
+      <c r="F20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
-      </c>
-      <c r="H20" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4648,26 +4909,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O20" s="6"/>
+      <c r="O20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
-      <c r="S20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.415)</f>
-        <v>3.415</v>
-      </c>
-      <c r="T20" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1383333333333334)</f>
-        <v>1.138333333</v>
+      <c r="S20" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.115)</f>
+        <v>4.115</v>
+      </c>
+      <c r="T20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3716666666666668)</f>
+        <v>1.371666667</v>
       </c>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="X20" s="6"/>
       <c r="Y20" s="6">
@@ -4697,15 +4961,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="G21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4727,26 +4997,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O21" s="6"/>
+      <c r="O21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.17)</f>
+        <v>4.17</v>
+      </c>
       <c r="P21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
-      <c r="S21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8299999999999996)</f>
-        <v>3.83</v>
-      </c>
-      <c r="T21" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2766666666666666)</f>
-        <v>1.276666667</v>
+      <c r="S21" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.630000000000001)</f>
+        <v>4.63</v>
+      </c>
+      <c r="T21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5433333333333337)</f>
+        <v>1.543333333</v>
       </c>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="W21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="6">
@@ -4776,15 +5049,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
-      <c r="F22" s="6"/>
+      <c r="F22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
-      </c>
-      <c r="H22" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="H22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="J22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4806,26 +5085,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O22" s="6"/>
+      <c r="O22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.85)</f>
+        <v>3.85</v>
+      </c>
       <c r="P22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
-      <c r="S22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.805)</f>
-        <v>2.805</v>
-      </c>
-      <c r="T22" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.935)</f>
-        <v>0.935</v>
+      <c r="S22" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6050000000000004)</f>
+        <v>3.605</v>
+      </c>
+      <c r="T22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2016666666666669)</f>
+        <v>1.201666667</v>
       </c>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="X22" s="6"/>
       <c r="Y22" s="6">
@@ -4855,15 +5137,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F23" s="6"/>
+      <c r="F23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="H23" s="6"/>
+      <c r="H23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4885,26 +5173,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O23" s="6"/>
+      <c r="O23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
+        <v>3.33</v>
+      </c>
       <c r="P23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
-      <c r="S23" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.71)</f>
-        <v>3.71</v>
-      </c>
-      <c r="T23" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2366666666666666)</f>
-        <v>1.236666667</v>
+      <c r="S23" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.71)</f>
+        <v>4.71</v>
+      </c>
+      <c r="T23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.57)</f>
+        <v>1.57</v>
       </c>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
       <c r="W23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X23" s="6"/>
       <c r="Y23" s="6">
@@ -4934,15 +5225,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F24" s="6"/>
+      <c r="F24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="H24" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -4964,26 +5261,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O24" s="6"/>
+      <c r="O24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.62)</f>
+        <v>4.62</v>
+      </c>
       <c r="P24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.96)</f>
-        <v>3.96</v>
-      </c>
-      <c r="T24" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.32)</f>
-        <v>1.32</v>
+      <c r="S24" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.98)</f>
+        <v>4.98</v>
+      </c>
+      <c r="T24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6600000000000001)</f>
+        <v>1.66</v>
       </c>
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
       <c r="W24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="X24" s="6"/>
       <c r="Y24" s="6">
@@ -5013,15 +5313,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F25" s="6"/>
+      <c r="F25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -5043,20 +5349,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O25" s="6"/>
+      <c r="O25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q25" s="6"/>
       <c r="R25" s="6"/>
-      <c r="S25" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="T25" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3333333333333333)</f>
-        <v>1.333333333</v>
+      <c r="S25" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T25" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6666666666666667)</f>
+        <v>1.666666667</v>
       </c>
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
@@ -5092,15 +5401,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="F26" s="6"/>
+      <c r="F26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="G26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
-      </c>
-      <c r="H26" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5122,26 +5437,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O26" s="6"/>
+      <c r="O26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
+        <v>3.33</v>
+      </c>
       <c r="P26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
-      <c r="S26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6450000000000005)</f>
-        <v>2.645</v>
-      </c>
-      <c r="T26" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8816666666666668)</f>
-        <v>0.8816666667</v>
+      <c r="S26" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.205)</f>
+        <v>3.205</v>
+      </c>
+      <c r="T26" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0683333333333334)</f>
+        <v>1.068333333</v>
       </c>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
       <c r="W26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="X26" s="6"/>
       <c r="Y26" s="6">
@@ -5171,15 +5489,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
         <v>3.6</v>
       </c>
-      <c r="F27" s="6"/>
+      <c r="F27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="G27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
-        <v>3.7</v>
-      </c>
-      <c r="H27" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="J27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -5201,26 +5525,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O27" s="6"/>
+      <c r="O27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q27" s="6"/>
       <c r="R27" s="6"/>
-      <c r="S27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4600000000000004)</f>
-        <v>3.46</v>
-      </c>
-      <c r="T27" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1533333333333335)</f>
-        <v>1.153333333</v>
+      <c r="S27" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5200000000000005)</f>
+        <v>4.52</v>
+      </c>
+      <c r="T27" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5066666666666668)</f>
+        <v>1.506666667</v>
       </c>
       <c r="U27" s="6"/>
       <c r="V27" s="6"/>
       <c r="W27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
-        <v>3.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="X27" s="6"/>
       <c r="Y27" s="6">
@@ -5250,15 +5577,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F28" s="6"/>
+      <c r="F28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="G28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
-      </c>
-      <c r="H28" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="H28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="I28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="J28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -5280,26 +5613,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O28" s="6"/>
+      <c r="O28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
-      <c r="S28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.605)</f>
-        <v>3.605</v>
-      </c>
-      <c r="T28" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2016666666666667)</f>
-        <v>1.201666667</v>
+      <c r="S28" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.365)</f>
+        <v>4.365</v>
+      </c>
+      <c r="T28" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.455)</f>
+        <v>1.455</v>
       </c>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="X28" s="6"/>
       <c r="Y28" s="6">
@@ -5329,15 +5665,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="F29" s="6"/>
+      <c r="F29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="G29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
-      </c>
-      <c r="H29" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -5359,26 +5701,29 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O29" s="6"/>
+      <c r="O29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
+        <v>3.33</v>
+      </c>
       <c r="P29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="Q29" s="6"/>
       <c r="R29" s="6"/>
-      <c r="S29" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
-        <v>3.9</v>
-      </c>
-      <c r="T29" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
-        <v>1.3</v>
+      <c r="S29" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.82)</f>
+        <v>4.82</v>
+      </c>
+      <c r="T29" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6066666666666667)</f>
+        <v>1.606666667</v>
       </c>
       <c r="U29" s="6"/>
       <c r="V29" s="6"/>
       <c r="W29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X29" s="6"/>
       <c r="Y29" s="6">
@@ -5462,11 +5807,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="9" t="str">
+      <c r="H1" s="10" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(8%)")</f>
         <v>TUTORIAS(8%)</v>
       </c>
-      <c r="I1" s="9" t="str">
+      <c r="I1" s="10" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu")</f>
         <v>PQT+Tu</v>
       </c>
@@ -5565,7 +5910,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
@@ -5616,13 +5964,13 @@
         <v>5</v>
       </c>
       <c r="T2" s="6"/>
-      <c r="U2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2349999999999994)</f>
-        <v>3.235</v>
-      </c>
-      <c r="V2" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0783333333333331)</f>
-        <v>1.078333333</v>
+      <c r="U2" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5349999999999993)</f>
+        <v>3.535</v>
+      </c>
+      <c r="V2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.178333333333333)</f>
+        <v>1.178333333</v>
       </c>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
@@ -5667,7 +6015,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -5718,13 +6069,13 @@
         <v>5</v>
       </c>
       <c r="T3" s="6"/>
-      <c r="U3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9299999999999997)</f>
-        <v>2.93</v>
-      </c>
-      <c r="V3" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9766666666666666)</f>
-        <v>0.9766666667</v>
+      <c r="U3" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2300000000000004)</f>
+        <v>3.23</v>
+      </c>
+      <c r="V3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0766666666666669)</f>
+        <v>1.076666667</v>
       </c>
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
@@ -5769,7 +6120,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -5820,13 +6174,13 @@
         <v>5</v>
       </c>
       <c r="T4" s="6"/>
-      <c r="U4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0149999999999997)</f>
-        <v>3.015</v>
-      </c>
-      <c r="V4" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.005)</f>
-        <v>1.005</v>
+      <c r="U4" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.315)</f>
+        <v>3.315</v>
+      </c>
+      <c r="V4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.105)</f>
+        <v>1.105</v>
       </c>
       <c r="W4" s="6"/>
       <c r="X4" s="6"/>
@@ -5871,7 +6225,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
@@ -5922,13 +6279,13 @@
         <v>5</v>
       </c>
       <c r="T5" s="6"/>
-      <c r="U5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.24)</f>
-        <v>2.24</v>
-      </c>
-      <c r="V5" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7466666666666667)</f>
-        <v>0.7466666667</v>
+      <c r="U5" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.54)</f>
+        <v>2.54</v>
+      </c>
+      <c r="V5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8466666666666667)</f>
+        <v>0.8466666667</v>
       </c>
       <c r="W5" s="6"/>
       <c r="X5" s="6"/>
@@ -5973,7 +6330,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="G6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
@@ -6024,13 +6384,13 @@
         <v>0</v>
       </c>
       <c r="T6" s="6"/>
-      <c r="U6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4300000000000002)</f>
-        <v>1.43</v>
-      </c>
-      <c r="V6" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.47666666666666674)</f>
-        <v>0.4766666667</v>
+      <c r="U6" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6300000000000001)</f>
+        <v>1.63</v>
+      </c>
+      <c r="V6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5433333333333333)</f>
+        <v>0.5433333333</v>
       </c>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
@@ -6075,7 +6435,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -6126,13 +6489,13 @@
         <v>5</v>
       </c>
       <c r="T7" s="6"/>
-      <c r="U7" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.27)</f>
-        <v>3.27</v>
-      </c>
-      <c r="V7" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.09)</f>
-        <v>1.09</v>
+      <c r="U7" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.57)</f>
+        <v>3.57</v>
+      </c>
+      <c r="V7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.19)</f>
+        <v>1.19</v>
       </c>
       <c r="W7" s="6"/>
       <c r="X7" s="6"/>
@@ -6177,7 +6540,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F8" s="6"/>
+      <c r="F8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
@@ -6228,13 +6594,13 @@
         <v>5</v>
       </c>
       <c r="T8" s="6"/>
-      <c r="U8" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.03)</f>
-        <v>3.03</v>
-      </c>
-      <c r="V8" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
-        <v>1.01</v>
+      <c r="U8" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3299999999999996)</f>
+        <v>3.33</v>
+      </c>
+      <c r="V8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1099999999999999)</f>
+        <v>1.11</v>
       </c>
       <c r="W8" s="6"/>
       <c r="X8" s="6"/>
@@ -6279,7 +6645,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
         <v>1.9</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -6330,13 +6699,13 @@
         <v>5</v>
       </c>
       <c r="T9" s="6"/>
-      <c r="U9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4099999999999997)</f>
-        <v>2.41</v>
-      </c>
-      <c r="V9" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8033333333333332)</f>
-        <v>0.8033333333</v>
+      <c r="U9" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.71)</f>
+        <v>2.71</v>
+      </c>
+      <c r="V9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9033333333333333)</f>
+        <v>0.9033333333</v>
       </c>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
@@ -6381,7 +6750,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F10" s="6"/>
+      <c r="F10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -6432,13 +6804,13 @@
         <v>5</v>
       </c>
       <c r="T10" s="6"/>
-      <c r="U10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.435)</f>
-        <v>3.435</v>
-      </c>
-      <c r="V10" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.145)</f>
-        <v>1.145</v>
+      <c r="U10" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.735)</f>
+        <v>3.735</v>
+      </c>
+      <c r="V10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2449999999999999)</f>
+        <v>1.245</v>
       </c>
       <c r="W10" s="6"/>
       <c r="X10" s="6"/>
@@ -6483,7 +6855,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -6534,13 +6909,13 @@
         <v>5</v>
       </c>
       <c r="T11" s="6"/>
-      <c r="U11" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.67)</f>
-        <v>2.67</v>
-      </c>
-      <c r="V11" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.89)</f>
-        <v>0.89</v>
+      <c r="U11" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9699999999999998)</f>
+        <v>2.97</v>
+      </c>
+      <c r="V11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9899999999999999)</f>
+        <v>0.99</v>
       </c>
       <c r="W11" s="6"/>
       <c r="X11" s="6"/>
@@ -6585,7 +6960,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
         <v>1.7</v>
       </c>
-      <c r="F12" s="6"/>
+      <c r="F12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -6636,13 +7014,13 @@
         <v>5</v>
       </c>
       <c r="T12" s="6"/>
-      <c r="U12" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.95)</f>
-        <v>2.95</v>
-      </c>
-      <c r="V12" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9833333333333334)</f>
-        <v>0.9833333333</v>
+      <c r="U12" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.25)</f>
+        <v>3.25</v>
+      </c>
+      <c r="V12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0833333333333333)</f>
+        <v>1.083333333</v>
       </c>
       <c r="W12" s="6"/>
       <c r="X12" s="6"/>
@@ -6687,7 +7065,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -6738,13 +7119,13 @@
         <v>5</v>
       </c>
       <c r="T13" s="6"/>
-      <c r="U13" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2950000000000004)</f>
-        <v>3.295</v>
-      </c>
-      <c r="V13" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0983333333333334)</f>
-        <v>1.098333333</v>
+      <c r="U13" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.595)</f>
+        <v>3.595</v>
+      </c>
+      <c r="V13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1983333333333335)</f>
+        <v>1.198333333</v>
       </c>
       <c r="W13" s="6"/>
       <c r="X13" s="6"/>
@@ -6789,7 +7170,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
@@ -6840,13 +7224,13 @@
         <v>5</v>
       </c>
       <c r="T14" s="6"/>
-      <c r="U14" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.085)</f>
-        <v>2.085</v>
-      </c>
-      <c r="V14" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.695)</f>
-        <v>0.695</v>
+      <c r="U14" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.385)</f>
+        <v>2.385</v>
+      </c>
+      <c r="V14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7949999999999999)</f>
+        <v>0.795</v>
       </c>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
@@ -6918,11 +7302,11 @@
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
-      <c r="U15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="V15" s="10">
+      <c r="U15" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="V15" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -6966,7 +7350,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
@@ -7017,13 +7404,13 @@
         <v>5</v>
       </c>
       <c r="T16" s="6"/>
-      <c r="U16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.43)</f>
-        <v>2.43</v>
-      </c>
-      <c r="V16" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.81)</f>
-        <v>0.81</v>
+      <c r="U16" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.73)</f>
+        <v>2.73</v>
+      </c>
+      <c r="V16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.91)</f>
+        <v>0.91</v>
       </c>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
@@ -7068,7 +7455,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -7119,13 +7509,13 @@
         <v>5</v>
       </c>
       <c r="T17" s="6"/>
-      <c r="U17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.575)</f>
-        <v>2.575</v>
-      </c>
-      <c r="V17" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8583333333333334)</f>
-        <v>0.8583333333</v>
+      <c r="U17" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.875)</f>
+        <v>2.875</v>
+      </c>
+      <c r="V17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9583333333333334)</f>
+        <v>0.9583333333</v>
       </c>
       <c r="W17" s="6"/>
       <c r="X17" s="6"/>
@@ -7170,7 +7560,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="G18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
@@ -7221,13 +7614,13 @@
         <v>0</v>
       </c>
       <c r="T18" s="6"/>
-      <c r="U18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.775)</f>
-        <v>1.775</v>
-      </c>
-      <c r="V18" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5916666666666667)</f>
-        <v>0.5916666667</v>
+      <c r="U18" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.975)</f>
+        <v>1.975</v>
+      </c>
+      <c r="V18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6583333333333333)</f>
+        <v>0.6583333333</v>
       </c>
       <c r="W18" s="6"/>
       <c r="X18" s="6"/>
@@ -7272,7 +7665,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -7323,13 +7719,13 @@
         <v>5</v>
       </c>
       <c r="T19" s="6"/>
-      <c r="U19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7300000000000004)</f>
-        <v>2.73</v>
-      </c>
-      <c r="V19" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9100000000000001)</f>
-        <v>0.91</v>
+      <c r="U19" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0300000000000002)</f>
+        <v>3.03</v>
+      </c>
+      <c r="V19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
+        <v>1.01</v>
       </c>
       <c r="W19" s="6"/>
       <c r="X19" s="6"/>
@@ -7374,7 +7770,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="F20" s="6"/>
+      <c r="F20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="G20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -7425,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="T20" s="6"/>
-      <c r="U20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6249999999999996)</f>
-        <v>3.625</v>
-      </c>
-      <c r="V20" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2083333333333333)</f>
-        <v>1.208333333</v>
+      <c r="U20" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8249999999999997)</f>
+        <v>3.825</v>
+      </c>
+      <c r="V20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.275)</f>
+        <v>1.275</v>
       </c>
       <c r="W20" s="6"/>
       <c r="X20" s="6"/>
@@ -7476,7 +7875,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -7527,13 +7929,13 @@
         <v>5</v>
       </c>
       <c r="T21" s="6"/>
-      <c r="U21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8449999999999998)</f>
-        <v>2.845</v>
-      </c>
-      <c r="V21" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9483333333333333)</f>
-        <v>0.9483333333</v>
+      <c r="U21" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1450000000000005)</f>
+        <v>3.145</v>
+      </c>
+      <c r="V21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0483333333333336)</f>
+        <v>1.048333333</v>
       </c>
       <c r="W21" s="6"/>
       <c r="X21" s="6"/>
@@ -7578,7 +7980,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F22" s="6"/>
+      <c r="F22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -7629,13 +8034,13 @@
         <v>5</v>
       </c>
       <c r="T22" s="6"/>
-      <c r="U22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.17)</f>
-        <v>3.17</v>
-      </c>
-      <c r="V22" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0566666666666666)</f>
-        <v>1.056666667</v>
+      <c r="U22" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.47)</f>
+        <v>3.47</v>
+      </c>
+      <c r="V22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1566666666666667)</f>
+        <v>1.156666667</v>
       </c>
       <c r="W22" s="6"/>
       <c r="X22" s="6"/>
@@ -7680,7 +8085,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="F23" s="6"/>
+      <c r="F23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -7731,13 +8139,13 @@
         <v>5</v>
       </c>
       <c r="T23" s="6"/>
-      <c r="U23" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2600000000000002)</f>
-        <v>3.26</v>
-      </c>
-      <c r="V23" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0866666666666667)</f>
-        <v>1.086666667</v>
+      <c r="U23" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.56)</f>
+        <v>3.56</v>
+      </c>
+      <c r="V23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1866666666666668)</f>
+        <v>1.186666667</v>
       </c>
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
@@ -7782,7 +8190,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="F24" s="6"/>
+      <c r="F24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
@@ -7833,13 +8244,13 @@
         <v>5</v>
       </c>
       <c r="T24" s="6"/>
-      <c r="U24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0100000000000002)</f>
-        <v>2.01</v>
-      </c>
-      <c r="V24" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.67)</f>
-        <v>0.67</v>
+      <c r="U24" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3100000000000005)</f>
+        <v>2.31</v>
+      </c>
+      <c r="V24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7700000000000001)</f>
+        <v>0.77</v>
       </c>
       <c r="W24" s="6"/>
       <c r="X24" s="6"/>
@@ -7884,7 +8295,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
         <v>2.7</v>
       </c>
-      <c r="F25" s="6"/>
+      <c r="F25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="G25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -7935,13 +8349,13 @@
         <v>0</v>
       </c>
       <c r="T25" s="6"/>
-      <c r="U25" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
-      </c>
-      <c r="V25" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0666666666666667)</f>
-        <v>1.066666667</v>
+      <c r="U25" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4000000000000004)</f>
+        <v>3.4</v>
+      </c>
+      <c r="V25" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1333333333333335)</f>
+        <v>1.133333333</v>
       </c>
       <c r="W25" s="6"/>
       <c r="X25" s="6"/>
@@ -7986,7 +8400,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="F26" s="6"/>
+      <c r="F26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -8037,13 +8454,13 @@
         <v>5</v>
       </c>
       <c r="T26" s="6"/>
-      <c r="U26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7449999999999997)</f>
-        <v>2.745</v>
-      </c>
-      <c r="V26" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9149999999999999)</f>
-        <v>0.915</v>
+      <c r="U26" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.045)</f>
+        <v>3.045</v>
+      </c>
+      <c r="V26" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.015)</f>
+        <v>1.015</v>
       </c>
       <c r="W26" s="6"/>
       <c r="X26" s="6"/>
@@ -8088,7 +8505,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F27" s="6"/>
+      <c r="F27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
@@ -8139,13 +8559,13 @@
         <v>5</v>
       </c>
       <c r="T27" s="6"/>
-      <c r="U27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4650000000000003)</f>
-        <v>2.465</v>
-      </c>
-      <c r="V27" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8216666666666668)</f>
-        <v>0.8216666667</v>
+      <c r="U27" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.765)</f>
+        <v>2.765</v>
+      </c>
+      <c r="V27" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9216666666666667)</f>
+        <v>0.9216666667</v>
       </c>
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
@@ -8190,7 +8610,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F28" s="6"/>
+      <c r="F28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -8241,13 +8664,13 @@
         <v>5</v>
       </c>
       <c r="T28" s="6"/>
-      <c r="U28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.26)</f>
-        <v>3.26</v>
-      </c>
-      <c r="V28" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0866666666666667)</f>
-        <v>1.086666667</v>
+      <c r="U28" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5599999999999996)</f>
+        <v>3.56</v>
+      </c>
+      <c r="V28" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1866666666666665)</f>
+        <v>1.186666667</v>
       </c>
       <c r="W28" s="6"/>
       <c r="X28" s="6"/>
@@ -8292,7 +8715,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="F29" s="6"/>
+      <c r="F29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
@@ -8343,13 +8769,13 @@
         <v>5</v>
       </c>
       <c r="T29" s="6"/>
-      <c r="U29" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.025)</f>
-        <v>2.025</v>
-      </c>
-      <c r="V29" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6749999999999999)</f>
-        <v>0.675</v>
+      <c r="U29" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.325)</f>
+        <v>2.325</v>
+      </c>
+      <c r="V29" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.775)</f>
+        <v>0.775</v>
       </c>
       <c r="W29" s="6"/>
       <c r="X29" s="6"/>
@@ -8394,7 +8820,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F30" s="6"/>
+      <c r="F30" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G30" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -8433,13 +8862,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="U30" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.535)</f>
-        <v>2.535</v>
-      </c>
-      <c r="V30" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8450000000000001)</f>
-        <v>0.845</v>
+      <c r="U30" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.935)</f>
+        <v>2.935</v>
+      </c>
+      <c r="V30" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9783333333333334)</f>
+        <v>0.9783333333</v>
       </c>
       <c r="W30" s="6"/>
       <c r="X30" s="6"/>
@@ -8484,7 +8913,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
-      <c r="F31" s="6"/>
+      <c r="F31" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G31" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -8535,13 +8967,13 @@
         <v>5</v>
       </c>
       <c r="T31" s="6"/>
-      <c r="U31" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7849999999999997)</f>
-        <v>2.785</v>
-      </c>
-      <c r="V31" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9283333333333332)</f>
-        <v>0.9283333333</v>
+      <c r="U31" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.085)</f>
+        <v>3.085</v>
+      </c>
+      <c r="V31" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0283333333333333)</f>
+        <v>1.028333333</v>
       </c>
       <c r="W31" s="6"/>
       <c r="X31" s="6"/>
@@ -8586,7 +9018,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="6"/>
+      <c r="F32" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="G32" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
         <v>1.2</v>
@@ -8637,13 +9072,13 @@
         <v>0</v>
       </c>
       <c r="T32" s="6"/>
-      <c r="U32" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3499999999999999)</f>
-        <v>1.35</v>
-      </c>
-      <c r="V32" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.44999999999999996)</f>
-        <v>0.45</v>
+      <c r="U32" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5499999999999998)</f>
+        <v>1.55</v>
+      </c>
+      <c r="V32" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5166666666666666)</f>
+        <v>0.5166666667</v>
       </c>
       <c r="W32" s="6"/>
       <c r="X32" s="6"/>
@@ -8688,7 +9123,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F33" s="6"/>
+      <c r="F33" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G33" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -8739,13 +9177,13 @@
         <v>5</v>
       </c>
       <c r="T33" s="6"/>
-      <c r="U33" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.725)</f>
-        <v>2.725</v>
-      </c>
-      <c r="V33" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9083333333333333)</f>
-        <v>0.9083333333</v>
+      <c r="U33" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.025)</f>
+        <v>3.025</v>
+      </c>
+      <c r="V33" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0083333333333333)</f>
+        <v>1.008333333</v>
       </c>
       <c r="W33" s="6"/>
       <c r="X33" s="6"/>
@@ -8790,7 +9228,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="F34" s="6"/>
+      <c r="F34" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G34" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -8841,13 +9282,13 @@
         <v>5</v>
       </c>
       <c r="T34" s="6"/>
-      <c r="U34" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.345)</f>
-        <v>3.345</v>
-      </c>
-      <c r="V34" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.115)</f>
-        <v>1.115</v>
+      <c r="U34" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.645)</f>
+        <v>3.645</v>
+      </c>
+      <c r="V34" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.215)</f>
+        <v>1.215</v>
       </c>
       <c r="W34" s="6"/>
       <c r="X34" s="6"/>
@@ -8892,7 +9333,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="F35" s="6"/>
+      <c r="F35" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G35" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -8943,13 +9387,13 @@
         <v>5</v>
       </c>
       <c r="T35" s="6"/>
-      <c r="U35" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6199999999999997)</f>
-        <v>2.62</v>
-      </c>
-      <c r="V35" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8733333333333332)</f>
-        <v>0.8733333333</v>
+      <c r="U35" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.92)</f>
+        <v>2.92</v>
+      </c>
+      <c r="V35" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9733333333333333)</f>
+        <v>0.9733333333</v>
       </c>
       <c r="W35" s="6"/>
       <c r="X35" s="6"/>
@@ -8994,7 +9438,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="F36" s="6"/>
+      <c r="F36" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G36" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
@@ -9045,13 +9492,13 @@
         <v>5</v>
       </c>
       <c r="T36" s="6"/>
-      <c r="U36" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.915)</f>
-        <v>2.915</v>
-      </c>
-      <c r="V36" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9716666666666667)</f>
-        <v>0.9716666667</v>
+      <c r="U36" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.215)</f>
+        <v>3.215</v>
+      </c>
+      <c r="V36" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0716666666666665)</f>
+        <v>1.071666667</v>
       </c>
       <c r="W36" s="6"/>
       <c r="X36" s="6"/>
@@ -9096,7 +9543,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="F37" s="6"/>
+      <c r="F37" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G37" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -9147,13 +9597,13 @@
         <v>5</v>
       </c>
       <c r="T37" s="6"/>
-      <c r="U37" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.02)</f>
-        <v>2.02</v>
-      </c>
-      <c r="V37" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6733333333333333)</f>
-        <v>0.6733333333</v>
+      <c r="U37" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.32)</f>
+        <v>2.32</v>
+      </c>
+      <c r="V37" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7733333333333333)</f>
+        <v>0.7733333333</v>
       </c>
       <c r="W37" s="6"/>
       <c r="X37" s="6"/>
@@ -9198,7 +9648,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
-      <c r="F38" s="6"/>
+      <c r="F38" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G38" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
@@ -9249,13 +9702,13 @@
         <v>5</v>
       </c>
       <c r="T38" s="6"/>
-      <c r="U38" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2150000000000003)</f>
-        <v>3.215</v>
-      </c>
-      <c r="V38" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0716666666666668)</f>
-        <v>1.071666667</v>
+      <c r="U38" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.515)</f>
+        <v>3.515</v>
+      </c>
+      <c r="V38" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1716666666666666)</f>
+        <v>1.171666667</v>
       </c>
       <c r="W38" s="6"/>
       <c r="X38" s="6"/>
@@ -9353,11 +9806,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="9" t="str">
+      <c r="H1" s="10" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(10%)")</f>
         <v>TUTORIAS(10%)</v>
       </c>
-      <c r="I1" s="9" t="str">
+      <c r="I1" s="10" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu")</f>
         <v>PQT+Tu</v>
       </c>
@@ -9389,7 +9842,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr4")</f>
         <v>Tr4</v>
       </c>
-      <c r="Q1" s="1"/>
+      <c r="Q1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta2")</f>
+        <v>Ta2</v>
+      </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
@@ -9436,15 +9892,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="G2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H2" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -9466,26 +9928,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O2" s="6"/>
+      <c r="O2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q2" s="6"/>
+      <c r="Q2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="R2" s="6"/>
-      <c r="S2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.725)</f>
-        <v>3.725</v>
-      </c>
-      <c r="T2" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2416666666666667)</f>
-        <v>1.241666667</v>
+      <c r="S2" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.665)</f>
+        <v>4.665</v>
+      </c>
+      <c r="T2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.555)</f>
+        <v>1.555</v>
       </c>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
       <c r="W2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="X2" s="6"/>
       <c r="Y2" s="6">
@@ -9515,15 +9983,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="G3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H3" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="H3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="J3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -9545,26 +10019,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O3" s="6"/>
+      <c r="O3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.31)</f>
+        <v>1.31</v>
+      </c>
       <c r="P3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q3" s="6"/>
+      <c r="Q3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="R3" s="6"/>
-      <c r="S3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.13)</f>
-        <v>3.13</v>
-      </c>
-      <c r="T3" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0433333333333332)</f>
-        <v>1.043333333</v>
+      <c r="S3" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6100000000000003)</f>
+        <v>3.61</v>
+      </c>
+      <c r="T3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2033333333333334)</f>
+        <v>1.203333333</v>
       </c>
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
       <c r="W3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="X3" s="6"/>
       <c r="Y3" s="6">
@@ -9594,15 +10074,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="G4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
-      </c>
-      <c r="H4" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="H4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="I4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="J4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -9624,26 +10110,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O4" s="6"/>
+      <c r="O4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q4" s="6"/>
+      <c r="Q4" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R4" s="6"/>
-      <c r="S4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0300000000000002)</f>
-        <v>3.03</v>
-      </c>
-      <c r="T4" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
-        <v>1.01</v>
+      <c r="S4" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7300000000000004)</f>
+        <v>3.73</v>
+      </c>
+      <c r="T4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2433333333333334)</f>
+        <v>1.243333333</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
       </c>
       <c r="X4" s="6"/>
       <c r="Y4" s="6">
@@ -9673,15 +10165,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="G5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H5" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="I5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -9703,20 +10201,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O5" s="6"/>
+      <c r="O5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="P5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q5" s="6"/>
+      <c r="Q5" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R5" s="6"/>
-      <c r="S5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.335)</f>
-        <v>3.335</v>
-      </c>
-      <c r="T5" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1116666666666666)</f>
-        <v>1.111666667</v>
+      <c r="S5" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.075)</f>
+        <v>4.075</v>
+      </c>
+      <c r="T5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3583333333333334)</f>
+        <v>1.358333333</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -9752,15 +10256,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="G6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H6" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="I6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -9782,20 +10292,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O6" s="6"/>
+      <c r="O6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.45)</f>
+        <v>4.45</v>
+      </c>
       <c r="P6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q6" s="6"/>
+      <c r="Q6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.75)</f>
+        <v>4.75</v>
+      </c>
       <c r="R6" s="6"/>
-      <c r="S6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.65)</f>
-        <v>3.65</v>
-      </c>
-      <c r="T6" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2166666666666666)</f>
-        <v>1.216666667</v>
+      <c r="S6" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.49)</f>
+        <v>4.49</v>
+      </c>
+      <c r="T6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4966666666666668)</f>
+        <v>1.496666667</v>
       </c>
       <c r="U6" s="6"/>
       <c r="V6" s="6"/>
@@ -9831,15 +10347,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="G7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
-      </c>
-      <c r="H7" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="H7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="I7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="J7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -9858,26 +10380,32 @@
         <v>5</v>
       </c>
       <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
+      <c r="O7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="6"/>
+      <c r="Q7" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R7" s="6"/>
-      <c r="S7" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.605)</f>
-        <v>2.605</v>
-      </c>
-      <c r="T7" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8683333333333333)</f>
-        <v>0.8683333333</v>
+      <c r="S7" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4850000000000003)</f>
+        <v>3.485</v>
+      </c>
+      <c r="T7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1616666666666668)</f>
+        <v>1.161666667</v>
       </c>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
       <c r="W7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="X7" s="6"/>
       <c r="Y7" s="6">
@@ -9907,15 +10435,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="F8" s="6"/>
+      <c r="F8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="G8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="H8" s="6"/>
+      <c r="H8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -9937,26 +10471,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O8" s="6"/>
+      <c r="O8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q8" s="6"/>
+      <c r="Q8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="R8" s="6"/>
-      <c r="S8" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.725)</f>
-        <v>3.725</v>
-      </c>
-      <c r="T8" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2416666666666667)</f>
-        <v>1.241666667</v>
+      <c r="S8" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.705)</f>
+        <v>4.705</v>
+      </c>
+      <c r="T8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5683333333333334)</f>
+        <v>1.568333333</v>
       </c>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="X8" s="6"/>
       <c r="Y8" s="6">
@@ -9986,24 +10526,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="H9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="O9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
+      <c r="Q9" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R9" s="6"/>
-      <c r="S9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="T9" s="10">
+      <c r="S9" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -10038,15 +10590,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F10" s="6"/>
+      <c r="F10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
-      </c>
-      <c r="H10" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -10068,26 +10626,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O10" s="6"/>
+      <c r="O10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q10" s="6"/>
+      <c r="Q10" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R10" s="6"/>
-      <c r="S10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3550000000000004)</f>
-        <v>3.355</v>
-      </c>
-      <c r="T10" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1183333333333334)</f>
-        <v>1.118333333</v>
+      <c r="S10" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4350000000000005)</f>
+        <v>4.435</v>
+      </c>
+      <c r="T10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4783333333333335)</f>
+        <v>1.478333333</v>
       </c>
       <c r="U10" s="6"/>
       <c r="V10" s="6"/>
       <c r="W10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X10" s="6"/>
       <c r="Y10" s="6">
@@ -10117,15 +10681,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="G11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="H11" s="6"/>
+      <c r="H11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -10147,20 +10717,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O11" s="6"/>
+      <c r="O11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q11" s="6"/>
+      <c r="Q11" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R11" s="6"/>
-      <c r="S11" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.44)</f>
-        <v>3.44</v>
-      </c>
-      <c r="T11" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1466666666666667)</f>
-        <v>1.146666667</v>
+      <c r="S11" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.74)</f>
+        <v>3.74</v>
+      </c>
+      <c r="T11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2466666666666668)</f>
+        <v>1.246666667</v>
       </c>
       <c r="U11" s="6"/>
       <c r="V11" s="6"/>
@@ -10196,15 +10772,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="F12" s="6"/>
+      <c r="F12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
+        <v>5.5</v>
+      </c>
       <c r="G12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H12" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -10226,20 +10808,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O12" s="6"/>
+      <c r="O12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.25)</f>
+        <v>4.25</v>
+      </c>
       <c r="P12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q12" s="6"/>
+      <c r="Q12" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R12" s="6"/>
-      <c r="S12" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.29)</f>
-        <v>3.29</v>
-      </c>
-      <c r="T12" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0966666666666667)</f>
-        <v>1.096666667</v>
+      <c r="S12" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.449999999999999)</f>
+        <v>4.45</v>
+      </c>
+      <c r="T12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4833333333333332)</f>
+        <v>1.483333333</v>
       </c>
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
@@ -10275,15 +10863,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H13" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -10305,20 +10899,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.38)</f>
+        <v>4.38</v>
+      </c>
       <c r="P13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q13" s="6"/>
+      <c r="Q13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="R13" s="6"/>
-      <c r="S13" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3449999999999998)</f>
-        <v>3.345</v>
-      </c>
-      <c r="T13" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.115)</f>
-        <v>1.115</v>
+      <c r="S13" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.405)</f>
+        <v>4.405</v>
+      </c>
+      <c r="T13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4683333333333335)</f>
+        <v>1.468333333</v>
       </c>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
@@ -10354,15 +10954,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="G14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="H14" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -10384,20 +10990,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O14" s="6"/>
+      <c r="O14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q14" s="6"/>
+      <c r="Q14" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R14" s="6"/>
-      <c r="S14" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.835)</f>
-        <v>3.835</v>
-      </c>
-      <c r="T14" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2783333333333333)</f>
-        <v>1.278333333</v>
+      <c r="S14" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.755000000000001)</f>
+        <v>4.755</v>
+      </c>
+      <c r="T14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5850000000000002)</f>
+        <v>1.585</v>
       </c>
       <c r="U14" s="6"/>
       <c r="V14" s="6"/>
@@ -10433,15 +11045,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
-        <v>3.7</v>
-      </c>
-      <c r="H15" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -10452,8 +11070,8 @@
         <v>5</v>
       </c>
       <c r="L15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="M15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -10463,26 +11081,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O15" s="6"/>
+      <c r="O15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q15" s="6"/>
+      <c r="Q15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.75)</f>
+        <v>4.75</v>
+      </c>
       <c r="R15" s="6"/>
-      <c r="S15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2950000000000004)</f>
-        <v>3.295</v>
-      </c>
-      <c r="T15" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0983333333333334)</f>
-        <v>1.098333333</v>
+      <c r="S15" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.515000000000001)</f>
+        <v>4.515</v>
+      </c>
+      <c r="T15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5050000000000001)</f>
+        <v>1.505</v>
       </c>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
-        <v>3.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X15" s="6"/>
       <c r="Y15" s="6">
@@ -10512,15 +11136,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="G16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H16" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="H16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="J16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -10542,26 +11172,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O16" s="6"/>
+      <c r="O16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q16" s="6"/>
+      <c r="Q16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="R16" s="6"/>
-      <c r="S16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.635)</f>
-        <v>3.635</v>
-      </c>
-      <c r="T16" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2116666666666667)</f>
-        <v>1.211666667</v>
+      <c r="S16" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.415)</f>
+        <v>4.415</v>
+      </c>
+      <c r="T16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4716666666666667)</f>
+        <v>1.471666667</v>
       </c>
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="X16" s="6"/>
       <c r="Y16" s="6">
@@ -10591,15 +11227,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="G17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H17" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -10621,20 +11263,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O17" s="6"/>
+      <c r="O17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="P17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q17" s="6"/>
+      <c r="Q17" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R17" s="6"/>
-      <c r="S17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9899999999999998)</f>
-        <v>2.99</v>
-      </c>
-      <c r="T17" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9966666666666666)</f>
-        <v>0.9966666667</v>
+      <c r="S17" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.73)</f>
+        <v>3.73</v>
+      </c>
+      <c r="T17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2433333333333334)</f>
+        <v>1.243333333</v>
       </c>
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
@@ -10670,15 +11318,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="G18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
-      </c>
-      <c r="H18" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -10700,26 +11354,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O18" s="6"/>
+      <c r="O18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q18" s="6"/>
+      <c r="Q18" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R18" s="6"/>
-      <c r="S18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.995)</f>
-        <v>2.995</v>
-      </c>
-      <c r="T18" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9983333333333334)</f>
-        <v>0.9983333333</v>
+      <c r="S18" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.775)</f>
+        <v>3.775</v>
+      </c>
+      <c r="T18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2583333333333333)</f>
+        <v>1.258333333</v>
       </c>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
       <c r="W18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="X18" s="6"/>
       <c r="Y18" s="6">
@@ -10749,15 +11409,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="G19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -10779,26 +11445,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O19" s="6"/>
+      <c r="O19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.46)</f>
+        <v>2.46</v>
+      </c>
       <c r="P19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q19" s="6"/>
+      <c r="Q19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="R19" s="6"/>
-      <c r="S19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.685)</f>
-        <v>3.685</v>
-      </c>
-      <c r="T19" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2283333333333333)</f>
-        <v>1.228333333</v>
+      <c r="S19" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.485)</f>
+        <v>4.485</v>
+      </c>
+      <c r="T19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.495)</f>
+        <v>1.495</v>
       </c>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X19" s="6"/>
       <c r="Y19" s="6">
@@ -10828,15 +11500,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="F20" s="6"/>
+      <c r="F20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="G20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="J20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -10858,26 +11536,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O20" s="6"/>
+      <c r="O20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="P20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q20" s="6"/>
+      <c r="Q20" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R20" s="6"/>
-      <c r="S20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.31)</f>
-        <v>3.31</v>
-      </c>
-      <c r="T20" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1033333333333333)</f>
-        <v>1.103333333</v>
+      <c r="S20" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.01)</f>
+        <v>4.01</v>
+      </c>
+      <c r="T20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3366666666666667)</f>
+        <v>1.336666667</v>
       </c>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="X20" s="6"/>
       <c r="Y20" s="6">
@@ -10907,15 +11591,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="G21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H21" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="H21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="I21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="J21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -10937,26 +11627,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O21" s="6"/>
+      <c r="O21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q21" s="6"/>
+      <c r="Q21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="R21" s="6"/>
-      <c r="S21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.65)</f>
-        <v>3.65</v>
-      </c>
-      <c r="T21" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2166666666666666)</f>
-        <v>1.216666667</v>
+      <c r="S21" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.61)</f>
+        <v>4.61</v>
+      </c>
+      <c r="T21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5366666666666668)</f>
+        <v>1.536666667</v>
       </c>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="W21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="6">
@@ -10986,15 +11682,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F22" s="6"/>
+      <c r="F22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.4)</f>
+        <v>5.4</v>
+      </c>
       <c r="G22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H22" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="I22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="J22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -11016,26 +11718,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O22" s="6"/>
+      <c r="O22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
+        <v>3.33</v>
+      </c>
       <c r="P22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q22" s="6"/>
+      <c r="Q22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.25)</f>
+        <v>4.25</v>
+      </c>
       <c r="R22" s="6"/>
-      <c r="S22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.64)</f>
-        <v>3.64</v>
-      </c>
-      <c r="T22" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2133333333333334)</f>
-        <v>1.213333333</v>
+      <c r="S22" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.680000000000001)</f>
+        <v>4.68</v>
+      </c>
+      <c r="T22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5600000000000003)</f>
+        <v>1.56</v>
       </c>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="X22" s="6"/>
       <c r="Y22" s="6">
@@ -11065,15 +11773,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F23" s="6"/>
+      <c r="F23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
+      </c>
       <c r="G23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="H23" s="6"/>
+      <c r="H23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -11095,20 +11809,26 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O23" s="6"/>
+      <c r="O23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q23" s="6"/>
+      <c r="Q23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="R23" s="6"/>
-      <c r="S23" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="T23" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3333333333333333)</f>
-        <v>1.333333333</v>
+      <c r="S23" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.2)</f>
+        <v>5.2</v>
+      </c>
+      <c r="T23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7333333333333334)</f>
+        <v>1.733333333</v>
       </c>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
@@ -11144,15 +11864,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="F24" s="6"/>
+      <c r="F24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
       <c r="G24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="H24" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="H24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="J24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -11174,26 +11900,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O24" s="6"/>
+      <c r="O24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.13)</f>
+        <v>0.13</v>
+      </c>
       <c r="P24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q24" s="6"/>
+      <c r="Q24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
+      </c>
       <c r="R24" s="6"/>
-      <c r="S24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.64)</f>
-        <v>3.64</v>
-      </c>
-      <c r="T24" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2133333333333334)</f>
-        <v>1.213333333</v>
+      <c r="S24" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.26)</f>
+        <v>4.26</v>
+      </c>
+      <c r="T24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.42)</f>
+        <v>1.42</v>
       </c>
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
       <c r="W24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="X24" s="6"/>
       <c r="Y24" s="6">
@@ -11223,15 +11955,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="F25" s="6"/>
+      <c r="F25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="G25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="H25" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -11253,26 +11991,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O25" s="6"/>
+      <c r="O25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q25" s="6"/>
+      <c r="Q25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="R25" s="6"/>
-      <c r="S25" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.725)</f>
-        <v>3.725</v>
-      </c>
-      <c r="T25" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2416666666666667)</f>
-        <v>1.241666667</v>
+      <c r="S25" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.365)</f>
+        <v>4.365</v>
+      </c>
+      <c r="T25" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.455)</f>
+        <v>1.455</v>
       </c>
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
       <c r="W25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="X25" s="6"/>
       <c r="Y25" s="6">
@@ -11302,15 +12046,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="6"/>
+      <c r="F26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="G26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
-      </c>
-      <c r="H26" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="H26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="I26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
-        <v>1.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="J26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -11332,26 +12082,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="6"/>
+      <c r="O26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="Q26" s="6"/>
+      <c r="Q26" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R26" s="6"/>
-      <c r="S26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9500000000000001)</f>
-        <v>0.95</v>
-      </c>
-      <c r="T26" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3166666666666667)</f>
-        <v>0.3166666667</v>
+      <c r="S26" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.89)</f>
+        <v>0.89</v>
+      </c>
+      <c r="T26" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.2966666666666667)</f>
+        <v>0.2966666667</v>
       </c>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
       <c r="W26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="X26" s="6"/>
       <c r="Y26" s="6">
@@ -11381,15 +12137,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="F27" s="6"/>
+      <c r="F27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="G27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H27" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -11411,26 +12173,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O27" s="6"/>
+      <c r="O27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q27" s="6"/>
+      <c r="Q27" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="R27" s="6"/>
-      <c r="S27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.605)</f>
-        <v>2.605</v>
-      </c>
-      <c r="T27" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8683333333333333)</f>
-        <v>0.8683333333</v>
+      <c r="S27" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.165)</f>
+        <v>3.165</v>
+      </c>
+      <c r="T27" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.055)</f>
+        <v>1.055</v>
       </c>
       <c r="U27" s="6"/>
       <c r="V27" s="6"/>
       <c r="W27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X27" s="6"/>
       <c r="Y27" s="6">
@@ -11460,15 +12228,21 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="F28" s="6"/>
+      <c r="F28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="G28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H28" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -11490,26 +12264,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="O28" s="6"/>
+      <c r="O28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Q28" s="6"/>
+      <c r="Q28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="R28" s="6"/>
-      <c r="S28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.96)</f>
-        <v>2.96</v>
-      </c>
-      <c r="T28" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9866666666666667)</f>
-        <v>0.9866666667</v>
+      <c r="S28" s="8">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.52)</f>
+        <v>3.52</v>
+      </c>
+      <c r="T28" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1733333333333333)</f>
+        <v>1.173333333</v>
       </c>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="X28" s="6"/>
       <c r="Y28" s="6">

--- a/app_notas_uis.xlsx
+++ b/app_notas_uis.xlsx
@@ -55,7 +55,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -79,6 +79,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -3204,10 +3207,10 @@
         <v>PQT</v>
       </c>
       <c r="H1" s="10" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(10%)")</f>
-        <v>TUTORIAS(10%)</v>
-      </c>
-      <c r="I1" s="10" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTO")</f>
+        <v>TUTO</v>
+      </c>
+      <c r="I1" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu(20%)")</f>
         <v>PQT+Tu(20%)</v>
       </c>
@@ -3339,7 +3342,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4350000000000005)</f>
         <v>4.435</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4783333333333335)</f>
         <v>1.478333333</v>
       </c>
@@ -3427,7 +3430,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T3" s="11">
+      <c r="T3" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6666666666666667)</f>
         <v>1.666666667</v>
       </c>
@@ -3515,7 +3518,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T4" s="11">
+      <c r="T4" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6666666666666667)</f>
         <v>1.666666667</v>
       </c>
@@ -3603,7 +3606,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.575)</f>
         <v>3.575</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1916666666666667)</f>
         <v>1.191666667</v>
       </c>
@@ -3691,7 +3694,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.91)</f>
         <v>3.91</v>
       </c>
-      <c r="T6" s="11">
+      <c r="T6" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3033333333333335)</f>
         <v>1.303333333</v>
       </c>
@@ -3779,7 +3782,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.875)</f>
         <v>4.875</v>
       </c>
-      <c r="T7" s="11">
+      <c r="T7" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.625)</f>
         <v>1.625</v>
       </c>
@@ -3867,7 +3870,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.565)</f>
         <v>4.565</v>
       </c>
-      <c r="T8" s="11">
+      <c r="T8" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5216666666666667)</f>
         <v>1.521666667</v>
       </c>
@@ -3955,7 +3958,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.86)</f>
         <v>3.86</v>
       </c>
-      <c r="T9" s="11">
+      <c r="T9" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2866666666666666)</f>
         <v>1.286666667</v>
       </c>
@@ -4043,7 +4046,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.96)</f>
         <v>4.96</v>
       </c>
-      <c r="T10" s="11">
+      <c r="T10" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6533333333333333)</f>
         <v>1.653333333</v>
       </c>
@@ -4131,7 +4134,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.73)</f>
         <v>4.73</v>
       </c>
-      <c r="T11" s="11">
+      <c r="T11" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5766666666666669)</f>
         <v>1.576666667</v>
       </c>
@@ -4219,7 +4222,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.855)</f>
         <v>4.855</v>
       </c>
-      <c r="T12" s="11">
+      <c r="T12" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6183333333333334)</f>
         <v>1.618333333</v>
       </c>
@@ -4307,7 +4310,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="T13" s="11">
+      <c r="T13" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5666666666666667)</f>
         <v>1.566666667</v>
       </c>
@@ -4395,7 +4398,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.975)</f>
         <v>4.975</v>
       </c>
-      <c r="T14" s="11">
+      <c r="T14" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6583333333333332)</f>
         <v>1.658333333</v>
       </c>
@@ -4483,7 +4486,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.840000000000001)</f>
         <v>4.84</v>
       </c>
-      <c r="T15" s="11">
+      <c r="T15" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6133333333333335)</f>
         <v>1.613333333</v>
       </c>
@@ -4571,7 +4574,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.995)</f>
         <v>3.995</v>
       </c>
-      <c r="T16" s="11">
+      <c r="T16" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3316666666666668)</f>
         <v>1.331666667</v>
       </c>
@@ -4659,7 +4662,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.63)</f>
         <v>3.63</v>
       </c>
-      <c r="T17" s="11">
+      <c r="T17" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.21)</f>
         <v>1.21</v>
       </c>
@@ -4747,7 +4750,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.655)</f>
         <v>4.655</v>
       </c>
-      <c r="T18" s="11">
+      <c r="T18" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5516666666666667)</f>
         <v>1.551666667</v>
       </c>
@@ -4835,7 +4838,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.73)</f>
         <v>4.73</v>
       </c>
-      <c r="T19" s="11">
+      <c r="T19" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5766666666666669)</f>
         <v>1.576666667</v>
       </c>
@@ -4923,7 +4926,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.115)</f>
         <v>4.115</v>
       </c>
-      <c r="T20" s="11">
+      <c r="T20" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3716666666666668)</f>
         <v>1.371666667</v>
       </c>
@@ -5011,7 +5014,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.630000000000001)</f>
         <v>4.63</v>
       </c>
-      <c r="T21" s="11">
+      <c r="T21" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5433333333333337)</f>
         <v>1.543333333</v>
       </c>
@@ -5099,7 +5102,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6050000000000004)</f>
         <v>3.605</v>
       </c>
-      <c r="T22" s="11">
+      <c r="T22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2016666666666669)</f>
         <v>1.201666667</v>
       </c>
@@ -5187,7 +5190,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.71)</f>
         <v>4.71</v>
       </c>
-      <c r="T23" s="11">
+      <c r="T23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.57)</f>
         <v>1.57</v>
       </c>
@@ -5275,7 +5278,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.98)</f>
         <v>4.98</v>
       </c>
-      <c r="T24" s="11">
+      <c r="T24" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6600000000000001)</f>
         <v>1.66</v>
       </c>
@@ -5363,7 +5366,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T25" s="11">
+      <c r="T25" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6666666666666667)</f>
         <v>1.666666667</v>
       </c>
@@ -5451,7 +5454,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.205)</f>
         <v>3.205</v>
       </c>
-      <c r="T26" s="11">
+      <c r="T26" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0683333333333334)</f>
         <v>1.068333333</v>
       </c>
@@ -5539,7 +5542,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5200000000000005)</f>
         <v>4.52</v>
       </c>
-      <c r="T27" s="11">
+      <c r="T27" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5066666666666668)</f>
         <v>1.506666667</v>
       </c>
@@ -5627,7 +5630,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.365)</f>
         <v>4.365</v>
       </c>
-      <c r="T28" s="11">
+      <c r="T28" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.455)</f>
         <v>1.455</v>
       </c>
@@ -5715,7 +5718,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.82)</f>
         <v>4.82</v>
       </c>
-      <c r="T29" s="11">
+      <c r="T29" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6066666666666667)</f>
         <v>1.606666667</v>
       </c>
@@ -5807,11 +5810,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="10" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(8%)")</f>
-        <v>TUTORIAS(8%)</v>
-      </c>
-      <c r="I1" s="10" t="str">
+      <c r="H1" s="11" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTO")</f>
+        <v>TUTO</v>
+      </c>
+      <c r="I1" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu")</f>
         <v>PQT+Tu</v>
       </c>
@@ -5968,7 +5971,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5349999999999993)</f>
         <v>3.535</v>
       </c>
-      <c r="V2" s="11">
+      <c r="V2" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.178333333333333)</f>
         <v>1.178333333</v>
       </c>
@@ -6073,7 +6076,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2300000000000004)</f>
         <v>3.23</v>
       </c>
-      <c r="V3" s="11">
+      <c r="V3" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0766666666666669)</f>
         <v>1.076666667</v>
       </c>
@@ -6178,7 +6181,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.315)</f>
         <v>3.315</v>
       </c>
-      <c r="V4" s="11">
+      <c r="V4" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.105)</f>
         <v>1.105</v>
       </c>
@@ -6283,7 +6286,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.54)</f>
         <v>2.54</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8466666666666667)</f>
         <v>0.8466666667</v>
       </c>
@@ -6388,7 +6391,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6300000000000001)</f>
         <v>1.63</v>
       </c>
-      <c r="V6" s="11">
+      <c r="V6" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5433333333333333)</f>
         <v>0.5433333333</v>
       </c>
@@ -6493,7 +6496,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.57)</f>
         <v>3.57</v>
       </c>
-      <c r="V7" s="11">
+      <c r="V7" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.19)</f>
         <v>1.19</v>
       </c>
@@ -6598,7 +6601,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3299999999999996)</f>
         <v>3.33</v>
       </c>
-      <c r="V8" s="11">
+      <c r="V8" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1099999999999999)</f>
         <v>1.11</v>
       </c>
@@ -6703,7 +6706,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.71)</f>
         <v>2.71</v>
       </c>
-      <c r="V9" s="11">
+      <c r="V9" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9033333333333333)</f>
         <v>0.9033333333</v>
       </c>
@@ -6808,7 +6811,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.735)</f>
         <v>3.735</v>
       </c>
-      <c r="V10" s="11">
+      <c r="V10" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2449999999999999)</f>
         <v>1.245</v>
       </c>
@@ -6913,7 +6916,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9699999999999998)</f>
         <v>2.97</v>
       </c>
-      <c r="V11" s="11">
+      <c r="V11" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9899999999999999)</f>
         <v>0.99</v>
       </c>
@@ -7018,7 +7021,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.25)</f>
         <v>3.25</v>
       </c>
-      <c r="V12" s="11">
+      <c r="V12" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0833333333333333)</f>
         <v>1.083333333</v>
       </c>
@@ -7123,7 +7126,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.595)</f>
         <v>3.595</v>
       </c>
-      <c r="V13" s="11">
+      <c r="V13" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1983333333333335)</f>
         <v>1.198333333</v>
       </c>
@@ -7228,7 +7231,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.385)</f>
         <v>2.385</v>
       </c>
-      <c r="V14" s="11">
+      <c r="V14" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7949999999999999)</f>
         <v>0.795</v>
       </c>
@@ -7306,7 +7309,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V15" s="11">
+      <c r="V15" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -7408,7 +7411,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.73)</f>
         <v>2.73</v>
       </c>
-      <c r="V16" s="11">
+      <c r="V16" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.91)</f>
         <v>0.91</v>
       </c>
@@ -7513,7 +7516,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.875)</f>
         <v>2.875</v>
       </c>
-      <c r="V17" s="11">
+      <c r="V17" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9583333333333334)</f>
         <v>0.9583333333</v>
       </c>
@@ -7618,7 +7621,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.975)</f>
         <v>1.975</v>
       </c>
-      <c r="V18" s="11">
+      <c r="V18" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6583333333333333)</f>
         <v>0.6583333333</v>
       </c>
@@ -7723,7 +7726,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0300000000000002)</f>
         <v>3.03</v>
       </c>
-      <c r="V19" s="11">
+      <c r="V19" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
         <v>1.01</v>
       </c>
@@ -7828,7 +7831,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8249999999999997)</f>
         <v>3.825</v>
       </c>
-      <c r="V20" s="11">
+      <c r="V20" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.275)</f>
         <v>1.275</v>
       </c>
@@ -7933,7 +7936,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1450000000000005)</f>
         <v>3.145</v>
       </c>
-      <c r="V21" s="11">
+      <c r="V21" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0483333333333336)</f>
         <v>1.048333333</v>
       </c>
@@ -8038,7 +8041,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.47)</f>
         <v>3.47</v>
       </c>
-      <c r="V22" s="11">
+      <c r="V22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1566666666666667)</f>
         <v>1.156666667</v>
       </c>
@@ -8143,7 +8146,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.56)</f>
         <v>3.56</v>
       </c>
-      <c r="V23" s="11">
+      <c r="V23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1866666666666668)</f>
         <v>1.186666667</v>
       </c>
@@ -8248,7 +8251,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3100000000000005)</f>
         <v>2.31</v>
       </c>
-      <c r="V24" s="11">
+      <c r="V24" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7700000000000001)</f>
         <v>0.77</v>
       </c>
@@ -8353,7 +8356,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4000000000000004)</f>
         <v>3.4</v>
       </c>
-      <c r="V25" s="11">
+      <c r="V25" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1333333333333335)</f>
         <v>1.133333333</v>
       </c>
@@ -8458,7 +8461,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.045)</f>
         <v>3.045</v>
       </c>
-      <c r="V26" s="11">
+      <c r="V26" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.015)</f>
         <v>1.015</v>
       </c>
@@ -8563,7 +8566,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.765)</f>
         <v>2.765</v>
       </c>
-      <c r="V27" s="11">
+      <c r="V27" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9216666666666667)</f>
         <v>0.9216666667</v>
       </c>
@@ -8668,7 +8671,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5599999999999996)</f>
         <v>3.56</v>
       </c>
-      <c r="V28" s="11">
+      <c r="V28" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1866666666666665)</f>
         <v>1.186666667</v>
       </c>
@@ -8773,7 +8776,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.325)</f>
         <v>2.325</v>
       </c>
-      <c r="V29" s="11">
+      <c r="V29" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.775)</f>
         <v>0.775</v>
       </c>
@@ -8866,7 +8869,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.935)</f>
         <v>2.935</v>
       </c>
-      <c r="V30" s="11">
+      <c r="V30" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9783333333333334)</f>
         <v>0.9783333333</v>
       </c>
@@ -8971,7 +8974,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.085)</f>
         <v>3.085</v>
       </c>
-      <c r="V31" s="11">
+      <c r="V31" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0283333333333333)</f>
         <v>1.028333333</v>
       </c>
@@ -9076,7 +9079,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5499999999999998)</f>
         <v>1.55</v>
       </c>
-      <c r="V32" s="11">
+      <c r="V32" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5166666666666666)</f>
         <v>0.5166666667</v>
       </c>
@@ -9181,7 +9184,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.025)</f>
         <v>3.025</v>
       </c>
-      <c r="V33" s="11">
+      <c r="V33" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0083333333333333)</f>
         <v>1.008333333</v>
       </c>
@@ -9286,7 +9289,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.645)</f>
         <v>3.645</v>
       </c>
-      <c r="V34" s="11">
+      <c r="V34" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.215)</f>
         <v>1.215</v>
       </c>
@@ -9391,7 +9394,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.92)</f>
         <v>2.92</v>
       </c>
-      <c r="V35" s="11">
+      <c r="V35" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9733333333333333)</f>
         <v>0.9733333333</v>
       </c>
@@ -9496,7 +9499,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.215)</f>
         <v>3.215</v>
       </c>
-      <c r="V36" s="11">
+      <c r="V36" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0716666666666665)</f>
         <v>1.071666667</v>
       </c>
@@ -9601,7 +9604,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.32)</f>
         <v>2.32</v>
       </c>
-      <c r="V37" s="11">
+      <c r="V37" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7733333333333333)</f>
         <v>0.7733333333</v>
       </c>
@@ -9706,7 +9709,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.515)</f>
         <v>3.515</v>
       </c>
-      <c r="V38" s="11">
+      <c r="V38" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1716666666666666)</f>
         <v>1.171666667</v>
       </c>
@@ -9806,11 +9809,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="10" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTORIAS(10%)")</f>
-        <v>TUTORIAS(10%)</v>
-      </c>
-      <c r="I1" s="10" t="str">
+      <c r="H1" s="11" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTO")</f>
+        <v>TUTO</v>
+      </c>
+      <c r="I1" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT+Tu")</f>
         <v>PQT+Tu</v>
       </c>
@@ -9945,7 +9948,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.665)</f>
         <v>4.665</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.555)</f>
         <v>1.555</v>
       </c>
@@ -10036,7 +10039,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6100000000000003)</f>
         <v>3.61</v>
       </c>
-      <c r="T3" s="11">
+      <c r="T3" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2033333333333334)</f>
         <v>1.203333333</v>
       </c>
@@ -10127,7 +10130,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7300000000000004)</f>
         <v>3.73</v>
       </c>
-      <c r="T4" s="11">
+      <c r="T4" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2433333333333334)</f>
         <v>1.243333333</v>
       </c>
@@ -10218,7 +10221,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.075)</f>
         <v>4.075</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3583333333333334)</f>
         <v>1.358333333</v>
       </c>
@@ -10309,7 +10312,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.49)</f>
         <v>4.49</v>
       </c>
-      <c r="T6" s="11">
+      <c r="T6" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4966666666666668)</f>
         <v>1.496666667</v>
       </c>
@@ -10397,7 +10400,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4850000000000003)</f>
         <v>3.485</v>
       </c>
-      <c r="T7" s="11">
+      <c r="T7" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1616666666666668)</f>
         <v>1.161666667</v>
       </c>
@@ -10488,7 +10491,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.705)</f>
         <v>4.705</v>
       </c>
-      <c r="T8" s="11">
+      <c r="T8" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5683333333333334)</f>
         <v>1.568333333</v>
       </c>
@@ -10555,7 +10558,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="T9" s="11">
+      <c r="T9" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -10643,7 +10646,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4350000000000005)</f>
         <v>4.435</v>
       </c>
-      <c r="T10" s="11">
+      <c r="T10" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4783333333333335)</f>
         <v>1.478333333</v>
       </c>
@@ -10734,7 +10737,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.74)</f>
         <v>3.74</v>
       </c>
-      <c r="T11" s="11">
+      <c r="T11" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2466666666666668)</f>
         <v>1.246666667</v>
       </c>
@@ -10825,7 +10828,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.449999999999999)</f>
         <v>4.45</v>
       </c>
-      <c r="T12" s="11">
+      <c r="T12" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4833333333333332)</f>
         <v>1.483333333</v>
       </c>
@@ -10916,7 +10919,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.405)</f>
         <v>4.405</v>
       </c>
-      <c r="T13" s="11">
+      <c r="T13" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4683333333333335)</f>
         <v>1.468333333</v>
       </c>
@@ -11007,7 +11010,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.755000000000001)</f>
         <v>4.755</v>
       </c>
-      <c r="T14" s="11">
+      <c r="T14" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5850000000000002)</f>
         <v>1.585</v>
       </c>
@@ -11098,7 +11101,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.515000000000001)</f>
         <v>4.515</v>
       </c>
-      <c r="T15" s="11">
+      <c r="T15" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5050000000000001)</f>
         <v>1.505</v>
       </c>
@@ -11189,7 +11192,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.415)</f>
         <v>4.415</v>
       </c>
-      <c r="T16" s="11">
+      <c r="T16" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4716666666666667)</f>
         <v>1.471666667</v>
       </c>
@@ -11280,7 +11283,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.73)</f>
         <v>3.73</v>
       </c>
-      <c r="T17" s="11">
+      <c r="T17" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2433333333333334)</f>
         <v>1.243333333</v>
       </c>
@@ -11371,7 +11374,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.775)</f>
         <v>3.775</v>
       </c>
-      <c r="T18" s="11">
+      <c r="T18" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2583333333333333)</f>
         <v>1.258333333</v>
       </c>
@@ -11462,7 +11465,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.485)</f>
         <v>4.485</v>
       </c>
-      <c r="T19" s="11">
+      <c r="T19" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.495)</f>
         <v>1.495</v>
       </c>
@@ -11553,7 +11556,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.01)</f>
         <v>4.01</v>
       </c>
-      <c r="T20" s="11">
+      <c r="T20" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3366666666666667)</f>
         <v>1.336666667</v>
       </c>
@@ -11644,7 +11647,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.61)</f>
         <v>4.61</v>
       </c>
-      <c r="T21" s="11">
+      <c r="T21" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5366666666666668)</f>
         <v>1.536666667</v>
       </c>
@@ -11735,7 +11738,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.680000000000001)</f>
         <v>4.68</v>
       </c>
-      <c r="T22" s="11">
+      <c r="T22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5600000000000003)</f>
         <v>1.56</v>
       </c>
@@ -11826,7 +11829,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.2)</f>
         <v>5.2</v>
       </c>
-      <c r="T23" s="11">
+      <c r="T23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7333333333333334)</f>
         <v>1.733333333</v>
       </c>
@@ -11917,7 +11920,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.26)</f>
         <v>4.26</v>
       </c>
-      <c r="T24" s="11">
+      <c r="T24" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.42)</f>
         <v>1.42</v>
       </c>
@@ -12008,7 +12011,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.365)</f>
         <v>4.365</v>
       </c>
-      <c r="T25" s="11">
+      <c r="T25" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.455)</f>
         <v>1.455</v>
       </c>
@@ -12099,7 +12102,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.89)</f>
         <v>0.89</v>
       </c>
-      <c r="T26" s="11">
+      <c r="T26" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.2966666666666667)</f>
         <v>0.2966666667</v>
       </c>
@@ -12190,7 +12193,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.165)</f>
         <v>3.165</v>
       </c>
-      <c r="T27" s="11">
+      <c r="T27" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.055)</f>
         <v>1.055</v>
       </c>
@@ -12281,7 +12284,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.52)</f>
         <v>3.52</v>
       </c>
-      <c r="T28" s="11">
+      <c r="T28" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1733333333333333)</f>
         <v>1.173333333</v>
       </c>

--- a/app_notas_uis.xlsx
+++ b/app_notas_uis.xlsx
@@ -93,7 +93,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font/>
       <fill>
@@ -122,6 +122,16 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE599"/>
+          <bgColor rgb="FFFFE599"/>
         </patternFill>
       </fill>
       <border/>
@@ -368,7 +378,8 @@
     <col customWidth="1" min="3" max="17" width="3.88"/>
     <col customWidth="1" min="18" max="18" width="6.0"/>
     <col customWidth="1" min="19" max="19" width="7.0"/>
-    <col customWidth="1" min="20" max="22" width="3.88"/>
+    <col customWidth="1" min="20" max="20" width="7.5"/>
+    <col customWidth="1" min="21" max="22" width="3.88"/>
     <col customWidth="1" min="23" max="23" width="6.13"/>
     <col customWidth="1" min="24" max="24" width="7.25"/>
     <col customWidth="1" min="25" max="37" width="3.88"/>
@@ -497,12 +508,12 @@
         <v>0</v>
       </c>
       <c r="F2" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
       </c>
       <c r="H2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -548,14 +559,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="S2" s="6"/>
+      <c r="S2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="T2" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.015)</f>
-        <v>2.015</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.54)</f>
+        <v>1.54</v>
       </c>
       <c r="U2" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6716666666666667)</f>
-        <v>0.6716666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5133333333333333)</f>
+        <v>0.5133333333</v>
       </c>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
@@ -592,12 +606,12 @@
         <v>1.5</v>
       </c>
       <c r="F3" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -643,14 +657,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S3" s="6"/>
+      <c r="S3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T3" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.18)</f>
-        <v>3.18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.61)</f>
+        <v>3.61</v>
       </c>
       <c r="U3" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.06)</f>
-        <v>1.06</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2033333333333334)</f>
+        <v>1.203333333</v>
       </c>
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
@@ -687,8 +704,8 @@
         <v>1.8</v>
       </c>
       <c r="F4" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="G4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -738,14 +755,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="S4" s="6"/>
+      <c r="S4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T4" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.905)</f>
-        <v>2.905</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9650000000000003)</f>
+        <v>2.965</v>
       </c>
       <c r="U4" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9683333333333333)</f>
-        <v>0.9683333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9883333333333334)</f>
+        <v>0.9883333333</v>
       </c>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
@@ -782,12 +802,12 @@
         <v>1.8</v>
       </c>
       <c r="F5" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="G5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -833,14 +853,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S5" s="6"/>
+      <c r="S5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T5" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.24)</f>
-        <v>3.24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.630000000000001)</f>
+        <v>3.63</v>
       </c>
       <c r="U5" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2100000000000002)</f>
+        <v>1.21</v>
       </c>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
@@ -877,8 +900,8 @@
         <v>1.8</v>
       </c>
       <c r="F6" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -928,14 +951,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="S6" s="6"/>
+      <c r="S6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1100000000000003)</f>
-        <v>3.11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5300000000000002)</f>
+        <v>3.53</v>
       </c>
       <c r="U6" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0366666666666668)</f>
-        <v>1.036666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1766666666666667)</f>
+        <v>1.176666667</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
@@ -972,12 +998,12 @@
         <v>1.5</v>
       </c>
       <c r="F7" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="G7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -1023,14 +1049,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S7" s="6"/>
+      <c r="S7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T7" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5100000000000002)</f>
-        <v>2.51</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7850000000000006)</f>
+        <v>2.785</v>
       </c>
       <c r="U7" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8366666666666668)</f>
-        <v>0.8366666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9283333333333336)</f>
+        <v>0.9283333333</v>
       </c>
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
@@ -1067,12 +1096,12 @@
         <v>1.3</v>
       </c>
       <c r="F8" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="G8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -1118,14 +1147,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S8" s="6"/>
+      <c r="S8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="T8" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.575)</f>
-        <v>2.575</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.47)</f>
+        <v>2.47</v>
       </c>
       <c r="U8" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8583333333333334)</f>
-        <v>0.8583333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8233333333333334)</f>
+        <v>0.8233333333</v>
       </c>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
@@ -1162,12 +1194,12 @@
         <v>2.2</v>
       </c>
       <c r="F9" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -1213,14 +1245,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S9" s="6"/>
+      <c r="S9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T9" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2649999999999997)</f>
-        <v>3.265</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.71)</f>
+        <v>3.71</v>
       </c>
       <c r="U9" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0883333333333332)</f>
-        <v>1.088333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2366666666666666)</f>
+        <v>1.236666667</v>
       </c>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
@@ -1257,12 +1292,12 @@
         <v>2</v>
       </c>
       <c r="F10" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="G10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="H10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -1308,14 +1343,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S10" s="6"/>
+      <c r="S10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T10" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.34)</f>
-        <v>3.34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.67)</f>
+        <v>3.67</v>
       </c>
       <c r="U10" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1133333333333333)</f>
-        <v>1.113333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2233333333333334)</f>
+        <v>1.223333333</v>
       </c>
       <c r="V10" s="6"/>
       <c r="W10" s="6"/>
@@ -1352,12 +1390,12 @@
         <v>2</v>
       </c>
       <c r="F11" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="G11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -1403,14 +1441,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="S11" s="6"/>
+      <c r="S11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T11" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.08)</f>
-        <v>3.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2199999999999998)</f>
+        <v>3.22</v>
       </c>
       <c r="U11" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0266666666666666)</f>
-        <v>1.026666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0733333333333333)</f>
+        <v>1.073333333</v>
       </c>
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
@@ -1447,12 +1488,12 @@
         <v>1.5</v>
       </c>
       <c r="F12" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
       </c>
       <c r="G12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="H12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -1498,14 +1539,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="S12" s="6"/>
+      <c r="S12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T12" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.92)</f>
-        <v>2.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.05)</f>
+        <v>3.05</v>
       </c>
       <c r="U12" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9733333333333333)</f>
-        <v>0.9733333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0166666666666666)</f>
+        <v>1.016666667</v>
       </c>
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
@@ -1542,12 +1586,12 @@
         <v>1</v>
       </c>
       <c r="F13" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="G13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="H13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -1593,14 +1637,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S13" s="6"/>
+      <c r="S13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T13" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4649999999999999)</f>
-        <v>1.465</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8649999999999998)</f>
+        <v>1.865</v>
       </c>
       <c r="U13" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4883333333333333)</f>
-        <v>0.4883333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6216666666666666)</f>
+        <v>0.6216666667</v>
       </c>
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
@@ -1637,12 +1684,12 @@
         <v>2.3</v>
       </c>
       <c r="F14" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -1688,14 +1735,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S14" s="6"/>
+      <c r="S14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T14" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7750000000000004)</f>
-        <v>3.775</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.22)</f>
+        <v>4.22</v>
       </c>
       <c r="U14" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2583333333333335)</f>
-        <v>1.258333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4066666666666665)</f>
+        <v>1.406666667</v>
       </c>
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
@@ -1732,12 +1782,12 @@
         <v>1</v>
       </c>
       <c r="F15" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="G15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="H15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
@@ -1780,14 +1830,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="S15" s="6"/>
+      <c r="S15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T15" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.305)</f>
+        <v>3.305</v>
       </c>
       <c r="U15" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1016666666666668)</f>
+        <v>1.101666667</v>
       </c>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
@@ -1824,12 +1877,12 @@
         <v>1.3</v>
       </c>
       <c r="F16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="H16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
@@ -1875,14 +1928,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S16" s="6"/>
+      <c r="S16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T16" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.26)</f>
-        <v>3.26</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7900000000000005)</f>
+        <v>3.79</v>
       </c>
       <c r="U16" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0866666666666667)</f>
-        <v>1.086666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2633333333333334)</f>
+        <v>1.263333333</v>
       </c>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
@@ -1919,8 +1975,8 @@
         <v>1.5</v>
       </c>
       <c r="F17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -1970,14 +2026,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S17" s="6"/>
+      <c r="S17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T17" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8449999999999998)</f>
-        <v>2.845</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.245)</f>
+        <v>3.245</v>
       </c>
       <c r="U17" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9483333333333333)</f>
-        <v>0.9483333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0816666666666668)</f>
+        <v>1.081666667</v>
       </c>
       <c r="V17" s="6"/>
       <c r="W17" s="6"/>
@@ -2014,8 +2073,8 @@
         <v>1.5</v>
       </c>
       <c r="F18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -2065,14 +2124,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S18" s="6"/>
+      <c r="S18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="T18" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.465)</f>
-        <v>3.465</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.865)</f>
+        <v>3.865</v>
       </c>
       <c r="U18" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.155)</f>
-        <v>1.155</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2883333333333333)</f>
+        <v>1.288333333</v>
       </c>
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
@@ -2109,12 +2171,12 @@
         <v>2</v>
       </c>
       <c r="F19" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -2160,14 +2222,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S19" s="6"/>
+      <c r="S19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T19" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.03)</f>
-        <v>3.03</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.46)</f>
+        <v>3.46</v>
       </c>
       <c r="U19" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
-        <v>1.01</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1533333333333333)</f>
+        <v>1.153333333</v>
       </c>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
@@ -2204,12 +2269,12 @@
         <v>2.4</v>
       </c>
       <c r="F20" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="H20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -2255,14 +2320,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S20" s="6"/>
+      <c r="S20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T20" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.825)</f>
-        <v>3.825</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2700000000000005)</f>
+        <v>4.27</v>
       </c>
       <c r="U20" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2750000000000001)</f>
-        <v>1.275</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4233333333333336)</f>
+        <v>1.423333333</v>
       </c>
       <c r="V20" s="6"/>
       <c r="W20" s="6"/>
@@ -2299,12 +2367,12 @@
         <v>2.2</v>
       </c>
       <c r="F21" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -2350,14 +2418,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S21" s="6"/>
+      <c r="S21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T21" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5649999999999995)</f>
-        <v>3.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.01)</f>
+        <v>4.01</v>
       </c>
       <c r="U21" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1883333333333332)</f>
-        <v>1.188333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3366666666666667)</f>
+        <v>1.336666667</v>
       </c>
       <c r="V21" s="6"/>
       <c r="W21" s="6"/>
@@ -2394,12 +2465,12 @@
         <v>2.2</v>
       </c>
       <c r="F22" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
@@ -2445,14 +2516,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S22" s="6"/>
+      <c r="S22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T22" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.965)</f>
-        <v>2.965</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4250000000000003)</f>
+        <v>3.425</v>
       </c>
       <c r="U22" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9883333333333333)</f>
-        <v>0.9883333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1416666666666668)</f>
+        <v>1.141666667</v>
       </c>
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
@@ -2489,12 +2563,12 @@
         <v>2</v>
       </c>
       <c r="F23" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
@@ -2540,14 +2614,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S23" s="6"/>
+      <c r="S23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T23" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.925)</f>
-        <v>2.925</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.355)</f>
+        <v>3.355</v>
       </c>
       <c r="U23" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.975)</f>
-        <v>0.975</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1183333333333334)</f>
+        <v>1.118333333</v>
       </c>
       <c r="V23" s="6"/>
       <c r="W23" s="6"/>
@@ -2584,12 +2661,12 @@
         <v>2</v>
       </c>
       <c r="F24" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -2635,14 +2712,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S24" s="6"/>
+      <c r="S24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T24" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9000000000000004)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.315)</f>
+        <v>3.315</v>
       </c>
       <c r="U24" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9666666666666668)</f>
-        <v>0.9666666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.105)</f>
+        <v>1.105</v>
       </c>
       <c r="V24" s="6"/>
       <c r="W24" s="6"/>
@@ -2679,12 +2759,12 @@
         <v>1.4</v>
       </c>
       <c r="F25" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="H25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -2730,14 +2810,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S25" s="6"/>
+      <c r="S25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T25" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6550000000000002)</f>
-        <v>3.655</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="U25" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2183333333333335)</f>
-        <v>1.218333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3666666666666665)</f>
+        <v>1.366666667</v>
       </c>
       <c r="V25" s="6"/>
       <c r="W25" s="6"/>
@@ -2774,12 +2857,12 @@
         <v>1.4</v>
       </c>
       <c r="F26" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="G26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
-        <v>3.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="H26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
@@ -2825,14 +2908,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S26" s="6"/>
+      <c r="S26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T26" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2150000000000003)</f>
-        <v>3.215</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4300000000000006)</f>
+        <v>3.43</v>
       </c>
       <c r="U26" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0716666666666668)</f>
-        <v>1.071666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1433333333333335)</f>
+        <v>1.143333333</v>
       </c>
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
@@ -2869,12 +2955,12 @@
         <v>2.5</v>
       </c>
       <c r="F27" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -2920,14 +3006,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S27" s="6"/>
+      <c r="S27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T27" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.125)</f>
-        <v>3.125</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5999999999999996)</f>
+        <v>3.6</v>
       </c>
       <c r="U27" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0416666666666667)</f>
-        <v>1.041666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
       </c>
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
@@ -2964,8 +3053,8 @@
         <v>1.5</v>
       </c>
       <c r="F28" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3015,14 +3104,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S28" s="6"/>
+      <c r="S28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T28" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.645)</f>
-        <v>2.645</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.745)</f>
+        <v>2.745</v>
       </c>
       <c r="U28" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8816666666666667)</f>
-        <v>0.8816666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.915)</f>
+        <v>0.915</v>
       </c>
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
@@ -3063,8 +3155,8 @@
         <v>3</v>
       </c>
       <c r="G29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -3110,14 +3202,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="S29" s="6"/>
+      <c r="S29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="T29" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.34)</f>
-        <v>3.34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.355)</f>
+        <v>3.355</v>
       </c>
       <c r="U29" s="9">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1133333333333333)</f>
-        <v>1.113333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1183333333333334)</f>
+        <v>1.118333333</v>
       </c>
       <c r="V29" s="6"/>
       <c r="W29" s="6"/>
@@ -3147,6 +3242,11 @@
   <conditionalFormatting sqref="R2:R29">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
       <formula>2.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T29">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
   <drawing r:id="rId1"/>
@@ -3242,10 +3342,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr4")</f>
         <v>Tr4</v>
       </c>
-      <c r="Q1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta2")</f>
-        <v>Ta2</v>
-      </c>
+      <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
@@ -3825,16 +3922,16 @@
         <v>5</v>
       </c>
       <c r="G8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="H8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="I8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3861,24 +3958,24 @@
         <v>5</v>
       </c>
       <c r="P8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.565)</f>
-        <v>4.565</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.625)</f>
+        <v>4.625</v>
       </c>
       <c r="T8" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5216666666666667)</f>
-        <v>1.521666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5416666666666667)</f>
+        <v>1.541666667</v>
       </c>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="X8" s="6"/>
       <c r="Y8" s="6">
@@ -5772,7 +5869,8 @@
     <col customWidth="1" min="18" max="18" width="7.13"/>
     <col customWidth="1" min="19" max="19" width="5.88"/>
     <col customWidth="1" min="20" max="20" width="6.88"/>
-    <col customWidth="1" min="21" max="22" width="3.88"/>
+    <col customWidth="1" min="21" max="21" width="10.88"/>
+    <col customWidth="1" min="22" max="22" width="8.5"/>
     <col customWidth="1" min="23" max="23" width="7.75"/>
     <col customWidth="1" min="24" max="24" width="3.88"/>
     <col customWidth="1" min="25" max="25" width="7.75"/>
@@ -5914,17 +6012,20 @@
         <v>3.3</v>
       </c>
       <c r="F2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="G2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
-      </c>
-      <c r="H2" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="I2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="J2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -5966,20 +6067,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T2" s="6"/>
+      <c r="T2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U2" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5349999999999993)</f>
-        <v>3.535</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7199999999999998)</f>
+        <v>3.72</v>
       </c>
       <c r="V2" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.178333333333333)</f>
-        <v>1.178333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
+        <v>1.24</v>
       </c>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
       <c r="Y2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="Z2" s="6"/>
       <c r="AA2" s="6">
@@ -6019,17 +6123,20 @@
         <v>2.2</v>
       </c>
       <c r="F3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="G3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="H3" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
       <c r="I3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="J3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -6071,20 +6178,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T3" s="6"/>
+      <c r="T3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U3" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2300000000000004)</f>
-        <v>3.23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5450000000000004)</f>
+        <v>3.545</v>
       </c>
       <c r="V3" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0766666666666669)</f>
-        <v>1.076666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1816666666666669)</f>
+        <v>1.181666667</v>
       </c>
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Z3" s="6"/>
       <c r="AA3" s="6">
@@ -6124,17 +6234,20 @@
         <v>2.4</v>
       </c>
       <c r="F4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="G4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H4" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -6176,20 +6289,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T4" s="6"/>
+      <c r="T4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U4" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.315)</f>
-        <v>3.315</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7350000000000003)</f>
+        <v>3.735</v>
       </c>
       <c r="V4" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.105)</f>
-        <v>1.105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.245)</f>
+        <v>1.245</v>
       </c>
       <c r="W4" s="6"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z4" s="6"/>
       <c r="AA4" s="6">
@@ -6229,17 +6345,20 @@
         <v>2.8</v>
       </c>
       <c r="F5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="G5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
-      </c>
-      <c r="H5" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="I5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -6281,20 +6400,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T5" s="6"/>
+      <c r="T5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U5" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.54)</f>
-        <v>2.54</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1850000000000005)</f>
+        <v>3.185</v>
       </c>
       <c r="V5" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8466666666666667)</f>
-        <v>0.8466666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0616666666666668)</f>
+        <v>1.061666667</v>
       </c>
       <c r="W5" s="6"/>
       <c r="X5" s="6"/>
       <c r="Y5" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="Z5" s="6"/>
       <c r="AA5" s="6">
@@ -6334,8 +6456,8 @@
         <v>0</v>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
@@ -6386,14 +6508,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="T6" s="6"/>
+      <c r="T6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="U6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6300000000000001)</f>
-        <v>1.63</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4300000000000002)</f>
+        <v>1.43</v>
       </c>
       <c r="V6" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5433333333333333)</f>
-        <v>0.5433333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.47666666666666674)</f>
+        <v>0.4766666667</v>
       </c>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
@@ -6439,17 +6564,20 @@
         <v>3.2</v>
       </c>
       <c r="F7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
-      </c>
-      <c r="H7" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="I7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="J7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -6491,20 +6619,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T7" s="6"/>
+      <c r="T7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U7" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.57)</f>
-        <v>3.57</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="V7" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.19)</f>
-        <v>1.19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4333333333333333)</f>
+        <v>1.433333333</v>
       </c>
       <c r="W7" s="6"/>
       <c r="X7" s="6"/>
       <c r="Y7" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z7" s="6"/>
       <c r="AA7" s="6">
@@ -6544,17 +6675,20 @@
         <v>3.2</v>
       </c>
       <c r="F8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="G8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="I8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
-      </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
       </c>
       <c r="J8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -6596,20 +6730,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T8" s="6"/>
+      <c r="T8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U8" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3299999999999996)</f>
-        <v>3.33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.62)</f>
+        <v>3.62</v>
       </c>
       <c r="V8" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1099999999999999)</f>
-        <v>1.11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2066666666666668)</f>
+        <v>1.206666667</v>
       </c>
       <c r="W8" s="6"/>
       <c r="X8" s="6"/>
       <c r="Y8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z8" s="6"/>
       <c r="AA8" s="6">
@@ -6649,17 +6786,20 @@
         <v>1.9</v>
       </c>
       <c r="F9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H9" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="I9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -6701,20 +6841,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T9" s="6"/>
+      <c r="T9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U9" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.71)</f>
-        <v>2.71</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.14)</f>
+        <v>3.14</v>
       </c>
       <c r="V9" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9033333333333333)</f>
-        <v>0.9033333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0466666666666666)</f>
+        <v>1.046666667</v>
       </c>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="Z9" s="6"/>
       <c r="AA9" s="6">
@@ -6754,17 +6897,20 @@
         <v>3.2</v>
       </c>
       <c r="F10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="G10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
-      </c>
-      <c r="H10" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -6806,20 +6952,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T10" s="6"/>
+      <c r="T10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U10" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.735)</f>
-        <v>3.735</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3500000000000005)</f>
+        <v>4.35</v>
       </c>
       <c r="V10" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2449999999999999)</f>
-        <v>1.245</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4500000000000002)</f>
+        <v>1.45</v>
       </c>
       <c r="W10" s="6"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Z10" s="6"/>
       <c r="AA10" s="6">
@@ -6859,17 +7008,20 @@
         <v>2.5</v>
       </c>
       <c r="F11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="G11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H11" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -6911,20 +7063,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T11" s="6"/>
+      <c r="T11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U11" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9699999999999998)</f>
-        <v>2.97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1999999999999997)</f>
+        <v>3.2</v>
       </c>
       <c r="V11" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9899999999999999)</f>
-        <v>0.99</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0666666666666667)</f>
+        <v>1.066666667</v>
       </c>
       <c r="W11" s="6"/>
       <c r="X11" s="6"/>
       <c r="Y11" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z11" s="6"/>
       <c r="AA11" s="6">
@@ -6964,17 +7119,20 @@
         <v>1.7</v>
       </c>
       <c r="F12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H12" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
       <c r="I12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="J12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -7016,20 +7174,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T12" s="6"/>
+      <c r="T12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U12" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.25)</f>
-        <v>3.25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.665)</f>
+        <v>3.665</v>
       </c>
       <c r="V12" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0833333333333333)</f>
-        <v>1.083333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2216666666666667)</f>
+        <v>1.221666667</v>
       </c>
       <c r="W12" s="6"/>
       <c r="X12" s="6"/>
       <c r="Y12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z12" s="6"/>
       <c r="AA12" s="6">
@@ -7069,17 +7230,20 @@
         <v>2.8</v>
       </c>
       <c r="F13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
-      </c>
-      <c r="H13" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -7121,20 +7285,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T13" s="6"/>
+      <c r="T13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U13" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.595)</f>
-        <v>3.595</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3100000000000005)</f>
+        <v>4.31</v>
       </c>
       <c r="V13" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1983333333333335)</f>
-        <v>1.198333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4366666666666668)</f>
+        <v>1.436666667</v>
       </c>
       <c r="W13" s="6"/>
       <c r="X13" s="6"/>
       <c r="Y13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Z13" s="6"/>
       <c r="AA13" s="6">
@@ -7174,17 +7341,20 @@
         <v>1.3</v>
       </c>
       <c r="F14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
-      </c>
-      <c r="H14" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="H14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="I14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="J14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -7226,20 +7396,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T14" s="6"/>
+      <c r="T14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U14" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.385)</f>
-        <v>2.385</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2050000000000005)</f>
+        <v>3.205</v>
       </c>
       <c r="V14" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7949999999999999)</f>
-        <v>0.795</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0683333333333336)</f>
+        <v>1.068333333</v>
       </c>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
       <c r="Y14" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="Z14" s="6"/>
       <c r="AA14" s="6">
@@ -7354,17 +7527,20 @@
         <v>2.9</v>
       </c>
       <c r="F16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="G16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
-      </c>
-      <c r="H16" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="I16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="J16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -7406,20 +7582,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T16" s="6"/>
+      <c r="T16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U16" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.73)</f>
-        <v>2.73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.005)</f>
+        <v>3.005</v>
       </c>
       <c r="V16" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.91)</f>
-        <v>0.91</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0016666666666667)</f>
+        <v>1.001666667</v>
       </c>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
       <c r="Y16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z16" s="6"/>
       <c r="AA16" s="6">
@@ -7459,17 +7638,20 @@
         <v>2.8</v>
       </c>
       <c r="F17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H17" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="I17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="J17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -7511,20 +7693,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T17" s="6"/>
+      <c r="T17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U17" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.875)</f>
-        <v>2.875</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3200000000000003)</f>
+        <v>3.32</v>
       </c>
       <c r="V17" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9583333333333334)</f>
-        <v>0.9583333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1066666666666667)</f>
+        <v>1.106666667</v>
       </c>
       <c r="W17" s="6"/>
       <c r="X17" s="6"/>
       <c r="Y17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z17" s="6"/>
       <c r="AA17" s="6">
@@ -7564,17 +7749,20 @@
         <v>2.5</v>
       </c>
       <c r="F18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="G18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
-      </c>
-      <c r="H18" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="H18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
       <c r="I18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
       </c>
       <c r="J18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -7616,20 +7804,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="T18" s="6"/>
+      <c r="T18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="U18" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.975)</f>
-        <v>1.975</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.03)</f>
+        <v>2.03</v>
       </c>
       <c r="V18" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6583333333333333)</f>
-        <v>0.6583333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6766666666666666)</f>
+        <v>0.6766666667</v>
       </c>
       <c r="W18" s="6"/>
       <c r="X18" s="6"/>
       <c r="Y18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="Z18" s="6"/>
       <c r="AA18" s="6">
@@ -7669,17 +7860,20 @@
         <v>2.6</v>
       </c>
       <c r="F19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
       </c>
       <c r="G19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="H19" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="I19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="J19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -7721,20 +7915,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T19" s="6"/>
+      <c r="T19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U19" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0300000000000002)</f>
-        <v>3.03</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.105)</f>
+        <v>3.105</v>
       </c>
       <c r="V19" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.01)</f>
-        <v>1.01</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.035)</f>
+        <v>1.035</v>
       </c>
       <c r="W19" s="6"/>
       <c r="X19" s="6"/>
       <c r="Y19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Z19" s="6"/>
       <c r="AA19" s="6">
@@ -7774,17 +7971,20 @@
         <v>3.8</v>
       </c>
       <c r="F20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="I20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="J20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -7826,14 +8026,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="T20" s="6"/>
+      <c r="T20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U20" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8249999999999997)</f>
-        <v>3.825</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.325)</f>
+        <v>4.325</v>
       </c>
       <c r="V20" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.275)</f>
-        <v>1.275</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4416666666666667)</f>
+        <v>1.441666667</v>
       </c>
       <c r="W20" s="6"/>
       <c r="X20" s="6"/>
@@ -7879,17 +8082,20 @@
         <v>2.9</v>
       </c>
       <c r="F21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
       </c>
       <c r="G21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="H21" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="I21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="J21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -7931,20 +8137,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T21" s="6"/>
+      <c r="T21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U21" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1450000000000005)</f>
-        <v>3.145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="V21" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0483333333333336)</f>
-        <v>1.048333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1333333333333333)</f>
+        <v>1.133333333</v>
       </c>
       <c r="W21" s="6"/>
       <c r="X21" s="6"/>
       <c r="Y21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Z21" s="6"/>
       <c r="AA21" s="6">
@@ -7984,17 +8193,20 @@
         <v>2.4</v>
       </c>
       <c r="F22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="G22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="I22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="J22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -8036,14 +8248,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T22" s="6"/>
+      <c r="T22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U22" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.47)</f>
-        <v>3.47</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8100000000000005)</f>
+        <v>3.81</v>
       </c>
       <c r="V22" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1566666666666667)</f>
-        <v>1.156666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2700000000000002)</f>
+        <v>1.27</v>
       </c>
       <c r="W22" s="6"/>
       <c r="X22" s="6"/>
@@ -8089,17 +8304,20 @@
         <v>3.3</v>
       </c>
       <c r="F23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="G23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
-      </c>
-      <c r="H23" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="I23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="J23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8141,20 +8359,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T23" s="6"/>
+      <c r="T23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U23" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.56)</f>
-        <v>3.56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.215)</f>
+        <v>4.215</v>
       </c>
       <c r="V23" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1866666666666668)</f>
-        <v>1.186666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.405)</f>
+        <v>1.405</v>
       </c>
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
       <c r="Y23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Z23" s="6"/>
       <c r="AA23" s="6">
@@ -8194,17 +8415,20 @@
         <v>1.5</v>
       </c>
       <c r="F24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
       </c>
       <c r="G24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
-      </c>
-      <c r="H24" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="H24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="I24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
-        <v>1.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="J24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -8246,20 +8470,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T24" s="6"/>
+      <c r="T24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U24" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3100000000000005)</f>
-        <v>2.31</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.73)</f>
+        <v>2.73</v>
       </c>
       <c r="V24" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7700000000000001)</f>
-        <v>0.77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.91)</f>
+        <v>0.91</v>
       </c>
       <c r="W24" s="6"/>
       <c r="X24" s="6"/>
       <c r="Y24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="Z24" s="6"/>
       <c r="AA24" s="6">
@@ -8299,17 +8526,20 @@
         <v>2.7</v>
       </c>
       <c r="F25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="G25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H25" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="I25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="J25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8351,20 +8581,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="T25" s="6"/>
+      <c r="T25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U25" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4000000000000004)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.615)</f>
+        <v>3.615</v>
       </c>
       <c r="V25" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1333333333333335)</f>
-        <v>1.133333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.205)</f>
+        <v>1.205</v>
       </c>
       <c r="W25" s="6"/>
       <c r="X25" s="6"/>
       <c r="Y25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z25" s="6"/>
       <c r="AA25" s="6">
@@ -8404,17 +8637,20 @@
         <v>2.6</v>
       </c>
       <c r="F26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="G26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H26" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
       <c r="I26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="J26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8456,20 +8692,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T26" s="6"/>
+      <c r="T26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U26" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.045)</f>
-        <v>3.045</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.29)</f>
+        <v>3.29</v>
       </c>
       <c r="V26" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.015)</f>
-        <v>1.015</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0966666666666667)</f>
+        <v>1.096666667</v>
       </c>
       <c r="W26" s="6"/>
       <c r="X26" s="6"/>
       <c r="Y26" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z26" s="6"/>
       <c r="AA26" s="6">
@@ -8509,17 +8748,20 @@
         <v>2.9</v>
       </c>
       <c r="F27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
       </c>
       <c r="G27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="H27" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
+      <c r="H27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
       <c r="I27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="J27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -8561,20 +8803,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T27" s="6"/>
+      <c r="T27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="U27" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.765)</f>
-        <v>2.765</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.58)</f>
+        <v>2.58</v>
       </c>
       <c r="V27" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9216666666666667)</f>
-        <v>0.9216666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.86)</f>
+        <v>0.86</v>
       </c>
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
       <c r="Y27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="Z27" s="6"/>
       <c r="AA27" s="6">
@@ -8614,17 +8859,20 @@
         <v>3.2</v>
       </c>
       <c r="F28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="H28" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="I28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="J28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8666,20 +8914,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T28" s="6"/>
+      <c r="T28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U28" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5599999999999996)</f>
-        <v>3.56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.975)</f>
+        <v>3.975</v>
       </c>
       <c r="V28" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1866666666666665)</f>
-        <v>1.186666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.325)</f>
+        <v>1.325</v>
       </c>
       <c r="W28" s="6"/>
       <c r="X28" s="6"/>
       <c r="Y28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Z28" s="6"/>
       <c r="AA28" s="6">
@@ -8719,17 +8970,20 @@
         <v>1.8</v>
       </c>
       <c r="F29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="H29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
+      <c r="I29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
-      </c>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
       </c>
       <c r="J29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -8771,20 +9025,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T29" s="6"/>
+      <c r="T29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U29" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.325)</f>
-        <v>2.325</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.115)</f>
+        <v>3.115</v>
       </c>
       <c r="V29" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.775)</f>
-        <v>0.775</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0383333333333333)</f>
+        <v>1.038333333</v>
       </c>
       <c r="W29" s="6"/>
       <c r="X29" s="6"/>
       <c r="Y29" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
-        <v>3.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="Z29" s="6"/>
       <c r="AA29" s="6">
@@ -8824,17 +9081,20 @@
         <v>2.4</v>
       </c>
       <c r="F30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
       </c>
       <c r="G30" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="H30" s="6"/>
+      <c r="H30" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="I30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
@@ -8861,17 +9121,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
+      <c r="T30" s="6"/>
       <c r="U30" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.935)</f>
-        <v>2.935</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.635)</f>
+        <v>2.635</v>
       </c>
       <c r="V30" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9783333333333334)</f>
-        <v>0.9783333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8783333333333333)</f>
+        <v>0.8783333333</v>
       </c>
       <c r="W30" s="6"/>
       <c r="X30" s="6"/>
@@ -8917,17 +9174,20 @@
         <v>2.2</v>
       </c>
       <c r="F31" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="G31" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
-      </c>
-      <c r="H31" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H31" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
       <c r="I31" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="J31" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8969,20 +9229,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T31" s="6"/>
+      <c r="T31" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U31" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.085)</f>
-        <v>3.085</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6000000000000005)</f>
+        <v>3.6</v>
       </c>
       <c r="V31" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0283333333333333)</f>
-        <v>1.028333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2000000000000002)</f>
+        <v>1.2</v>
       </c>
       <c r="W31" s="6"/>
       <c r="X31" s="6"/>
       <c r="Y31" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Z31" s="6"/>
       <c r="AA31" s="6">
@@ -9022,17 +9285,20 @@
         <v>1</v>
       </c>
       <c r="F32" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
       </c>
       <c r="G32" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
-        <v>1.2</v>
-      </c>
-      <c r="H32" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="H32" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
       <c r="I32" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6)</f>
-        <v>0.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="J32" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -9074,20 +9340,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="T32" s="6"/>
+      <c r="T32" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="U32" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5499999999999998)</f>
-        <v>1.55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7500000000000002)</f>
+        <v>1.75</v>
       </c>
       <c r="V32" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5166666666666666)</f>
-        <v>0.5166666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5833333333333334)</f>
+        <v>0.5833333333</v>
       </c>
       <c r="W32" s="6"/>
       <c r="X32" s="6"/>
       <c r="Y32" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
-        <v>1.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
+        <v>1.1</v>
       </c>
       <c r="Z32" s="6"/>
       <c r="AA32" s="6">
@@ -9127,17 +9396,20 @@
         <v>2.4</v>
       </c>
       <c r="F33" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G33" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
-      </c>
-      <c r="H33" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H33" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I33" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J33" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
@@ -9179,20 +9451,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T33" s="6"/>
+      <c r="T33" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U33" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.025)</f>
-        <v>3.025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.455)</f>
+        <v>3.455</v>
       </c>
       <c r="V33" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0083333333333333)</f>
-        <v>1.008333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1516666666666666)</f>
+        <v>1.151666667</v>
       </c>
       <c r="W33" s="6"/>
       <c r="X33" s="6"/>
       <c r="Y33" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Z33" s="6"/>
       <c r="AA33" s="6">
@@ -9232,17 +9507,20 @@
         <v>3</v>
       </c>
       <c r="F34" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G34" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
-      </c>
-      <c r="H34" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H34" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I34" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J34" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -9284,20 +9562,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T34" s="6"/>
+      <c r="T34" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U34" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.645)</f>
-        <v>3.645</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.36)</f>
+        <v>4.36</v>
       </c>
       <c r="V34" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.215)</f>
-        <v>1.215</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4533333333333334)</f>
+        <v>1.453333333</v>
       </c>
       <c r="W34" s="6"/>
       <c r="X34" s="6"/>
       <c r="Y34" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Z34" s="6"/>
       <c r="AA34" s="6">
@@ -9337,17 +9618,20 @@
         <v>2.9</v>
       </c>
       <c r="F35" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="G35" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H35" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H35" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="I35" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J35" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -9389,20 +9673,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T35" s="6"/>
+      <c r="T35" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U35" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.92)</f>
-        <v>2.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.36)</f>
+        <v>3.36</v>
       </c>
       <c r="V35" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9733333333333333)</f>
-        <v>0.9733333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1199999999999999)</f>
+        <v>1.12</v>
       </c>
       <c r="W35" s="6"/>
       <c r="X35" s="6"/>
       <c r="Y35" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="Z35" s="6"/>
       <c r="AA35" s="6">
@@ -9442,17 +9729,20 @@
         <v>2.4</v>
       </c>
       <c r="F36" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="G36" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="H36" s="6"/>
+      <c r="H36" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="I36" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="J36" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -9494,14 +9784,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T36" s="6"/>
+      <c r="T36" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="U36" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.215)</f>
-        <v>3.215</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.315)</f>
+        <v>3.315</v>
       </c>
       <c r="V36" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0716666666666665)</f>
-        <v>1.071666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.105)</f>
+        <v>1.105</v>
       </c>
       <c r="W36" s="6"/>
       <c r="X36" s="6"/>
@@ -9547,17 +9840,20 @@
         <v>2.6</v>
       </c>
       <c r="F37" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="G37" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
-      </c>
-      <c r="H37" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="H37" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="I37" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="J37" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -9599,20 +9895,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T37" s="6"/>
+      <c r="T37" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U37" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.32)</f>
-        <v>2.32</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.88)</f>
+        <v>2.88</v>
       </c>
       <c r="V37" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7733333333333333)</f>
-        <v>0.7733333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.96)</f>
+        <v>0.96</v>
       </c>
       <c r="W37" s="6"/>
       <c r="X37" s="6"/>
       <c r="Y37" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="Z37" s="6"/>
       <c r="AA37" s="6">
@@ -9652,17 +9951,20 @@
         <v>3.4</v>
       </c>
       <c r="F38" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="G38" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H38" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="I38" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
-      </c>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
       </c>
       <c r="J38" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -9704,20 +10006,23 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T38" s="6"/>
+      <c r="T38" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U38" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.515)</f>
-        <v>3.515</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.045000000000001)</f>
+        <v>4.045</v>
       </c>
       <c r="V38" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1716666666666666)</f>
-        <v>1.171666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3483333333333336)</f>
+        <v>1.348333333</v>
       </c>
       <c r="W38" s="6"/>
       <c r="X38" s="6"/>
       <c r="Y38" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Z38" s="6"/>
       <c r="AA38" s="6">
@@ -9750,6 +10055,11 @@
   <conditionalFormatting sqref="T2:T38">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
       <formula>2.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U38">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
   <drawing r:id="rId1"/>
@@ -9896,8 +10206,8 @@
         <v>4</v>
       </c>
       <c r="F2" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="G2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -9945,12 +10255,12 @@
       </c>
       <c r="R2" s="6"/>
       <c r="S2" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.665)</f>
-        <v>4.665</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.565)</f>
+        <v>4.565</v>
       </c>
       <c r="T2" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.555)</f>
-        <v>1.555</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5216666666666667)</f>
+        <v>1.521666667</v>
       </c>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
@@ -9987,8 +10297,8 @@
         <v>4.1</v>
       </c>
       <c r="F3" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="G3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
@@ -10036,12 +10346,12 @@
       </c>
       <c r="R3" s="6"/>
       <c r="S3" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6100000000000003)</f>
-        <v>3.61</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.51)</f>
+        <v>3.51</v>
       </c>
       <c r="T3" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2033333333333334)</f>
-        <v>1.203333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.17)</f>
+        <v>1.17</v>
       </c>
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
@@ -10260,8 +10570,8 @@
         <v>5</v>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G6" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -10309,12 +10619,12 @@
       </c>
       <c r="R6" s="6"/>
       <c r="S6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.49)</f>
-        <v>4.49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.390000000000001)</f>
+        <v>4.39</v>
       </c>
       <c r="T6" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4966666666666668)</f>
-        <v>1.496666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4633333333333336)</f>
+        <v>1.463333333</v>
       </c>
       <c r="U6" s="6"/>
       <c r="V6" s="6"/>
@@ -10439,8 +10749,8 @@
         <v>4</v>
       </c>
       <c r="F8" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="G8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -10488,12 +10798,12 @@
       </c>
       <c r="R8" s="6"/>
       <c r="S8" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.705)</f>
-        <v>4.705</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.625)</f>
+        <v>4.625</v>
       </c>
       <c r="T8" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5683333333333334)</f>
-        <v>1.568333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5416666666666667)</f>
+        <v>1.541666667</v>
       </c>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
@@ -10776,8 +11086,8 @@
         <v>4.2</v>
       </c>
       <c r="F12" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
-        <v>5.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -10825,12 +11135,12 @@
       </c>
       <c r="R12" s="6"/>
       <c r="S12" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.449999999999999)</f>
-        <v>4.45</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.35)</f>
+        <v>4.35</v>
       </c>
       <c r="T12" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4833333333333332)</f>
-        <v>1.483333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.45)</f>
+        <v>1.45</v>
       </c>
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
@@ -10867,8 +11177,8 @@
         <v>4.1</v>
       </c>
       <c r="F13" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="G13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -10916,12 +11226,12 @@
       </c>
       <c r="R13" s="6"/>
       <c r="S13" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.405)</f>
-        <v>4.405</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.305)</f>
+        <v>4.305</v>
       </c>
       <c r="T13" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4683333333333335)</f>
-        <v>1.468333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4349999999999998)</f>
+        <v>1.435</v>
       </c>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
@@ -11049,8 +11359,8 @@
         <v>4.4</v>
       </c>
       <c r="F15" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="G15" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -11098,12 +11408,12 @@
       </c>
       <c r="R15" s="6"/>
       <c r="S15" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.515000000000001)</f>
-        <v>4.515</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.415)</f>
+        <v>4.415</v>
       </c>
       <c r="T15" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5050000000000001)</f>
-        <v>1.505</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4716666666666667)</f>
+        <v>1.471666667</v>
       </c>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
@@ -11140,8 +11450,8 @@
         <v>4.1</v>
       </c>
       <c r="F16" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
@@ -11189,12 +11499,12 @@
       </c>
       <c r="R16" s="6"/>
       <c r="S16" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.415)</f>
-        <v>4.415</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3149999999999995)</f>
+        <v>4.315</v>
       </c>
       <c r="T16" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4716666666666667)</f>
-        <v>1.471666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4383333333333332)</f>
+        <v>1.438333333</v>
       </c>
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
@@ -11413,8 +11723,8 @@
         <v>4.5</v>
       </c>
       <c r="F19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -11462,12 +11772,12 @@
       </c>
       <c r="R19" s="6"/>
       <c r="S19" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.485)</f>
-        <v>4.485</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.385000000000001)</f>
+        <v>4.385</v>
       </c>
       <c r="T19" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.495)</f>
-        <v>1.495</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.461666666666667)</f>
+        <v>1.461666667</v>
       </c>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
@@ -11595,8 +11905,8 @@
         <v>5</v>
       </c>
       <c r="F21" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="G21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -11644,12 +11954,12 @@
       </c>
       <c r="R21" s="6"/>
       <c r="S21" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.61)</f>
-        <v>4.61</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.510000000000001)</f>
+        <v>4.51</v>
       </c>
       <c r="T21" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5366666666666668)</f>
-        <v>1.536666667</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5033333333333336)</f>
+        <v>1.503333333</v>
       </c>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
@@ -11686,8 +11996,8 @@
         <v>5</v>
       </c>
       <c r="F22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.4)</f>
-        <v>5.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -11735,12 +12045,12 @@
       </c>
       <c r="R22" s="6"/>
       <c r="S22" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.680000000000001)</f>
-        <v>4.68</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6000000000000005)</f>
+        <v>4.6</v>
       </c>
       <c r="T22" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5600000000000003)</f>
-        <v>1.56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5333333333333334)</f>
+        <v>1.533333333</v>
       </c>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
@@ -11777,8 +12087,8 @@
         <v>5</v>
       </c>
       <c r="F23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -11826,12 +12136,12 @@
       </c>
       <c r="R23" s="6"/>
       <c r="S23" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.2)</f>
-        <v>5.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="T23" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7333333333333334)</f>
-        <v>1.733333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6666666666666667)</f>
+        <v>1.666666667</v>
       </c>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
@@ -11868,8 +12178,8 @@
         <v>4.4</v>
       </c>
       <c r="F24" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
-        <v>3.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -11917,12 +12227,12 @@
       </c>
       <c r="R24" s="6"/>
       <c r="S24" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.26)</f>
-        <v>4.26</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.24)</f>
+        <v>4.24</v>
       </c>
       <c r="T24" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.42)</f>
-        <v>1.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4133333333333333)</f>
+        <v>1.413333333</v>
       </c>
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
@@ -11959,8 +12269,8 @@
         <v>5</v>
       </c>
       <c r="F25" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="G25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -12008,12 +12318,12 @@
       </c>
       <c r="R25" s="6"/>
       <c r="S25" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.365)</f>
-        <v>4.365</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.265000000000001)</f>
+        <v>4.265</v>
       </c>
       <c r="T25" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.455)</f>
-        <v>1.455</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4216666666666669)</f>
+        <v>1.421666667</v>
       </c>
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
@@ -12232,8 +12542,8 @@
         <v>4</v>
       </c>
       <c r="F28" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="G28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -12281,12 +12591,12 @@
       </c>
       <c r="R28" s="6"/>
       <c r="S28" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.52)</f>
-        <v>3.52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.42)</f>
+        <v>3.42</v>
       </c>
       <c r="T28" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1733333333333333)</f>
-        <v>1.173333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.14)</f>
+        <v>1.14</v>
       </c>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
@@ -12314,7 +12624,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S28">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThan">
       <formula>2.8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/app_notas_uis.xlsx
+++ b/app_notas_uis.xlsx
@@ -572,7 +572,10 @@
         <v>0.5133333333</v>
       </c>
       <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
+      <c r="W2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.62)</f>
+        <v>1.62</v>
+      </c>
       <c r="X2" s="6"/>
       <c r="Y2" s="5"/>
       <c r="Z2" s="5">
@@ -670,7 +673,10 @@
         <v>1.203333333</v>
       </c>
       <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
+      <c r="W3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.605)</f>
+        <v>3.605</v>
+      </c>
       <c r="X3" s="6"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
@@ -768,7 +774,10 @@
         <v>0.9883333333</v>
       </c>
       <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
+      <c r="W4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0500000000000003)</f>
+        <v>3.05</v>
+      </c>
       <c r="X4" s="6"/>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5">
@@ -866,7 +875,10 @@
         <v>1.21</v>
       </c>
       <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
+      <c r="W5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.63)</f>
+        <v>3.63</v>
+      </c>
       <c r="X5" s="6"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
@@ -964,7 +976,10 @@
         <v>1.176666667</v>
       </c>
       <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
+      <c r="W6" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.52)</f>
+        <v>3.52</v>
+      </c>
       <c r="X6" s="6"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
@@ -1062,7 +1077,10 @@
         <v>0.9283333333</v>
       </c>
       <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
+      <c r="W7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8249999999999997)</f>
+        <v>2.825</v>
+      </c>
       <c r="X7" s="6"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
@@ -1160,7 +1178,10 @@
         <v>0.8233333333</v>
       </c>
       <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
+      <c r="W8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.585)</f>
+        <v>2.585</v>
+      </c>
       <c r="X8" s="6"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
@@ -1258,7 +1279,10 @@
         <v>1.236666667</v>
       </c>
       <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
+      <c r="W9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
       <c r="X9" s="6"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
@@ -1356,7 +1380,10 @@
         <v>1.223333333</v>
       </c>
       <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
+      <c r="W10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.695)</f>
+        <v>3.695</v>
+      </c>
       <c r="X10" s="6"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
@@ -1454,7 +1481,10 @@
         <v>1.073333333</v>
       </c>
       <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
+      <c r="W11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.29)</f>
+        <v>3.29</v>
+      </c>
       <c r="X11" s="6"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
@@ -1552,7 +1582,10 @@
         <v>1.016666667</v>
       </c>
       <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
+      <c r="W12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.11)</f>
+        <v>3.11</v>
+      </c>
       <c r="X12" s="6"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
@@ -1650,7 +1683,10 @@
         <v>0.6216666667</v>
       </c>
       <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
+      <c r="W13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8250000000000002)</f>
+        <v>1.825</v>
+      </c>
       <c r="X13" s="6"/>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5">
@@ -1748,7 +1784,10 @@
         <v>1.406666667</v>
       </c>
       <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
+      <c r="W14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.205)</f>
+        <v>4.205</v>
+      </c>
       <c r="X14" s="6"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
@@ -1843,7 +1882,10 @@
         <v>1.101666667</v>
       </c>
       <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
+      <c r="W15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.315)</f>
+        <v>3.315</v>
+      </c>
       <c r="X15" s="6"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
@@ -1941,7 +1983,10 @@
         <v>1.263333333</v>
       </c>
       <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
+      <c r="W16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.755)</f>
+        <v>3.755</v>
+      </c>
       <c r="X16" s="6"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
@@ -2039,7 +2084,10 @@
         <v>1.081666667</v>
       </c>
       <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
+      <c r="W17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.245)</f>
+        <v>3.245</v>
+      </c>
       <c r="X17" s="6"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
@@ -2137,7 +2185,10 @@
         <v>1.288333333</v>
       </c>
       <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
+      <c r="W18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.865)</f>
+        <v>3.865</v>
+      </c>
       <c r="X18" s="6"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
@@ -2235,7 +2286,10 @@
         <v>1.153333333</v>
       </c>
       <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
+      <c r="W19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.45)</f>
+        <v>3.45</v>
+      </c>
       <c r="X19" s="6"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
@@ -2333,7 +2387,10 @@
         <v>1.423333333</v>
       </c>
       <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
+      <c r="W20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.25)</f>
+        <v>4.25</v>
+      </c>
       <c r="X20" s="6"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5">
@@ -2431,7 +2488,10 @@
         <v>1.336666667</v>
       </c>
       <c r="V21" s="6"/>
-      <c r="W21" s="6"/>
+      <c r="W21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
@@ -2529,7 +2589,10 @@
         <v>1.141666667</v>
       </c>
       <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
+      <c r="W22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4200000000000004)</f>
+        <v>3.42</v>
+      </c>
       <c r="X22" s="6"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="5">
@@ -2627,7 +2690,10 @@
         <v>1.118333333</v>
       </c>
       <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
+      <c r="W23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.35)</f>
+        <v>3.35</v>
+      </c>
       <c r="X23" s="6"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
@@ -2725,7 +2791,10 @@
         <v>1.105</v>
       </c>
       <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
+      <c r="W24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.31)</f>
+        <v>3.31</v>
+      </c>
       <c r="X24" s="6"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
@@ -2823,7 +2892,10 @@
         <v>1.366666667</v>
       </c>
       <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
+      <c r="W25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="X25" s="6"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
@@ -2921,7 +2993,10 @@
         <v>1.143333333</v>
       </c>
       <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
+      <c r="W26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4650000000000007)</f>
+        <v>3.465</v>
+      </c>
       <c r="X26" s="6"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5">
@@ -3019,7 +3094,10 @@
         <v>1.2</v>
       </c>
       <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
+      <c r="W27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.595)</f>
+        <v>3.595</v>
+      </c>
       <c r="X27" s="6"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
@@ -3117,7 +3195,10 @@
         <v>0.915</v>
       </c>
       <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
+      <c r="W28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.82)</f>
+        <v>2.82</v>
+      </c>
       <c r="X28" s="6"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
@@ -3215,7 +3296,10 @@
         <v>1.118333333</v>
       </c>
       <c r="V29" s="6"/>
-      <c r="W29" s="6"/>
+      <c r="W29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4499999999999997)</f>
+        <v>3.45</v>
+      </c>
       <c r="X29" s="6"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
@@ -6085,7 +6169,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="Z2" s="6"/>
+      <c r="Z2" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5949999999999993)</f>
+        <v>3.595</v>
+      </c>
       <c r="AA2" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261221.0)</f>
         <v>2261221</v>
@@ -6196,7 +6283,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Z3" s="6"/>
+      <c r="Z3" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
+        <v>3.33</v>
+      </c>
       <c r="AA3" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261862.0)</f>
         <v>2261862</v>
@@ -6307,7 +6397,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z4" s="6"/>
+      <c r="Z4" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.665)</f>
+        <v>3.665</v>
+      </c>
       <c r="AA4" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261933.0)</f>
         <v>2261933</v>
@@ -6418,7 +6511,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="Z5" s="6"/>
+      <c r="Z5" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.185)</f>
+        <v>3.185</v>
+      </c>
       <c r="AA5" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262154.0)</f>
         <v>2262154</v>
@@ -6637,7 +6733,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z7" s="6"/>
+      <c r="Z7" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.25)</f>
+        <v>4.25</v>
+      </c>
       <c r="AA7" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261224.0)</f>
         <v>2261224</v>
@@ -6748,7 +6847,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z8" s="6"/>
+      <c r="Z8" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.49)</f>
+        <v>3.49</v>
+      </c>
       <c r="AA8" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262001.0)</f>
         <v>2262001</v>
@@ -6859,7 +6961,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="Z9" s="6"/>
+      <c r="Z9" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.08)</f>
+        <v>3.08</v>
+      </c>
       <c r="AA9" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261874.0)</f>
         <v>2261874</v>
@@ -6970,7 +7075,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Z10" s="6"/>
+      <c r="Z10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.325)</f>
+        <v>4.325</v>
+      </c>
       <c r="AA10" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261914.0)</f>
         <v>2261914</v>
@@ -7081,7 +7189,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z11" s="6"/>
+      <c r="Z11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.09)</f>
+        <v>3.09</v>
+      </c>
       <c r="AA11" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262150.0)</f>
         <v>2262150</v>
@@ -7192,7 +7303,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z12" s="6"/>
+      <c r="Z12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4499999999999997)</f>
+        <v>3.45</v>
+      </c>
       <c r="AA12" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2260424.0)</f>
         <v>2260424</v>
@@ -7303,7 +7417,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Z13" s="6"/>
+      <c r="Z13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3100000000000005)</f>
+        <v>4.31</v>
+      </c>
       <c r="AA13" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262136.0)</f>
         <v>2262136</v>
@@ -7414,7 +7531,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="Z14" s="6"/>
+      <c r="Z14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2550000000000003)</f>
+        <v>3.255</v>
+      </c>
       <c r="AA14" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261756.0)</f>
         <v>2261756</v>
@@ -7600,7 +7720,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z16" s="6"/>
+      <c r="Z16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8200000000000003)</f>
+        <v>2.82</v>
+      </c>
       <c r="AA16" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262090.0)</f>
         <v>2262090</v>
@@ -7711,7 +7834,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z17" s="6"/>
+      <c r="Z17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1650000000000005)</f>
+        <v>3.165</v>
+      </c>
       <c r="AA17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262094.0)</f>
         <v>2262094</v>
@@ -7822,7 +7948,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
         <v>1.9</v>
       </c>
-      <c r="Z18" s="6"/>
+      <c r="Z18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9500000000000002)</f>
+        <v>1.95</v>
+      </c>
       <c r="AA18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261863.0)</f>
         <v>2261863</v>
@@ -7933,7 +8062,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Z19" s="6"/>
+      <c r="Z19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9000000000000004)</f>
+        <v>2.9</v>
+      </c>
       <c r="AA19" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262075.0)</f>
         <v>2262075</v>
@@ -8044,7 +8176,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Z20" s="6"/>
+      <c r="Z20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.185)</f>
+        <v>4.185</v>
+      </c>
       <c r="AA20" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2260425.0)</f>
         <v>2260425</v>
@@ -8155,7 +8290,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Z21" s="6"/>
+      <c r="Z21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.19)</f>
+        <v>3.19</v>
+      </c>
       <c r="AA21" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261219.0)</f>
         <v>2261219</v>
@@ -8266,7 +8404,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Z22" s="6"/>
+      <c r="Z22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.65)</f>
+        <v>3.65</v>
+      </c>
       <c r="AA22" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261864.0)</f>
         <v>2261864</v>
@@ -8377,7 +8518,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Z23" s="6"/>
+      <c r="Z23" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.17)</f>
+        <v>4.17</v>
+      </c>
       <c r="AA23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261216.0)</f>
         <v>2261216</v>
@@ -8488,7 +8632,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
-      <c r="Z24" s="6"/>
+      <c r="Z24" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7100000000000004)</f>
+        <v>2.71</v>
+      </c>
       <c r="AA24" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261215.0)</f>
         <v>2261215</v>
@@ -8599,7 +8746,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z25" s="6"/>
+      <c r="Z25" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.345)</f>
+        <v>3.345</v>
+      </c>
       <c r="AA25" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261195.0)</f>
         <v>2261195</v>
@@ -8710,7 +8860,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z26" s="6"/>
+      <c r="Z26" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.065)</f>
+        <v>3.065</v>
+      </c>
       <c r="AA26" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261681.0)</f>
         <v>2261681</v>
@@ -8748,20 +8901,20 @@
         <v>2.9</v>
       </c>
       <c r="F27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
-        <v>0.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="G27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
       <c r="I27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
-        <v>3.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="J27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -8804,24 +8957,27 @@
         <v>5</v>
       </c>
       <c r="T27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="U27" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.58)</f>
-        <v>2.58</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.06)</f>
+        <v>3.06</v>
       </c>
       <c r="V27" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.86)</f>
-        <v>0.86</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.02)</f>
+        <v>1.02</v>
       </c>
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
       <c r="Y27" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
-      </c>
-      <c r="Z27" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="Z27" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8850000000000002)</f>
+        <v>2.885</v>
+      </c>
       <c r="AA27" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261757.0)</f>
         <v>2261757</v>
@@ -8932,7 +9088,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Z28" s="6"/>
+      <c r="Z28" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.815)</f>
+        <v>3.815</v>
+      </c>
       <c r="AA28" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261218.0)</f>
         <v>2261218</v>
@@ -9043,7 +9202,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="Z29" s="6"/>
+      <c r="Z29" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.04)</f>
+        <v>3.04</v>
+      </c>
       <c r="AA29" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261915.0)</f>
         <v>2261915</v>
@@ -9081,20 +9243,20 @@
         <v>2.4</v>
       </c>
       <c r="F30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
-        <v>0.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="G30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="H30" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
       <c r="I30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
@@ -9121,22 +9283,28 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="T30" s="6"/>
+      <c r="T30" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U30" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.635)</f>
-        <v>2.635</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5500000000000003)</f>
+        <v>3.55</v>
       </c>
       <c r="V30" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8783333333333333)</f>
-        <v>0.8783333333</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1833333333333333)</f>
+        <v>1.183333333</v>
       </c>
       <c r="W30" s="6"/>
       <c r="X30" s="6"/>
       <c r="Y30" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
-      </c>
-      <c r="Z30" s="6"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z30" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.45)</f>
+        <v>3.45</v>
+      </c>
       <c r="AA30" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2202217.0)</f>
         <v>2202217</v>
@@ -9247,7 +9415,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Z31" s="6"/>
+      <c r="Z31" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4299999999999997)</f>
+        <v>3.43</v>
+      </c>
       <c r="AA31" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261881.0)</f>
         <v>2261881</v>
@@ -9358,7 +9529,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
         <v>1.1</v>
       </c>
-      <c r="Z32" s="6"/>
+      <c r="Z32" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
       <c r="AA32" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262036.0)</f>
         <v>2262036</v>
@@ -9469,7 +9643,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="Z33" s="6"/>
+      <c r="Z33" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.395)</f>
+        <v>3.395</v>
+      </c>
       <c r="AA33" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262165.0)</f>
         <v>2262165</v>
@@ -9580,7 +9757,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="Z34" s="6"/>
+      <c r="Z34" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.359999999999999)</f>
+        <v>4.36</v>
+      </c>
       <c r="AA34" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262141.0)</f>
         <v>2262141</v>
@@ -9691,7 +9871,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="Z35" s="6"/>
+      <c r="Z35" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2950000000000004)</f>
+        <v>3.295</v>
+      </c>
       <c r="AA35" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262202.0)</f>
         <v>2262202</v>
@@ -9802,7 +9985,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Z36" s="6"/>
+      <c r="Z36" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.08)</f>
+        <v>3.08</v>
+      </c>
       <c r="AA36" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262161.0)</f>
         <v>2262161</v>
@@ -9913,7 +10099,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="Z37" s="6"/>
+      <c r="Z37" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.835)</f>
+        <v>2.835</v>
+      </c>
       <c r="AA37" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261809.0)</f>
         <v>2261809</v>
@@ -10024,7 +10213,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="Z38" s="6"/>
+      <c r="Z38" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9600000000000004)</f>
+        <v>3.96</v>
+      </c>
       <c r="AA38" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262214.0)</f>
         <v>2262214</v>
